--- a/Streamlit/Data/knowledge_base.xlsx
+++ b/Streamlit/Data/knowledge_base.xlsx
@@ -3230,7 +3230,7 @@
     <t>Bayesian inference is a statistical method for updating the probability of a hypothesis based on new evidence., "It works by using Bayes theorem to calculate the posterior distribution of the hypothesis given the new evidence, taking into account prior knowledge and uncertainty.", Bayesian inference is important because it allows us to quantify uncertainty and make predictions in complex systems with incomplete data., Typical applications include Bayesian regression, Bayesian classification, and Bayesian time series analysis.</t>
   </si>
   <si>
-    <t>{What the analytical method is: Expectation-Maximization (EM) is a statistical algorithm for finding maximum likelihood estimates of parameters in probabilistic models., How it works: The EM algorithm iteratively updates the model parameters and the unobserved variables until convergence, alternating between two steps: expectation (E-step) and maximization (M-step)., Why it is important: EM is essential for handling missing data and identifying underlying patterns in datasets. It is widely used in various applications, including clustering, classification, and dimensionality reduction., Its typical applications: EM is commonly employed in machine learning tasks such as cluster analysis, anomaly detection, and feature extraction.}</t>
+    <t>Expectation-Maximization (EM) is an iterative optimization algorithm for estimating parameters of probabilistic models when the data contain latent or unobserved variables, alternating between an Expectation (E) step that estimates the latent-variable distribution and a Maximization (M) step that updates model parameters. It is particularly relevant to problems such as Gaussian mixture model clustering, missing-data estimation, and other latent-variable models where direct maximum-likelihood estimation is difficult. EM is important because it transforms a difficult optimization involving hidden information into a sequence of more tractable estimation problems, with each iteration guaranteed not to decrease the observed-data likelihood under standard conditions. The general EM algorithm was formally named and popularized by Arthur Dempster, Nan Laird, and Donald Rubin in their influential 1977 paper, although related iterative estimation techniques existed earlier.</t>
   </si>
   <si>
     <t>{What the analytical method is: Decision Rules are a type of analytical technique that involves making decisions based on predefined rules., How it works: The decision-making process follows a set of rules, which are applied to input data to generate output or predictions., Why it is important: Decision Rules provide a transparent and interpretable way to make predictions or classify instances., Its typical applications: Decision Rules are often used in classification problems where the goal is to predict a categorical label based on input features.}</t>
@@ -3284,7 +3284,7 @@
     <t>{What the analytical method is: Convolutional Neural Networks (CNNs) are a type of neural network architecture., How it works: They work by applying multiple convolution and downsampling operations followed by fully connected layers to classify images., Why it is important: CNNs have been instrumental in achieving state-of-the-art results in image classification tasks, object detection, and segmentation., Its typical applications: CNNs are widely used in computer vision tasks such as image classification, object detection, and image generation.}</t>
   </si>
   <si>
-    <t>{What the analytical method is: As Features is a technique used to select relevant features from a dataset, often in the context of classification or regression problems., How it works: It typically involves evaluating the importance or relevance of each feature using various metrics such as mutual information, correlation coefficient, or recursive feature elimination (RFE), and selecting the top-ranked features for further analysis or modeling., Why it is important: Feature selection is crucial in machine learning to prevent overfitting, improve model interpretability, reduce dimensionality, and enhance prediction performance. By identifying the most relevant features, analysts can focus on the most informative variables and develop more accurate models., Its typical applications: As Features has been applied extensively in various domains such as text classification, image analysis, gene expression data analysis, and recommender systems.}</t>
+    <t>practice of transforming information, model outputs, or derived measurements into variables that serve as inputs to another statistical or machine-learning model. For example, cluster assignments, embeddings, predicted probabilities, dates, text-derived measurements, or aggregated historical behavior can all be represented as features for a downstream model. This approach is relevant to feature engineering, representation learning, ensemble methods, and multi-stage ML pipelines because it allows information discovered in one processing step to become predictive information for another. It is important because model performance often depends as much on how useful information is represented as features as on the choice of learning algorithm itself, although care must be taken to prevent problems such as target leakage.</t>
   </si>
   <si>
     <t>Translation invariance is a property of neural networks that refers to their ability to maintain performance even when the input data is shifted, rotated, or transformed in some other way., This property is achieved through the use of convolutional and pooling layers in deep learning architectures, which allow the network to learn features that are invariant to these transformations., Translation invariance is an important concept in computer vision and image processing because it enables the extraction of meaningful features from images without being sensitive to their spatial location or orientation., Typically, translation invariance is applied in tasks such as image classification, object detection, and segmentation.</t>
@@ -3404,7 +3404,7 @@
     <t>{What the analytical method is: Contrastive learning is a type of unsupervised machine learning algorithm that aims to learn representations by contrasting similar and dissimilar inputs., How it works: "The method involves two main steps: positive pair sampling, where similar input pairs are generated, and negative pair sampling, where dissimilar input pairs are generated. A contrastive loss function is then used to update the models parameters.", Why it is important: Contrastive learning has been shown to be effective in learning robust and transferable representations, which can improve the performance of downstream tasks., Its typical applications: Contrastive learning has applications in image classification, object detection, and recommendation systems.}</t>
   </si>
   <si>
-    <t>Autoencoding is a type of unsupervised learning algorithm that learns to compress and reconstruct input data., It works by defining an encoder network that maps the input data to a lower-dimensional latent space, and a decoder network that maps the latent space back to the original input data., The importance of autoencoding lies in its ability to learn compact representations of high-dimensional data, which can be useful for dimensionality reduction, anomaly detection, and generative modeling., Autoencoding is typically applied in areas such as image compression, text processing, and recommender systems.</t>
+    <t>Autoencoding is an unsupervised representation-learning technique in which a neural network learns to reconstruct its input after passing it through an intermediate latent representation, typically using an encoder and decoder. It is relevant when learning compact representations of high-dimensional data, particularly for dimensionality reduction, feature extraction, denoising, anomaly detection, and generative modeling. Autoencoding is important because the reconstruction objective allows useful features and structure to be learned from unlabeled data, while constraints such as a bottleneck, sparsity, or noise prevent the model from simply copying its input. Autoencoders developed from neural-network research into efficient data representations, with important early work appearing in the 1980s and later becoming prominent in deep learning through multilayer and variational architectures.</t>
   </si>
   <si>
     <t>Metric learning is a subfield of machine learning that focuses on learning distance metrics from data., It works by minimizing the difference between the learned metric and the true underlying metric, often using kernel-based methods or probabilistic approaches., Metric learning is important because it allows for more effective clustering, classification, and other tasks that rely on similarity measurements., It has applications in image recognition, natural language processing, and information retrieval.</t>
@@ -3508,7 +3508,7 @@
     <t>Linear Support Vector Classification (LinearSVC) is a supervised machine learning algorithm. It works by finding the optimal hyperplane that separates classes in the feature space, maximally preserving class separability. This method is important because it provides a simple and interpretable way to perform classification tasks with linear decision boundaries. Typical applications include image classification, text classification, and recommender systems.</t>
   </si>
   <si>
-    <t>MeanShift is a non-parametric, adaptive density-based clustering algorithm that automatically determines the number of clusters in the data. It works by iteratively shifting the centroids of overlapping Gaussian distributions towards higher-density regions until convergence. This method is important because it can handle complex, high-dimensional datasets and does not require any prior knowledge about the underlying structure. Typical applications include image segmentation, object tracking, and bioinformatics.</t>
+    <t>MeanShift is a non-parametric clustering algorithm that iteratively moves candidate cluster centers toward regions of higher estimated data density until they converge on local density modes. Unlike methods such as K-means, it does not require the number of clusters to be specified beforehand, but instead relies heavily on a bandwidth parameter that determines the neighborhood used for estimating density. It is relevant when clusters may have irregular distributions or when the appropriate number of clusters is unknown, although it can become computationally expensive for large or high-dimensional datasets. MeanShift originated in pattern-recognition research by Fukunaga and Hostetler in 1975 and was later popularized particularly in computer vision and image segmentation.</t>
   </si>
   <si>
     <t>NuSVR is a type of Support Vector Regression algorithm that uses a nu-regression parameter to control the fraction of training errors. It works by mapping the input data into a high-dimensional feature space using a kernel function, and then finding the optimal hyperplane in this space. The importance of NuSVR lies in its ability to handle non-linear relationships between inputs and outputs, making it useful for regression problems with complex underlying structures. Typically, NuSVR is applied to real-world problems such as forecasting, modeling, or prediction.</t>

--- a/Streamlit/Data/knowledge_base.xlsx
+++ b/Streamlit/Data/knowledge_base.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="275">
   <si>
     <t>Process</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Problem Definition</t>
   </si>
   <si>
+    <t>Python String Documentation</t>
+  </si>
+  <si>
     <t>Training</t>
   </si>
   <si>
@@ -458,6 +461,27 @@
   </si>
   <si>
     <t>Analytical Object Type</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
+  <si>
+    <t>Returns</t>
+  </si>
+  <si>
+    <t>Date Created</t>
+  </si>
+  <si>
+    <t>Date Last Modified</t>
+  </si>
+  <si>
+    <t>Usage</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Required Functions</t>
   </si>
   <si>
     <t>S-shaped mathematical function that transforms unbounded input values into a bounded range, most commonly between 0 and 1, making it particularly useful in logistic regression, probability estimation, and neural networks. Bounding provides stability and diminishing sensitivity to extreme values, but this compression also reduces distinctions between very large or small inputs and can contribute to vanishing gradients in neural networks; while it may moderate the influence of extreme values. The logistic sigmoid originated from the logistic function developed by Belgian mathematician Pierre François Verhulst in the 1830s to model population growth. Its combination of nonlinearity, bounded output, and smooth transitions has made it an important function in statistical modeling and machine learning.</t>
@@ -1167,7 +1191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1192,13 +1216,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1206,13 +1230,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1220,13 +1244,13 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1234,16 +1258,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1251,13 +1275,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1265,13 +1289,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1282,13 +1306,13 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1299,13 +1323,13 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1316,13 +1340,13 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1333,13 +1357,13 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1350,13 +1374,13 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="E12" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1367,13 +1391,13 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E13" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1384,13 +1408,13 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1401,13 +1425,13 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E15" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1418,13 +1442,13 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E16" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1435,13 +1459,13 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E17" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1452,13 +1476,13 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E18" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1469,13 +1493,13 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1486,13 +1510,13 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E20" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1503,13 +1527,13 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1517,16 +1541,16 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E22" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1534,16 +1558,16 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1551,16 +1575,16 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E24" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1568,16 +1592,16 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E25" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1585,16 +1609,16 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E26" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1602,16 +1626,16 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E27" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1619,16 +1643,16 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E28" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1636,16 +1660,16 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E29" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1653,16 +1677,16 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E30" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1670,16 +1694,16 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E31" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1687,16 +1711,16 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E32" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1704,16 +1728,16 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E33" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1721,16 +1745,16 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E34" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1738,16 +1762,16 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D35" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E35" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1755,16 +1779,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E36" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1772,16 +1796,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D37" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E37" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1789,16 +1813,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D38" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E38" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1806,16 +1830,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D39" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E39" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1823,16 +1847,16 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E40" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1840,16 +1864,16 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E41" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1857,16 +1881,16 @@
         <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D42" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E42" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1874,16 +1898,16 @@
         <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D43" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E43" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1891,16 +1915,16 @@
         <v>13</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="E44" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1908,16 +1932,16 @@
         <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E45" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1925,16 +1949,16 @@
         <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D46" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="E46" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1942,16 +1966,16 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D47" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E47" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1959,16 +1983,16 @@
         <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D48" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E48" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1976,16 +2000,16 @@
         <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D49" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E49" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1993,16 +2017,16 @@
         <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D50" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="E50" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2010,16 +2034,16 @@
         <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E51" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2027,16 +2051,16 @@
         <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D52" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E52" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2044,16 +2068,16 @@
         <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D53" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E53" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2061,13 +2085,13 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E54" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2075,13 +2099,13 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E55" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2089,13 +2113,13 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2103,13 +2127,13 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E57" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2117,13 +2141,13 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E58" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2131,13 +2155,13 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E59" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2145,13 +2169,13 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E60" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2159,16 +2183,16 @@
         <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D61" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="E61" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2176,16 +2200,16 @@
         <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D62" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E62" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2193,16 +2217,16 @@
         <v>15</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D63" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E63" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2210,16 +2234,16 @@
         <v>15</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D64" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E64" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2230,13 +2254,13 @@
         <v>0</v>
       </c>
       <c r="C65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D65" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="E65" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2244,16 +2268,16 @@
         <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="E66" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2264,10 +2288,10 @@
         <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E67" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2278,10 +2302,10 @@
         <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E68" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2292,10 +2316,10 @@
         <v>14</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E69" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2306,10 +2330,10 @@
         <v>14</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E70" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2320,10 +2344,10 @@
         <v>14</v>
       </c>
       <c r="C71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E71" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2334,10 +2358,10 @@
         <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E72" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2348,10 +2372,10 @@
         <v>14</v>
       </c>
       <c r="C73" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E73" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2359,16 +2383,16 @@
         <v>16</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C74" t="s">
         <v>22</v>
       </c>
       <c r="D74" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="E74" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2379,13 +2403,13 @@
         <v>22</v>
       </c>
       <c r="C75" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D75" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E75" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2396,13 +2420,13 @@
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D76" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E76" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2413,10 +2437,10 @@
         <v>22</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E77" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2427,10 +2451,10 @@
         <v>22</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E78" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2441,10 +2465,10 @@
         <v>22</v>
       </c>
       <c r="C79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E79" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2455,10 +2479,10 @@
         <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E80" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2469,13 +2493,13 @@
         <v>22</v>
       </c>
       <c r="C81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D81" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E81" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2486,13 +2510,13 @@
         <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D82" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E82" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2503,13 +2527,13 @@
         <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D83" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E83" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2520,13 +2544,13 @@
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D84" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E84" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2534,16 +2558,16 @@
         <v>16</v>
       </c>
       <c r="B85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C85" t="s">
         <v>7</v>
       </c>
       <c r="D85" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E85" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2554,13 +2578,13 @@
         <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D86" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E86" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2571,13 +2595,13 @@
         <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D87" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E87" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2588,13 +2612,13 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D88" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E88" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2605,13 +2629,13 @@
         <v>7</v>
       </c>
       <c r="C89" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D89" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E89" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2622,13 +2646,13 @@
         <v>7</v>
       </c>
       <c r="C90" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D90" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E90" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2636,16 +2660,16 @@
         <v>16</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C91" t="s">
         <v>9</v>
       </c>
       <c r="D91" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E91" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2656,13 +2680,13 @@
         <v>9</v>
       </c>
       <c r="C92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D92" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E92" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2673,13 +2697,13 @@
         <v>9</v>
       </c>
       <c r="C93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D93" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E93" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2687,13 +2711,13 @@
         <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C94" t="s">
         <v>8</v>
       </c>
       <c r="E94" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2704,13 +2728,13 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D95" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E95" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2721,13 +2745,13 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D96" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E96" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2738,13 +2762,13 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D97" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E97" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2755,13 +2779,13 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D98" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E98" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2769,16 +2793,16 @@
         <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="E99" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2789,13 +2813,13 @@
         <v>11</v>
       </c>
       <c r="C100" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D100" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E100" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2806,13 +2830,13 @@
         <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D101" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E101" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2823,13 +2847,13 @@
         <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D102" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E102" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2840,13 +2864,13 @@
         <v>11</v>
       </c>
       <c r="C103" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D103" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E103" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2854,16 +2878,16 @@
         <v>16</v>
       </c>
       <c r="B104" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C104" t="s">
         <v>12</v>
       </c>
       <c r="D104" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E104" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2874,13 +2898,13 @@
         <v>12</v>
       </c>
       <c r="C105" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D105" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E105" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2891,13 +2915,13 @@
         <v>12</v>
       </c>
       <c r="C106" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D106" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E106" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2905,16 +2929,16 @@
         <v>16</v>
       </c>
       <c r="B107" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E107" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2925,13 +2949,13 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D108" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E108" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2942,13 +2966,13 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D109" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E109" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2959,13 +2983,13 @@
         <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D110" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="E110" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2976,13 +3000,13 @@
         <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E111" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2993,13 +3017,13 @@
         <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D112" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="E112" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3010,13 +3034,13 @@
         <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D113" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E113" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3027,13 +3051,13 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D114" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E114" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3044,13 +3068,13 @@
         <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D115" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E115" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3061,13 +3085,13 @@
         <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D116" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="E116" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3078,13 +3102,13 @@
         <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D117" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E117" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3095,13 +3119,13 @@
         <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D118" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E118" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3112,13 +3136,13 @@
         <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D119" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E119" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3126,16 +3150,16 @@
         <v>16</v>
       </c>
       <c r="B120" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C120" t="s">
         <v>21</v>
       </c>
       <c r="D120" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="E120" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3146,10 +3170,10 @@
         <v>21</v>
       </c>
       <c r="C121" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E121" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3160,13 +3184,13 @@
         <v>21</v>
       </c>
       <c r="C122" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D122" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E122" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3177,13 +3201,13 @@
         <v>21</v>
       </c>
       <c r="C123" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D123" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E123" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3194,13 +3218,13 @@
         <v>21</v>
       </c>
       <c r="C124" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D124" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="E124" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3211,13 +3235,13 @@
         <v>21</v>
       </c>
       <c r="C125" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D125" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E125" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3228,13 +3252,13 @@
         <v>21</v>
       </c>
       <c r="C126" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D126" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="E126" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3245,13 +3269,13 @@
         <v>21</v>
       </c>
       <c r="C127" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D127" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E127" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3262,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="C128" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D128" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E128" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3279,13 +3303,13 @@
         <v>21</v>
       </c>
       <c r="C129" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D129" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E129" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3296,13 +3320,13 @@
         <v>21</v>
       </c>
       <c r="C130" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D130" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="E130" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3313,13 +3337,13 @@
         <v>21</v>
       </c>
       <c r="C131" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E131" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3330,13 +3354,13 @@
         <v>21</v>
       </c>
       <c r="C132" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D132" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E132" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3347,13 +3371,13 @@
         <v>21</v>
       </c>
       <c r="C133" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D133" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E133" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3364,13 +3388,13 @@
         <v>21</v>
       </c>
       <c r="C134" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D134" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E134" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3381,13 +3405,13 @@
         <v>21</v>
       </c>
       <c r="C135" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D135" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E135" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3398,13 +3422,13 @@
         <v>21</v>
       </c>
       <c r="C136" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D136" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E136" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3415,13 +3439,13 @@
         <v>21</v>
       </c>
       <c r="C137" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D137" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E137" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3432,13 +3456,13 @@
         <v>21</v>
       </c>
       <c r="C138" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D138" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E138" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3449,13 +3473,13 @@
         <v>21</v>
       </c>
       <c r="C139" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D139" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E139" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3466,13 +3490,13 @@
         <v>21</v>
       </c>
       <c r="C140" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D140" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E140" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3483,13 +3507,13 @@
         <v>21</v>
       </c>
       <c r="C141" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D141" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E141" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3500,13 +3524,13 @@
         <v>21</v>
       </c>
       <c r="C142" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D142" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E142" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3517,13 +3541,13 @@
         <v>21</v>
       </c>
       <c r="C143" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D143" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E143" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3534,10 +3558,10 @@
         <v>21</v>
       </c>
       <c r="C144" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E144" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3545,16 +3569,16 @@
         <v>16</v>
       </c>
       <c r="B145" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C145" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D145" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E145" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3562,16 +3586,16 @@
         <v>16</v>
       </c>
       <c r="B146" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C146" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D146" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E146" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3579,16 +3603,16 @@
         <v>16</v>
       </c>
       <c r="B147" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C147" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D147" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E147" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3596,16 +3620,16 @@
         <v>16</v>
       </c>
       <c r="B148" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C148" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D148" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E148" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3613,16 +3637,16 @@
         <v>16</v>
       </c>
       <c r="B149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C149" t="s">
         <v>5</v>
       </c>
       <c r="D149" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E149" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3633,10 +3657,10 @@
         <v>5</v>
       </c>
       <c r="C150" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E150" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3647,10 +3671,10 @@
         <v>5</v>
       </c>
       <c r="C151" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E151" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3661,10 +3685,10 @@
         <v>5</v>
       </c>
       <c r="C152" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E152" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3675,13 +3699,13 @@
         <v>5</v>
       </c>
       <c r="C153" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D153" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E153" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3692,10 +3716,10 @@
         <v>5</v>
       </c>
       <c r="C154" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E154" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3706,10 +3730,10 @@
         <v>5</v>
       </c>
       <c r="C155" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E155" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3717,16 +3741,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C156" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D156" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E156" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3734,16 +3758,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C157" t="s">
         <v>15</v>
       </c>
       <c r="D157" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E157" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3754,13 +3778,13 @@
         <v>15</v>
       </c>
       <c r="C158" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D158" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="E158" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3771,13 +3795,13 @@
         <v>15</v>
       </c>
       <c r="C159" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D159" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E159" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3788,13 +3812,13 @@
         <v>15</v>
       </c>
       <c r="C160" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D160" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E160" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3805,13 +3829,13 @@
         <v>15</v>
       </c>
       <c r="C161" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D161" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E161" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3819,16 +3843,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C162" t="s">
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E162" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3839,10 +3863,10 @@
         <v>18</v>
       </c>
       <c r="C163" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E163" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3853,13 +3877,13 @@
         <v>18</v>
       </c>
       <c r="C164" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D164" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E164" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3870,13 +3894,13 @@
         <v>18</v>
       </c>
       <c r="C165" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D165" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="E165" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3887,13 +3911,13 @@
         <v>18</v>
       </c>
       <c r="C166" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D166" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E166" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3901,16 +3925,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C167" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D167" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E167" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3918,16 +3942,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C168" t="s">
         <v>19</v>
       </c>
       <c r="D168" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E168" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3938,13 +3962,13 @@
         <v>19</v>
       </c>
       <c r="C169" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D169" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E169" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3955,13 +3979,13 @@
         <v>19</v>
       </c>
       <c r="C170" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D170" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E170" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3972,13 +3996,13 @@
         <v>19</v>
       </c>
       <c r="C171" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D171" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E171" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3986,16 +4010,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C172" t="s">
         <v>10</v>
       </c>
       <c r="D172" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E172" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4006,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="C173" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D173" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E173" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4023,13 +4047,13 @@
         <v>10</v>
       </c>
       <c r="C174" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D174" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E174" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4040,13 +4064,13 @@
         <v>10</v>
       </c>
       <c r="C175" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D175" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E175" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -4054,16 +4078,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C176" t="s">
         <v>20</v>
       </c>
       <c r="D176" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E176" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -4074,13 +4098,13 @@
         <v>20</v>
       </c>
       <c r="C177" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D177" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E177" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4091,13 +4115,13 @@
         <v>20</v>
       </c>
       <c r="C178" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D178" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E178" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4108,13 +4132,13 @@
         <v>20</v>
       </c>
       <c r="C179" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D179" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E179" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4122,16 +4146,16 @@
         <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C180" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D180" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E180" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4139,16 +4163,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C181" t="s">
         <v>3</v>
       </c>
       <c r="D181" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E181" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4156,16 +4180,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C182" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D182" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E182" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4173,16 +4197,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C183" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D183" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E183" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4190,16 +4214,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C184" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D184" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E184" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4207,16 +4231,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C185" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D185" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="E185" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4224,16 +4248,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C186" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D186" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E186" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -4241,13 +4265,13 @@
         <v>18</v>
       </c>
       <c r="B187" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C187" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E187" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4255,16 +4279,16 @@
         <v>18</v>
       </c>
       <c r="B188" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C188" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D188" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E188" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4272,16 +4296,16 @@
         <v>18</v>
       </c>
       <c r="B189" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C189" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D189" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="E189" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4289,16 +4313,16 @@
         <v>18</v>
       </c>
       <c r="B190" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C190" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D190" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E190" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4306,16 +4330,16 @@
         <v>19</v>
       </c>
       <c r="B191" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C191" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D191" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E191" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4323,16 +4347,16 @@
         <v>19</v>
       </c>
       <c r="B192" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C192" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D192" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E192" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4340,16 +4364,16 @@
         <v>19</v>
       </c>
       <c r="B193" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C193" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D193" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E193" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4357,16 +4381,16 @@
         <v>20</v>
       </c>
       <c r="B194" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C194" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D194" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E194" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4374,16 +4398,16 @@
         <v>20</v>
       </c>
       <c r="B195" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C195" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D195" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E195" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4391,16 +4415,16 @@
         <v>20</v>
       </c>
       <c r="B196" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C196" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D196" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E196" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4408,13 +4432,13 @@
         <v>21</v>
       </c>
       <c r="B197" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C197" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E197" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4422,16 +4446,16 @@
         <v>21</v>
       </c>
       <c r="B198" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C198" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D198" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E198" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4439,16 +4463,16 @@
         <v>21</v>
       </c>
       <c r="B199" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C199" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D199" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E199" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4456,16 +4480,16 @@
         <v>21</v>
       </c>
       <c r="B200" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C200" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D200" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="E200" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4473,16 +4497,16 @@
         <v>21</v>
       </c>
       <c r="B201" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C201" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D201" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E201" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4490,16 +4514,16 @@
         <v>21</v>
       </c>
       <c r="B202" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C202" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D202" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="E202" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4507,16 +4531,16 @@
         <v>21</v>
       </c>
       <c r="B203" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C203" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D203" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E203" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -4524,16 +4548,16 @@
         <v>21</v>
       </c>
       <c r="B204" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C204" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D204" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E204" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4541,16 +4565,16 @@
         <v>21</v>
       </c>
       <c r="B205" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C205" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D205" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E205" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4558,16 +4582,16 @@
         <v>21</v>
       </c>
       <c r="B206" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C206" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D206" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="E206" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4575,16 +4599,16 @@
         <v>21</v>
       </c>
       <c r="B207" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C207" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D207" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E207" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4592,16 +4616,16 @@
         <v>21</v>
       </c>
       <c r="B208" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C208" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D208" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E208" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4609,16 +4633,16 @@
         <v>21</v>
       </c>
       <c r="B209" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C209" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D209" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E209" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4626,16 +4650,16 @@
         <v>21</v>
       </c>
       <c r="B210" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C210" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D210" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E210" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4643,16 +4667,16 @@
         <v>21</v>
       </c>
       <c r="B211" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C211" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D211" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E211" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4660,16 +4684,16 @@
         <v>21</v>
       </c>
       <c r="B212" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C212" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D212" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E212" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4677,16 +4701,16 @@
         <v>21</v>
       </c>
       <c r="B213" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C213" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D213" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E213" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4694,16 +4718,16 @@
         <v>21</v>
       </c>
       <c r="B214" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C214" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D214" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E214" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4711,16 +4735,16 @@
         <v>21</v>
       </c>
       <c r="B215" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C215" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D215" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E215" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4728,16 +4752,16 @@
         <v>21</v>
       </c>
       <c r="B216" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C216" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D216" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E216" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4745,16 +4769,16 @@
         <v>21</v>
       </c>
       <c r="B217" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C217" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D217" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E217" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4762,16 +4786,16 @@
         <v>21</v>
       </c>
       <c r="B218" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C218" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D218" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E218" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4779,16 +4803,16 @@
         <v>21</v>
       </c>
       <c r="B219" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C219" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D219" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E219" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4796,13 +4820,13 @@
         <v>21</v>
       </c>
       <c r="B220" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C220" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E220" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4810,16 +4834,16 @@
         <v>22</v>
       </c>
       <c r="B221" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C221" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D221" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E221" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4827,16 +4851,16 @@
         <v>22</v>
       </c>
       <c r="B222" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C222" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D222" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E222" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4844,13 +4868,13 @@
         <v>22</v>
       </c>
       <c r="B223" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C223" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E223" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4858,13 +4882,13 @@
         <v>22</v>
       </c>
       <c r="B224" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C224" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E224" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4872,13 +4896,13 @@
         <v>22</v>
       </c>
       <c r="B225" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C225" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E225" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4886,13 +4910,13 @@
         <v>22</v>
       </c>
       <c r="B226" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C226" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E226" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4900,16 +4924,16 @@
         <v>22</v>
       </c>
       <c r="B227" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C227" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D227" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E227" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4917,16 +4941,16 @@
         <v>22</v>
       </c>
       <c r="B228" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C228" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D228" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E228" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4934,16 +4958,16 @@
         <v>22</v>
       </c>
       <c r="B229" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C229" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D229" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E229" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4951,16 +4975,16 @@
         <v>22</v>
       </c>
       <c r="B230" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C230" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D230" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E230" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4968,16 +4992,13 @@
         <v>23</v>
       </c>
       <c r="B231" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C231" t="s">
-        <v>127</v>
-      </c>
-      <c r="D231" t="s">
-        <v>237</v>
+        <v>3</v>
       </c>
       <c r="E231" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4985,16 +5006,13 @@
         <v>23</v>
       </c>
       <c r="B232" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C232" t="s">
-        <v>128</v>
-      </c>
-      <c r="D232" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="E232" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -5002,16 +5020,13 @@
         <v>23</v>
       </c>
       <c r="B233" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C233" t="s">
-        <v>129</v>
-      </c>
-      <c r="D233" t="s">
-        <v>239</v>
+        <v>150</v>
       </c>
       <c r="E233" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -5019,16 +5034,13 @@
         <v>23</v>
       </c>
       <c r="B234" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C234" t="s">
-        <v>5</v>
-      </c>
-      <c r="D234" t="s">
-        <v>240</v>
+        <v>151</v>
       </c>
       <c r="E234" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -5036,13 +5048,13 @@
         <v>23</v>
       </c>
       <c r="B235" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C235" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="E235" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -5050,13 +5062,13 @@
         <v>23</v>
       </c>
       <c r="B236" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C236" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E236" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -5064,13 +5076,13 @@
         <v>23</v>
       </c>
       <c r="B237" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C237" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E237" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -5078,16 +5090,13 @@
         <v>23</v>
       </c>
       <c r="B238" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C238" t="s">
-        <v>32</v>
-      </c>
-      <c r="D238" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E238" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -5095,13 +5104,13 @@
         <v>23</v>
       </c>
       <c r="B239" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C239" t="s">
-        <v>33</v>
+        <v>154</v>
       </c>
       <c r="E239" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -5109,30 +5118,185 @@
         <v>23</v>
       </c>
       <c r="B240" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C240" t="s">
-        <v>34</v>
+        <v>155</v>
       </c>
       <c r="E240" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B241" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C241" t="s">
+        <v>128</v>
+      </c>
+      <c r="D241" t="s">
+        <v>245</v>
+      </c>
+      <c r="E241" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" t="s">
+        <v>24</v>
+      </c>
+      <c r="B242" t="s">
+        <v>27</v>
+      </c>
+      <c r="C242" t="s">
+        <v>129</v>
+      </c>
+      <c r="D242" t="s">
+        <v>246</v>
+      </c>
+      <c r="E242" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" t="s">
+        <v>24</v>
+      </c>
+      <c r="B243" t="s">
+        <v>27</v>
+      </c>
+      <c r="C243" t="s">
         <v>130</v>
       </c>
-      <c r="D241" t="s">
-        <v>241</v>
-      </c>
-      <c r="E241" t="s">
-        <v>264</v>
+      <c r="D243" t="s">
+        <v>247</v>
+      </c>
+      <c r="E243" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" t="s">
+        <v>24</v>
+      </c>
+      <c r="B244" t="s">
+        <v>27</v>
+      </c>
+      <c r="C244" t="s">
+        <v>5</v>
+      </c>
+      <c r="D244" t="s">
+        <v>248</v>
+      </c>
+      <c r="E244" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="s">
+        <v>24</v>
+      </c>
+      <c r="B245" t="s">
+        <v>5</v>
+      </c>
+      <c r="C245" t="s">
+        <v>30</v>
+      </c>
+      <c r="E245" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" t="s">
+        <v>24</v>
+      </c>
+      <c r="B246" t="s">
+        <v>5</v>
+      </c>
+      <c r="C246" t="s">
+        <v>31</v>
+      </c>
+      <c r="E246" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" t="s">
+        <v>24</v>
+      </c>
+      <c r="B247" t="s">
+        <v>5</v>
+      </c>
+      <c r="C247" t="s">
+        <v>32</v>
+      </c>
+      <c r="E247" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" t="s">
+        <v>24</v>
+      </c>
+      <c r="B248" t="s">
+        <v>5</v>
+      </c>
+      <c r="C248" t="s">
+        <v>33</v>
+      </c>
+      <c r="D248" t="s">
+        <v>156</v>
+      </c>
+      <c r="E248" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" t="s">
+        <v>24</v>
+      </c>
+      <c r="B249" t="s">
+        <v>5</v>
+      </c>
+      <c r="C249" t="s">
+        <v>34</v>
+      </c>
+      <c r="E249" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" t="s">
+        <v>24</v>
+      </c>
+      <c r="B250" t="s">
+        <v>5</v>
+      </c>
+      <c r="C250" t="s">
+        <v>35</v>
+      </c>
+      <c r="E250" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" t="s">
+        <v>24</v>
+      </c>
+      <c r="B251" t="s">
+        <v>27</v>
+      </c>
+      <c r="C251" t="s">
+        <v>131</v>
+      </c>
+      <c r="D251" t="s">
+        <v>249</v>
+      </c>
+      <c r="E251" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/Streamlit/Data/knowledge_base.xlsx
+++ b/Streamlit/Data/knowledge_base.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3965" uniqueCount="1502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="1502">
   <si>
     <t>Process</t>
   </si>
@@ -4974,7 +4974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1033"/>
+  <dimension ref="A1:D1032"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10864,10 +10864,10 @@
         <v>13</v>
       </c>
       <c r="B431" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C431" t="s">
-        <v>77</v>
+        <v>458</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -10878,7 +10878,7 @@
         <v>67</v>
       </c>
       <c r="C432" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -10889,7 +10889,7 @@
         <v>67</v>
       </c>
       <c r="C433" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -10900,7 +10900,7 @@
         <v>67</v>
       </c>
       <c r="C434" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -10911,7 +10911,7 @@
         <v>67</v>
       </c>
       <c r="C435" t="s">
-        <v>461</v>
+        <v>365</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -10922,7 +10922,7 @@
         <v>67</v>
       </c>
       <c r="C436" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -10933,7 +10933,7 @@
         <v>67</v>
       </c>
       <c r="C437" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -10944,7 +10944,7 @@
         <v>67</v>
       </c>
       <c r="C438" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -10955,7 +10955,10 @@
         <v>67</v>
       </c>
       <c r="C439" t="s">
-        <v>464</v>
+        <v>451</v>
+      </c>
+      <c r="D439" t="s">
+        <v>1169</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -10966,10 +10969,7 @@
         <v>67</v>
       </c>
       <c r="C440" t="s">
-        <v>451</v>
-      </c>
-      <c r="D440" t="s">
-        <v>1169</v>
+        <v>465</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -10980,7 +10980,7 @@
         <v>67</v>
       </c>
       <c r="C441" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -10991,7 +10991,7 @@
         <v>67</v>
       </c>
       <c r="C442" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -11002,7 +11002,7 @@
         <v>67</v>
       </c>
       <c r="C443" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -11013,7 +11013,10 @@
         <v>67</v>
       </c>
       <c r="C444" t="s">
-        <v>468</v>
+        <v>478</v>
+      </c>
+      <c r="D444" t="s">
+        <v>1170</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -11024,10 +11027,10 @@
         <v>67</v>
       </c>
       <c r="C445" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D445" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -11038,10 +11041,7 @@
         <v>67</v>
       </c>
       <c r="C446" t="s">
-        <v>479</v>
-      </c>
-      <c r="D446" t="s">
-        <v>1173</v>
+        <v>469</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -11052,7 +11052,10 @@
         <v>67</v>
       </c>
       <c r="C447" t="s">
-        <v>469</v>
+        <v>449</v>
+      </c>
+      <c r="D447" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -11063,10 +11066,7 @@
         <v>67</v>
       </c>
       <c r="C448" t="s">
-        <v>449</v>
-      </c>
-      <c r="D448" t="s">
-        <v>1167</v>
+        <v>470</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -11077,7 +11077,7 @@
         <v>67</v>
       </c>
       <c r="C449" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -11088,7 +11088,10 @@
         <v>67</v>
       </c>
       <c r="C450" t="s">
-        <v>471</v>
+        <v>457</v>
+      </c>
+      <c r="D450" t="s">
+        <v>1178</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -11099,10 +11102,7 @@
         <v>67</v>
       </c>
       <c r="C451" t="s">
-        <v>457</v>
-      </c>
-      <c r="D451" t="s">
-        <v>1178</v>
+        <v>472</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -11113,7 +11113,10 @@
         <v>67</v>
       </c>
       <c r="C452" t="s">
-        <v>472</v>
+        <v>480</v>
+      </c>
+      <c r="D452" t="s">
+        <v>1172</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -11124,10 +11127,10 @@
         <v>67</v>
       </c>
       <c r="C453" t="s">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="D453" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -11138,10 +11141,7 @@
         <v>67</v>
       </c>
       <c r="C454" t="s">
-        <v>448</v>
-      </c>
-      <c r="D454" t="s">
-        <v>1166</v>
+        <v>473</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -11152,7 +11152,7 @@
         <v>67</v>
       </c>
       <c r="C455" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -11163,7 +11163,10 @@
         <v>67</v>
       </c>
       <c r="C456" t="s">
-        <v>474</v>
+        <v>481</v>
+      </c>
+      <c r="D456" t="s">
+        <v>1179</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -11174,10 +11177,10 @@
         <v>67</v>
       </c>
       <c r="C457" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D457" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -11188,10 +11191,7 @@
         <v>67</v>
       </c>
       <c r="C458" t="s">
-        <v>482</v>
-      </c>
-      <c r="D458" t="s">
-        <v>1174</v>
+        <v>475</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -11202,7 +11202,7 @@
         <v>67</v>
       </c>
       <c r="C459" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -11213,7 +11213,7 @@
         <v>67</v>
       </c>
       <c r="C460" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -11224,21 +11224,24 @@
         <v>67</v>
       </c>
       <c r="C461" t="s">
-        <v>477</v>
+        <v>450</v>
+      </c>
+      <c r="D461" t="s">
+        <v>1168</v>
       </c>
     </row>
     <row r="462" spans="1:4">
       <c r="A462" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B462" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C462" t="s">
-        <v>450</v>
+        <v>71</v>
       </c>
       <c r="D462" t="s">
-        <v>1168</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -11246,13 +11249,13 @@
         <v>14</v>
       </c>
       <c r="B463" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C463" t="s">
-        <v>71</v>
+        <v>483</v>
       </c>
       <c r="D463" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -11263,10 +11266,10 @@
         <v>65</v>
       </c>
       <c r="C464" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D464" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -11274,13 +11277,10 @@
         <v>14</v>
       </c>
       <c r="B465" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C465" t="s">
-        <v>484</v>
-      </c>
-      <c r="D465" t="s">
-        <v>1182</v>
+        <v>485</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -11291,7 +11291,7 @@
         <v>69</v>
       </c>
       <c r="C466" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -11302,7 +11302,7 @@
         <v>69</v>
       </c>
       <c r="C467" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -11313,7 +11313,7 @@
         <v>69</v>
       </c>
       <c r="C468" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -11324,7 +11324,10 @@
         <v>69</v>
       </c>
       <c r="C469" t="s">
-        <v>488</v>
+        <v>489</v>
+      </c>
+      <c r="D469" t="s">
+        <v>1183</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -11335,10 +11338,10 @@
         <v>69</v>
       </c>
       <c r="C470" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D470" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -11349,10 +11352,10 @@
         <v>69</v>
       </c>
       <c r="C471" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D471" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -11363,10 +11366,10 @@
         <v>69</v>
       </c>
       <c r="C472" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D472" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -11377,10 +11380,10 @@
         <v>69</v>
       </c>
       <c r="C473" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D473" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -11391,24 +11394,24 @@
         <v>69</v>
       </c>
       <c r="C474" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D474" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="475" spans="1:4">
       <c r="A475" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B475" t="s">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C475" t="s">
-        <v>494</v>
+        <v>404</v>
       </c>
       <c r="D475" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -11416,13 +11419,13 @@
         <v>15</v>
       </c>
       <c r="B476" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C476" t="s">
-        <v>404</v>
+        <v>495</v>
       </c>
       <c r="D476" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -11433,10 +11436,10 @@
         <v>68</v>
       </c>
       <c r="C477" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D477" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -11447,10 +11450,10 @@
         <v>68</v>
       </c>
       <c r="C478" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D478" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -11461,10 +11464,10 @@
         <v>68</v>
       </c>
       <c r="C479" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D479" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -11475,10 +11478,10 @@
         <v>68</v>
       </c>
       <c r="C480" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D480" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -11489,10 +11492,10 @@
         <v>68</v>
       </c>
       <c r="C481" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D481" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -11503,24 +11506,21 @@
         <v>68</v>
       </c>
       <c r="C482" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D482" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="483" spans="1:4">
       <c r="A483" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B483" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C483" t="s">
-        <v>501</v>
-      </c>
-      <c r="D483" t="s">
-        <v>1196</v>
+        <v>404</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -11528,10 +11528,13 @@
         <v>16</v>
       </c>
       <c r="B484" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C484" t="s">
-        <v>404</v>
+        <v>502</v>
+      </c>
+      <c r="D484" t="s">
+        <v>1197</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -11542,10 +11545,10 @@
         <v>68</v>
       </c>
       <c r="C485" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D485" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -11556,10 +11559,10 @@
         <v>68</v>
       </c>
       <c r="C486" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D486" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -11570,24 +11573,24 @@
         <v>68</v>
       </c>
       <c r="C487" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D487" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B488" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C488" t="s">
-        <v>505</v>
+        <v>404</v>
       </c>
       <c r="D488" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -11595,13 +11598,13 @@
         <v>17</v>
       </c>
       <c r="B489" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C489" t="s">
-        <v>404</v>
+        <v>506</v>
       </c>
       <c r="D489" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -11612,24 +11615,24 @@
         <v>68</v>
       </c>
       <c r="C490" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D490" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="491" spans="1:4">
       <c r="A491" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B491" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C491" t="s">
-        <v>507</v>
+        <v>404</v>
       </c>
       <c r="D491" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -11637,13 +11640,13 @@
         <v>18</v>
       </c>
       <c r="B492" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C492" t="s">
-        <v>404</v>
+        <v>508</v>
       </c>
       <c r="D492" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -11654,10 +11657,7 @@
         <v>68</v>
       </c>
       <c r="C493" t="s">
-        <v>508</v>
-      </c>
-      <c r="D493" t="s">
-        <v>1205</v>
+        <v>509</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -11668,7 +11668,10 @@
         <v>68</v>
       </c>
       <c r="C494" t="s">
-        <v>509</v>
+        <v>510</v>
+      </c>
+      <c r="D494" t="s">
+        <v>1206</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -11679,10 +11682,10 @@
         <v>68</v>
       </c>
       <c r="C495" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D495" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -11693,10 +11696,10 @@
         <v>68</v>
       </c>
       <c r="C496" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D496" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -11707,10 +11710,10 @@
         <v>68</v>
       </c>
       <c r="C497" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D497" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -11721,10 +11724,10 @@
         <v>68</v>
       </c>
       <c r="C498" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D498" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -11735,10 +11738,10 @@
         <v>68</v>
       </c>
       <c r="C499" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D499" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -11749,24 +11752,24 @@
         <v>68</v>
       </c>
       <c r="C500" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D500" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B501" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C501" t="s">
-        <v>516</v>
+        <v>404</v>
       </c>
       <c r="D501" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -11774,13 +11777,13 @@
         <v>19</v>
       </c>
       <c r="B502" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C502" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="D502" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -11791,10 +11794,10 @@
         <v>68</v>
       </c>
       <c r="C503" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D503" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -11805,24 +11808,21 @@
         <v>68</v>
       </c>
       <c r="C504" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D504" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="505" spans="1:4">
       <c r="A505" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B505" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C505" t="s">
-        <v>519</v>
-      </c>
-      <c r="D505" t="s">
-        <v>1216</v>
+        <v>404</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -11830,10 +11830,13 @@
         <v>20</v>
       </c>
       <c r="B506" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C506" t="s">
-        <v>404</v>
+        <v>46</v>
+      </c>
+      <c r="D506" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -11841,13 +11844,13 @@
         <v>20</v>
       </c>
       <c r="B507" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C507" t="s">
-        <v>46</v>
+        <v>520</v>
       </c>
       <c r="D507" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -11858,10 +11861,10 @@
         <v>46</v>
       </c>
       <c r="C508" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D508" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -11872,10 +11875,7 @@
         <v>46</v>
       </c>
       <c r="C509" t="s">
-        <v>521</v>
-      </c>
-      <c r="D509" t="s">
-        <v>1219</v>
+        <v>522</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -11886,7 +11886,7 @@
         <v>46</v>
       </c>
       <c r="C510" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -11897,7 +11897,7 @@
         <v>46</v>
       </c>
       <c r="C511" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -11908,7 +11908,7 @@
         <v>46</v>
       </c>
       <c r="C512" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -11919,7 +11919,10 @@
         <v>46</v>
       </c>
       <c r="C513" t="s">
-        <v>525</v>
+        <v>25</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1220</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -11930,10 +11933,10 @@
         <v>46</v>
       </c>
       <c r="C514" t="s">
-        <v>25</v>
+        <v>526</v>
       </c>
       <c r="D514" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -11944,10 +11947,10 @@
         <v>46</v>
       </c>
       <c r="C515" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D515" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -11958,10 +11961,10 @@
         <v>46</v>
       </c>
       <c r="C516" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D516" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -11969,13 +11972,13 @@
         <v>20</v>
       </c>
       <c r="B517" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C517" t="s">
-        <v>528</v>
+        <v>29</v>
       </c>
       <c r="D517" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -11983,13 +11986,10 @@
         <v>20</v>
       </c>
       <c r="B518" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C518" t="s">
-        <v>29</v>
-      </c>
-      <c r="D518" t="s">
-        <v>1224</v>
+        <v>529</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -12000,7 +12000,7 @@
         <v>29</v>
       </c>
       <c r="C519" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -12011,7 +12011,7 @@
         <v>29</v>
       </c>
       <c r="C520" t="s">
-        <v>530</v>
+        <v>28</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -12022,7 +12022,7 @@
         <v>29</v>
       </c>
       <c r="C521" t="s">
-        <v>28</v>
+        <v>531</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -12033,7 +12033,7 @@
         <v>29</v>
       </c>
       <c r="C522" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -12044,7 +12044,7 @@
         <v>29</v>
       </c>
       <c r="C523" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -12055,7 +12055,7 @@
         <v>29</v>
       </c>
       <c r="C524" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -12063,10 +12063,13 @@
         <v>20</v>
       </c>
       <c r="B525" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="C525" t="s">
-        <v>534</v>
+        <v>535</v>
+      </c>
+      <c r="D525" t="s">
+        <v>1225</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -12077,10 +12080,10 @@
         <v>68</v>
       </c>
       <c r="C526" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D526" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -12091,10 +12094,10 @@
         <v>68</v>
       </c>
       <c r="C527" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D527" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -12105,10 +12108,10 @@
         <v>68</v>
       </c>
       <c r="C528" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D528" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -12119,10 +12122,7 @@
         <v>68</v>
       </c>
       <c r="C529" t="s">
-        <v>538</v>
-      </c>
-      <c r="D529" t="s">
-        <v>1228</v>
+        <v>539</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -12133,7 +12133,10 @@
         <v>68</v>
       </c>
       <c r="C530" t="s">
-        <v>539</v>
+        <v>540</v>
+      </c>
+      <c r="D530" t="s">
+        <v>1229</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -12141,13 +12144,13 @@
         <v>20</v>
       </c>
       <c r="B531" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C531" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D531" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -12155,13 +12158,13 @@
         <v>20</v>
       </c>
       <c r="B532" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C532" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D532" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -12172,10 +12175,10 @@
         <v>68</v>
       </c>
       <c r="C533" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D533" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -12186,10 +12189,10 @@
         <v>68</v>
       </c>
       <c r="C534" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D534" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -12200,10 +12203,10 @@
         <v>68</v>
       </c>
       <c r="C535" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D535" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -12214,24 +12217,24 @@
         <v>68</v>
       </c>
       <c r="C536" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D536" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B537" t="s">
         <v>68</v>
       </c>
       <c r="C537" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D537" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -12239,13 +12242,13 @@
         <v>21</v>
       </c>
       <c r="B538" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C538" t="s">
-        <v>547</v>
+        <v>404</v>
       </c>
       <c r="D538" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -12253,13 +12256,13 @@
         <v>21</v>
       </c>
       <c r="B539" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C539" t="s">
-        <v>404</v>
+        <v>548</v>
       </c>
       <c r="D539" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -12270,10 +12273,10 @@
         <v>68</v>
       </c>
       <c r="C540" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D540" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -12284,10 +12287,10 @@
         <v>68</v>
       </c>
       <c r="C541" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D541" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -12298,10 +12301,10 @@
         <v>68</v>
       </c>
       <c r="C542" t="s">
-        <v>550</v>
+        <v>53</v>
       </c>
       <c r="D542" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -12309,13 +12312,13 @@
         <v>21</v>
       </c>
       <c r="B543" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C543" t="s">
-        <v>53</v>
+        <v>551</v>
       </c>
       <c r="D543" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -12326,10 +12329,10 @@
         <v>53</v>
       </c>
       <c r="C544" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D544" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -12340,10 +12343,10 @@
         <v>53</v>
       </c>
       <c r="C545" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D545" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -12354,10 +12357,10 @@
         <v>53</v>
       </c>
       <c r="C546" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D546" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -12368,10 +12371,10 @@
         <v>53</v>
       </c>
       <c r="C547" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D547" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -12382,24 +12385,24 @@
         <v>53</v>
       </c>
       <c r="C548" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D548" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B549" t="s">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C549" t="s">
-        <v>556</v>
+        <v>404</v>
       </c>
       <c r="D549" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -12407,13 +12410,13 @@
         <v>22</v>
       </c>
       <c r="B550" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C550" t="s">
-        <v>404</v>
+        <v>547</v>
       </c>
       <c r="D550" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -12424,10 +12427,10 @@
         <v>68</v>
       </c>
       <c r="C551" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="D551" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -12438,10 +12441,10 @@
         <v>68</v>
       </c>
       <c r="C552" t="s">
-        <v>557</v>
+        <v>23</v>
       </c>
       <c r="D552" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -12449,13 +12452,13 @@
         <v>22</v>
       </c>
       <c r="B553" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C553" t="s">
-        <v>23</v>
+        <v>558</v>
       </c>
       <c r="D553" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -12466,10 +12469,10 @@
         <v>23</v>
       </c>
       <c r="C554" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D554" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -12480,10 +12483,10 @@
         <v>23</v>
       </c>
       <c r="C555" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D555" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -12494,10 +12497,10 @@
         <v>23</v>
       </c>
       <c r="C556" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D556" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -12508,24 +12511,24 @@
         <v>23</v>
       </c>
       <c r="C557" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D557" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="558" spans="1:4">
       <c r="A558" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B558" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C558" t="s">
-        <v>562</v>
+        <v>404</v>
       </c>
       <c r="D558" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -12533,13 +12536,13 @@
         <v>23</v>
       </c>
       <c r="B559" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C559" t="s">
-        <v>404</v>
+        <v>558</v>
       </c>
       <c r="D559" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -12550,10 +12553,10 @@
         <v>68</v>
       </c>
       <c r="C560" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D560" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -12564,10 +12567,10 @@
         <v>68</v>
       </c>
       <c r="C561" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D561" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -12578,10 +12581,10 @@
         <v>68</v>
       </c>
       <c r="C562" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D562" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -12592,24 +12595,24 @@
         <v>68</v>
       </c>
       <c r="C563" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D563" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B564" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C564" t="s">
-        <v>562</v>
+        <v>404</v>
       </c>
       <c r="D564" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -12617,13 +12620,13 @@
         <v>24</v>
       </c>
       <c r="B565" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C565" t="s">
-        <v>404</v>
+        <v>563</v>
       </c>
       <c r="D565" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -12634,10 +12637,10 @@
         <v>68</v>
       </c>
       <c r="C566" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D566" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -12648,10 +12651,10 @@
         <v>68</v>
       </c>
       <c r="C567" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D567" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -12662,10 +12665,10 @@
         <v>68</v>
       </c>
       <c r="C568" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D568" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -12676,10 +12679,10 @@
         <v>68</v>
       </c>
       <c r="C569" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D569" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -12690,10 +12693,10 @@
         <v>68</v>
       </c>
       <c r="C570" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D570" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -12704,10 +12707,10 @@
         <v>68</v>
       </c>
       <c r="C571" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D571" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -12718,10 +12721,10 @@
         <v>68</v>
       </c>
       <c r="C572" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D572" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -12732,10 +12735,10 @@
         <v>68</v>
       </c>
       <c r="C573" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D573" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -12746,10 +12749,10 @@
         <v>68</v>
       </c>
       <c r="C574" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D574" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -12760,10 +12763,10 @@
         <v>68</v>
       </c>
       <c r="C575" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D575" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -12774,24 +12777,24 @@
         <v>68</v>
       </c>
       <c r="C576" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D576" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B577" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C577" t="s">
-        <v>574</v>
+        <v>404</v>
       </c>
       <c r="D577" t="s">
-        <v>1269</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -12799,13 +12802,13 @@
         <v>25</v>
       </c>
       <c r="B578" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C578" t="s">
-        <v>404</v>
+        <v>575</v>
       </c>
       <c r="D578" t="s">
-        <v>1220</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -12816,10 +12819,10 @@
         <v>68</v>
       </c>
       <c r="C579" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D579" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -12830,24 +12833,21 @@
         <v>68</v>
       </c>
       <c r="C580" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D580" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B581" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C581" t="s">
-        <v>577</v>
-      </c>
-      <c r="D581" t="s">
-        <v>1272</v>
+        <v>77</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -12855,10 +12855,10 @@
         <v>26</v>
       </c>
       <c r="B582" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C582" t="s">
-        <v>77</v>
+        <v>578</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -12869,7 +12869,7 @@
         <v>67</v>
       </c>
       <c r="C583" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -12880,7 +12880,7 @@
         <v>67</v>
       </c>
       <c r="C584" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -12891,7 +12891,10 @@
         <v>67</v>
       </c>
       <c r="C585" t="s">
-        <v>580</v>
+        <v>5</v>
+      </c>
+      <c r="D585" t="s">
+        <v>1273</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -12902,10 +12905,7 @@
         <v>67</v>
       </c>
       <c r="C586" t="s">
-        <v>5</v>
-      </c>
-      <c r="D586" t="s">
-        <v>1273</v>
+        <v>581</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -12916,7 +12916,10 @@
         <v>67</v>
       </c>
       <c r="C587" t="s">
-        <v>581</v>
+        <v>34</v>
+      </c>
+      <c r="D587" t="s">
+        <v>1274</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -12927,10 +12930,7 @@
         <v>67</v>
       </c>
       <c r="C588" t="s">
-        <v>34</v>
-      </c>
-      <c r="D588" t="s">
-        <v>1274</v>
+        <v>582</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -12941,21 +12941,21 @@
         <v>67</v>
       </c>
       <c r="C589" t="s">
-        <v>582</v>
+        <v>583</v>
+      </c>
+      <c r="D589" t="s">
+        <v>1275</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B590" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C590" t="s">
-        <v>583</v>
-      </c>
-      <c r="D590" t="s">
-        <v>1275</v>
+        <v>77</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -12963,10 +12963,13 @@
         <v>27</v>
       </c>
       <c r="B591" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C591" t="s">
-        <v>77</v>
+        <v>3</v>
+      </c>
+      <c r="D591" t="s">
+        <v>1276</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -12977,10 +12980,10 @@
         <v>67</v>
       </c>
       <c r="C592" t="s">
-        <v>3</v>
+        <v>584</v>
       </c>
       <c r="D592" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -12991,10 +12994,10 @@
         <v>67</v>
       </c>
       <c r="C593" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D593" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -13005,10 +13008,10 @@
         <v>67</v>
       </c>
       <c r="C594" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D594" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -13019,24 +13022,21 @@
         <v>67</v>
       </c>
       <c r="C595" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D595" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="596" spans="1:4">
       <c r="A596" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B596" t="s">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="C596" t="s">
-        <v>587</v>
-      </c>
-      <c r="D596" t="s">
-        <v>1280</v>
+        <v>404</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -13044,10 +13044,13 @@
         <v>28</v>
       </c>
       <c r="B597" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C597" t="s">
-        <v>404</v>
+        <v>588</v>
+      </c>
+      <c r="D597" t="s">
+        <v>1281</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -13058,10 +13061,10 @@
         <v>68</v>
       </c>
       <c r="C598" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D598" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -13072,10 +13075,10 @@
         <v>68</v>
       </c>
       <c r="C599" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D599" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -13086,10 +13089,10 @@
         <v>68</v>
       </c>
       <c r="C600" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D600" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -13100,24 +13103,24 @@
         <v>68</v>
       </c>
       <c r="C601" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D601" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="602" spans="1:4">
       <c r="A602" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B602" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C602" t="s">
-        <v>592</v>
+        <v>404</v>
       </c>
       <c r="D602" t="s">
-        <v>1285</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -13125,13 +13128,10 @@
         <v>29</v>
       </c>
       <c r="B603" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C603" t="s">
-        <v>404</v>
-      </c>
-      <c r="D603" t="s">
-        <v>1224</v>
+        <v>529</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -13142,7 +13142,7 @@
         <v>68</v>
       </c>
       <c r="C604" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -13153,7 +13153,7 @@
         <v>68</v>
       </c>
       <c r="C605" t="s">
-        <v>530</v>
+        <v>28</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -13161,10 +13161,13 @@
         <v>29</v>
       </c>
       <c r="B606" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="C606" t="s">
-        <v>28</v>
+        <v>588</v>
+      </c>
+      <c r="D606" t="s">
+        <v>1281</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -13175,10 +13178,10 @@
         <v>28</v>
       </c>
       <c r="C607" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D607" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -13189,10 +13192,10 @@
         <v>28</v>
       </c>
       <c r="C608" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D608" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -13203,10 +13206,10 @@
         <v>28</v>
       </c>
       <c r="C609" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D609" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -13217,10 +13220,10 @@
         <v>28</v>
       </c>
       <c r="C610" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D610" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -13228,13 +13231,10 @@
         <v>29</v>
       </c>
       <c r="B611" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="C611" t="s">
-        <v>592</v>
-      </c>
-      <c r="D611" t="s">
-        <v>1285</v>
+        <v>531</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -13245,7 +13245,7 @@
         <v>68</v>
       </c>
       <c r="C612" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -13256,7 +13256,7 @@
         <v>68</v>
       </c>
       <c r="C613" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -13267,18 +13267,21 @@
         <v>68</v>
       </c>
       <c r="C614" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="615" spans="1:4">
       <c r="A615" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B615" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C615" t="s">
-        <v>534</v>
+        <v>404</v>
+      </c>
+      <c r="D615" t="s">
+        <v>1286</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -13286,13 +13289,13 @@
         <v>30</v>
       </c>
       <c r="B616" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C616" t="s">
-        <v>404</v>
+        <v>593</v>
       </c>
       <c r="D616" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -13303,10 +13306,10 @@
         <v>68</v>
       </c>
       <c r="C617" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D617" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -13317,10 +13320,10 @@
         <v>68</v>
       </c>
       <c r="C618" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D618" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -13331,24 +13334,21 @@
         <v>68</v>
       </c>
       <c r="C619" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D619" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="620" spans="1:4">
       <c r="A620" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B620" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C620" t="s">
-        <v>596</v>
-      </c>
-      <c r="D620" t="s">
-        <v>1290</v>
+        <v>77</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -13356,10 +13356,13 @@
         <v>31</v>
       </c>
       <c r="B621" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C621" t="s">
-        <v>77</v>
+        <v>597</v>
+      </c>
+      <c r="D621" t="s">
+        <v>1291</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -13370,10 +13373,10 @@
         <v>67</v>
       </c>
       <c r="C622" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D622" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -13384,10 +13387,10 @@
         <v>67</v>
       </c>
       <c r="C623" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D623" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -13398,10 +13401,10 @@
         <v>67</v>
       </c>
       <c r="C624" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D624" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -13412,10 +13415,10 @@
         <v>67</v>
       </c>
       <c r="C625" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D625" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -13426,10 +13429,10 @@
         <v>67</v>
       </c>
       <c r="C626" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D626" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -13440,10 +13443,10 @@
         <v>67</v>
       </c>
       <c r="C627" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D627" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -13454,10 +13457,10 @@
         <v>67</v>
       </c>
       <c r="C628" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D628" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -13468,10 +13471,10 @@
         <v>67</v>
       </c>
       <c r="C629" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D629" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -13482,10 +13485,10 @@
         <v>67</v>
       </c>
       <c r="C630" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D630" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -13496,10 +13499,10 @@
         <v>67</v>
       </c>
       <c r="C631" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D631" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -13510,10 +13513,10 @@
         <v>67</v>
       </c>
       <c r="C632" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D632" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -13524,10 +13527,10 @@
         <v>67</v>
       </c>
       <c r="C633" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D633" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -13538,10 +13541,10 @@
         <v>67</v>
       </c>
       <c r="C634" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D634" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -13552,24 +13555,21 @@
         <v>67</v>
       </c>
       <c r="C635" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D635" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="636" spans="1:4">
       <c r="A636" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B636" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C636" t="s">
-        <v>611</v>
-      </c>
-      <c r="D636" t="s">
-        <v>1305</v>
+        <v>77</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -13577,10 +13577,13 @@
         <v>32</v>
       </c>
       <c r="B637" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C637" t="s">
-        <v>77</v>
+        <v>612</v>
+      </c>
+      <c r="D637" t="s">
+        <v>1306</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -13591,10 +13594,10 @@
         <v>67</v>
       </c>
       <c r="C638" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D638" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -13605,10 +13608,10 @@
         <v>67</v>
       </c>
       <c r="C639" t="s">
-        <v>613</v>
+        <v>11</v>
       </c>
       <c r="D639" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -13619,10 +13622,10 @@
         <v>67</v>
       </c>
       <c r="C640" t="s">
-        <v>11</v>
+        <v>614</v>
       </c>
       <c r="D640" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -13633,10 +13636,10 @@
         <v>67</v>
       </c>
       <c r="C641" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D641" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -13647,10 +13650,10 @@
         <v>67</v>
       </c>
       <c r="C642" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D642" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -13661,10 +13664,10 @@
         <v>67</v>
       </c>
       <c r="C643" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D643" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -13675,10 +13678,10 @@
         <v>67</v>
       </c>
       <c r="C644" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D644" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -13689,10 +13692,7 @@
         <v>67</v>
       </c>
       <c r="C645" t="s">
-        <v>618</v>
-      </c>
-      <c r="D645" t="s">
-        <v>1313</v>
+        <v>619</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -13703,7 +13703,7 @@
         <v>67</v>
       </c>
       <c r="C646" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="647" spans="1:4">
@@ -13714,7 +13714,10 @@
         <v>67</v>
       </c>
       <c r="C647" t="s">
-        <v>620</v>
+        <v>621</v>
+      </c>
+      <c r="D647" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -13725,10 +13728,10 @@
         <v>67</v>
       </c>
       <c r="C648" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D648" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -13739,24 +13742,21 @@
         <v>67</v>
       </c>
       <c r="C649" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D649" t="s">
-        <v>1315</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="650" spans="1:4">
       <c r="A650" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B650" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C650" t="s">
-        <v>623</v>
-      </c>
-      <c r="D650" t="s">
-        <v>1166</v>
+        <v>77</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -13764,10 +13764,13 @@
         <v>33</v>
       </c>
       <c r="B651" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C651" t="s">
-        <v>77</v>
+        <v>624</v>
+      </c>
+      <c r="D651" t="s">
+        <v>1316</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -13778,10 +13781,10 @@
         <v>67</v>
       </c>
       <c r="C652" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D652" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -13792,10 +13795,10 @@
         <v>67</v>
       </c>
       <c r="C653" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D653" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -13806,10 +13809,10 @@
         <v>67</v>
       </c>
       <c r="C654" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D654" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -13820,10 +13823,10 @@
         <v>67</v>
       </c>
       <c r="C655" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D655" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -13834,10 +13837,10 @@
         <v>67</v>
       </c>
       <c r="C656" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D656" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="657" spans="1:4">
@@ -13848,10 +13851,10 @@
         <v>67</v>
       </c>
       <c r="C657" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D657" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -13862,10 +13865,10 @@
         <v>67</v>
       </c>
       <c r="C658" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D658" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="659" spans="1:4">
@@ -13876,24 +13879,24 @@
         <v>67</v>
       </c>
       <c r="C659" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D659" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="660" spans="1:4">
       <c r="A660" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B660" t="s">
         <v>67</v>
       </c>
       <c r="C660" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D660" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="661" spans="1:4">
@@ -13904,24 +13907,24 @@
         <v>67</v>
       </c>
       <c r="C661" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D661" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="662" spans="1:4">
       <c r="A662" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B662" t="s">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="C662" t="s">
-        <v>634</v>
+        <v>404</v>
       </c>
       <c r="D662" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="663" spans="1:4">
@@ -13929,13 +13932,13 @@
         <v>35</v>
       </c>
       <c r="B663" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C663" t="s">
-        <v>404</v>
+        <v>29</v>
       </c>
       <c r="D663" t="s">
-        <v>1327</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="664" spans="1:4">
@@ -13943,13 +13946,10 @@
         <v>35</v>
       </c>
       <c r="B664" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C664" t="s">
-        <v>29</v>
-      </c>
-      <c r="D664" t="s">
-        <v>1224</v>
+        <v>529</v>
       </c>
     </row>
     <row r="665" spans="1:4">
@@ -13960,7 +13960,7 @@
         <v>29</v>
       </c>
       <c r="C665" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="666" spans="1:4">
@@ -13971,7 +13971,7 @@
         <v>29</v>
       </c>
       <c r="C666" t="s">
-        <v>530</v>
+        <v>28</v>
       </c>
     </row>
     <row r="667" spans="1:4">
@@ -13982,7 +13982,7 @@
         <v>29</v>
       </c>
       <c r="C667" t="s">
-        <v>28</v>
+        <v>531</v>
       </c>
     </row>
     <row r="668" spans="1:4">
@@ -13993,7 +13993,7 @@
         <v>29</v>
       </c>
       <c r="C668" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="669" spans="1:4">
@@ -14004,7 +14004,7 @@
         <v>29</v>
       </c>
       <c r="C669" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="670" spans="1:4">
@@ -14015,7 +14015,7 @@
         <v>29</v>
       </c>
       <c r="C670" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="671" spans="1:4">
@@ -14023,10 +14023,13 @@
         <v>35</v>
       </c>
       <c r="B671" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="C671" t="s">
-        <v>534</v>
+        <v>46</v>
+      </c>
+      <c r="D671" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="672" spans="1:4">
@@ -14034,13 +14037,13 @@
         <v>35</v>
       </c>
       <c r="B672" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C672" t="s">
-        <v>46</v>
+        <v>520</v>
       </c>
       <c r="D672" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="673" spans="1:4">
@@ -14051,10 +14054,10 @@
         <v>46</v>
       </c>
       <c r="C673" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D673" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="674" spans="1:4">
@@ -14065,10 +14068,7 @@
         <v>46</v>
       </c>
       <c r="C674" t="s">
-        <v>521</v>
-      </c>
-      <c r="D674" t="s">
-        <v>1219</v>
+        <v>522</v>
       </c>
     </row>
     <row r="675" spans="1:4">
@@ -14079,7 +14079,7 @@
         <v>46</v>
       </c>
       <c r="C675" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="676" spans="1:4">
@@ -14090,7 +14090,7 @@
         <v>46</v>
       </c>
       <c r="C676" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -14101,7 +14101,7 @@
         <v>46</v>
       </c>
       <c r="C677" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -14112,7 +14112,10 @@
         <v>46</v>
       </c>
       <c r="C678" t="s">
-        <v>525</v>
+        <v>25</v>
+      </c>
+      <c r="D678" t="s">
+        <v>1220</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -14123,10 +14126,10 @@
         <v>46</v>
       </c>
       <c r="C679" t="s">
-        <v>25</v>
+        <v>526</v>
       </c>
       <c r="D679" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -14137,10 +14140,10 @@
         <v>46</v>
       </c>
       <c r="C680" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D680" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -14151,10 +14154,10 @@
         <v>46</v>
       </c>
       <c r="C681" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D681" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -14162,13 +14165,13 @@
         <v>35</v>
       </c>
       <c r="B682" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C682" t="s">
-        <v>528</v>
+        <v>15</v>
       </c>
       <c r="D682" t="s">
-        <v>1223</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -14176,13 +14179,13 @@
         <v>35</v>
       </c>
       <c r="B683" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C683" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="D683" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="684" spans="1:4">
@@ -14193,10 +14196,10 @@
         <v>15</v>
       </c>
       <c r="C684" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D684" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="685" spans="1:4">
@@ -14207,10 +14210,10 @@
         <v>15</v>
       </c>
       <c r="C685" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D685" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -14221,10 +14224,10 @@
         <v>15</v>
       </c>
       <c r="C686" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D686" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -14235,10 +14238,10 @@
         <v>15</v>
       </c>
       <c r="C687" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D687" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="688" spans="1:4">
@@ -14249,10 +14252,10 @@
         <v>15</v>
       </c>
       <c r="C688" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D688" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -14263,10 +14266,10 @@
         <v>15</v>
       </c>
       <c r="C689" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D689" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="690" spans="1:4">
@@ -14274,13 +14277,13 @@
         <v>35</v>
       </c>
       <c r="B690" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="C690" t="s">
-        <v>501</v>
+        <v>17</v>
       </c>
       <c r="D690" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="691" spans="1:4">
@@ -14288,13 +14291,13 @@
         <v>35</v>
       </c>
       <c r="B691" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="C691" t="s">
-        <v>17</v>
+        <v>506</v>
       </c>
       <c r="D691" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="692" spans="1:4">
@@ -14305,10 +14308,10 @@
         <v>17</v>
       </c>
       <c r="C692" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D692" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -14316,13 +14319,10 @@
         <v>35</v>
       </c>
       <c r="B693" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C693" t="s">
-        <v>507</v>
-      </c>
-      <c r="D693" t="s">
-        <v>1203</v>
+        <v>16</v>
       </c>
     </row>
     <row r="694" spans="1:4">
@@ -14330,10 +14330,13 @@
         <v>35</v>
       </c>
       <c r="B694" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="C694" t="s">
-        <v>16</v>
+        <v>502</v>
+      </c>
+      <c r="D694" t="s">
+        <v>1197</v>
       </c>
     </row>
     <row r="695" spans="1:4">
@@ -14344,10 +14347,10 @@
         <v>16</v>
       </c>
       <c r="C695" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D695" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -14358,10 +14361,10 @@
         <v>16</v>
       </c>
       <c r="C696" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D696" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="697" spans="1:4">
@@ -14372,10 +14375,10 @@
         <v>16</v>
       </c>
       <c r="C697" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D697" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="698" spans="1:4">
@@ -14383,13 +14386,13 @@
         <v>35</v>
       </c>
       <c r="B698" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C698" t="s">
-        <v>505</v>
+        <v>21</v>
       </c>
       <c r="D698" t="s">
-        <v>1200</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="699" spans="1:4">
@@ -14397,13 +14400,13 @@
         <v>35</v>
       </c>
       <c r="B699" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="C699" t="s">
-        <v>21</v>
+        <v>547</v>
       </c>
       <c r="D699" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -14414,10 +14417,10 @@
         <v>21</v>
       </c>
       <c r="C700" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D700" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -14428,10 +14431,10 @@
         <v>21</v>
       </c>
       <c r="C701" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D701" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="702" spans="1:4">
@@ -14442,10 +14445,10 @@
         <v>21</v>
       </c>
       <c r="C702" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D702" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -14456,10 +14459,10 @@
         <v>21</v>
       </c>
       <c r="C703" t="s">
-        <v>550</v>
+        <v>53</v>
       </c>
       <c r="D703" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="704" spans="1:4">
@@ -14467,13 +14470,13 @@
         <v>35</v>
       </c>
       <c r="B704" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="C704" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="D704" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -14481,13 +14484,13 @@
         <v>35</v>
       </c>
       <c r="B705" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="C705" t="s">
-        <v>22</v>
+        <v>547</v>
       </c>
       <c r="D705" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -14498,10 +14501,10 @@
         <v>22</v>
       </c>
       <c r="C706" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="D706" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -14512,10 +14515,10 @@
         <v>22</v>
       </c>
       <c r="C707" t="s">
-        <v>557</v>
+        <v>23</v>
       </c>
       <c r="D707" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -14523,13 +14526,13 @@
         <v>35</v>
       </c>
       <c r="B708" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C708" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D708" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -14537,13 +14540,13 @@
         <v>35</v>
       </c>
       <c r="B709" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="C709" t="s">
-        <v>24</v>
+        <v>563</v>
       </c>
       <c r="D709" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -14554,10 +14557,10 @@
         <v>24</v>
       </c>
       <c r="C710" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D710" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -14568,10 +14571,10 @@
         <v>24</v>
       </c>
       <c r="C711" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D711" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -14582,10 +14585,10 @@
         <v>24</v>
       </c>
       <c r="C712" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D712" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -14596,10 +14599,10 @@
         <v>24</v>
       </c>
       <c r="C713" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D713" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -14610,10 +14613,10 @@
         <v>24</v>
       </c>
       <c r="C714" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D714" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -14624,10 +14627,10 @@
         <v>24</v>
       </c>
       <c r="C715" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D715" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -14638,10 +14641,10 @@
         <v>24</v>
       </c>
       <c r="C716" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D716" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -14652,10 +14655,10 @@
         <v>24</v>
       </c>
       <c r="C717" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D717" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -14666,10 +14669,10 @@
         <v>24</v>
       </c>
       <c r="C718" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D718" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -14680,10 +14683,10 @@
         <v>24</v>
       </c>
       <c r="C719" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D719" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -14694,10 +14697,10 @@
         <v>24</v>
       </c>
       <c r="C720" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D720" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="721" spans="1:4">
@@ -14705,13 +14708,13 @@
         <v>35</v>
       </c>
       <c r="B721" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C721" t="s">
-        <v>574</v>
+        <v>40</v>
       </c>
       <c r="D721" t="s">
-        <v>1269</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="722" spans="1:4">
@@ -14719,13 +14722,10 @@
         <v>35</v>
       </c>
       <c r="B722" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C722" t="s">
-        <v>40</v>
-      </c>
-      <c r="D722" t="s">
-        <v>1328</v>
+        <v>635</v>
       </c>
     </row>
     <row r="723" spans="1:4">
@@ -14736,7 +14736,10 @@
         <v>40</v>
       </c>
       <c r="C723" t="s">
-        <v>635</v>
+        <v>636</v>
+      </c>
+      <c r="D723" t="s">
+        <v>1329</v>
       </c>
     </row>
     <row r="724" spans="1:4">
@@ -14747,10 +14750,10 @@
         <v>40</v>
       </c>
       <c r="C724" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D724" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="725" spans="1:4">
@@ -14761,10 +14764,10 @@
         <v>40</v>
       </c>
       <c r="C725" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D725" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="726" spans="1:4">
@@ -14775,10 +14778,10 @@
         <v>40</v>
       </c>
       <c r="C726" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D726" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="727" spans="1:4">
@@ -14789,10 +14792,10 @@
         <v>40</v>
       </c>
       <c r="C727" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D727" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="728" spans="1:4">
@@ -14803,10 +14806,10 @@
         <v>40</v>
       </c>
       <c r="C728" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D728" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="729" spans="1:4">
@@ -14817,10 +14820,10 @@
         <v>40</v>
       </c>
       <c r="C729" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D729" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="730" spans="1:4">
@@ -14831,10 +14834,10 @@
         <v>40</v>
       </c>
       <c r="C730" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D730" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="731" spans="1:4">
@@ -14845,10 +14848,10 @@
         <v>40</v>
       </c>
       <c r="C731" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D731" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="732" spans="1:4">
@@ -14859,10 +14862,10 @@
         <v>40</v>
       </c>
       <c r="C732" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D732" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="733" spans="1:4">
@@ -14873,10 +14876,10 @@
         <v>40</v>
       </c>
       <c r="C733" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D733" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -14887,10 +14890,10 @@
         <v>40</v>
       </c>
       <c r="C734" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D734" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="735" spans="1:4">
@@ -14901,10 +14904,10 @@
         <v>40</v>
       </c>
       <c r="C735" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D735" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="736" spans="1:4">
@@ -14915,10 +14918,10 @@
         <v>40</v>
       </c>
       <c r="C736" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D736" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="737" spans="1:4">
@@ -14929,10 +14932,10 @@
         <v>40</v>
       </c>
       <c r="C737" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D737" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="738" spans="1:4">
@@ -14943,10 +14946,10 @@
         <v>40</v>
       </c>
       <c r="C738" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D738" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="739" spans="1:4">
@@ -14957,10 +14960,10 @@
         <v>40</v>
       </c>
       <c r="C739" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D739" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="740" spans="1:4">
@@ -14971,10 +14974,10 @@
         <v>40</v>
       </c>
       <c r="C740" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D740" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="741" spans="1:4">
@@ -14985,10 +14988,10 @@
         <v>40</v>
       </c>
       <c r="C741" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D741" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="742" spans="1:4">
@@ -14999,10 +15002,10 @@
         <v>40</v>
       </c>
       <c r="C742" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D742" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="743" spans="1:4">
@@ -15013,10 +15016,10 @@
         <v>40</v>
       </c>
       <c r="C743" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D743" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="744" spans="1:4">
@@ -15027,10 +15030,10 @@
         <v>40</v>
       </c>
       <c r="C744" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D744" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="745" spans="1:4">
@@ -15041,10 +15044,10 @@
         <v>40</v>
       </c>
       <c r="C745" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D745" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="746" spans="1:4">
@@ -15055,10 +15058,7 @@
         <v>40</v>
       </c>
       <c r="C746" t="s">
-        <v>658</v>
-      </c>
-      <c r="D746" t="s">
-        <v>1351</v>
+        <v>14</v>
       </c>
     </row>
     <row r="747" spans="1:4">
@@ -15066,10 +15066,13 @@
         <v>35</v>
       </c>
       <c r="B747" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C747" t="s">
-        <v>14</v>
+        <v>57</v>
+      </c>
+      <c r="D747" t="s">
+        <v>1352</v>
       </c>
     </row>
     <row r="748" spans="1:4">
@@ -15077,13 +15080,13 @@
         <v>35</v>
       </c>
       <c r="B748" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C748" t="s">
-        <v>57</v>
+        <v>659</v>
       </c>
       <c r="D748" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="749" spans="1:4">
@@ -15094,10 +15097,10 @@
         <v>57</v>
       </c>
       <c r="C749" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D749" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="750" spans="1:4">
@@ -15108,10 +15111,10 @@
         <v>57</v>
       </c>
       <c r="C750" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D750" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="751" spans="1:4">
@@ -15122,10 +15125,10 @@
         <v>57</v>
       </c>
       <c r="C751" t="s">
-        <v>661</v>
+        <v>5</v>
       </c>
       <c r="D751" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="752" spans="1:4">
@@ -15136,10 +15139,10 @@
         <v>57</v>
       </c>
       <c r="C752" t="s">
-        <v>5</v>
+        <v>662</v>
       </c>
       <c r="D752" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="753" spans="1:4">
@@ -15147,13 +15150,13 @@
         <v>35</v>
       </c>
       <c r="B753" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C753" t="s">
-        <v>662</v>
+        <v>30</v>
       </c>
       <c r="D753" t="s">
-        <v>1357</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="754" spans="1:4">
@@ -15161,13 +15164,13 @@
         <v>35</v>
       </c>
       <c r="B754" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C754" t="s">
-        <v>30</v>
+        <v>593</v>
       </c>
       <c r="D754" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="755" spans="1:4">
@@ -15178,10 +15181,10 @@
         <v>30</v>
       </c>
       <c r="C755" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D755" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="756" spans="1:4">
@@ -15192,10 +15195,10 @@
         <v>30</v>
       </c>
       <c r="C756" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D756" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="757" spans="1:4">
@@ -15206,10 +15209,10 @@
         <v>30</v>
       </c>
       <c r="C757" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D757" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="758" spans="1:4">
@@ -15217,13 +15220,13 @@
         <v>35</v>
       </c>
       <c r="B758" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C758" t="s">
-        <v>596</v>
+        <v>37</v>
       </c>
       <c r="D758" t="s">
-        <v>1290</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="759" spans="1:4">
@@ -15231,13 +15234,10 @@
         <v>35</v>
       </c>
       <c r="B759" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="C759" t="s">
-        <v>37</v>
-      </c>
-      <c r="D759" t="s">
-        <v>1358</v>
+        <v>663</v>
       </c>
     </row>
     <row r="760" spans="1:4">
@@ -15248,7 +15248,10 @@
         <v>37</v>
       </c>
       <c r="C760" t="s">
-        <v>663</v>
+        <v>664</v>
+      </c>
+      <c r="D760" t="s">
+        <v>1359</v>
       </c>
     </row>
     <row r="761" spans="1:4">
@@ -15259,10 +15262,10 @@
         <v>37</v>
       </c>
       <c r="C761" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D761" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="762" spans="1:4">
@@ -15273,10 +15276,10 @@
         <v>37</v>
       </c>
       <c r="C762" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D762" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="763" spans="1:4">
@@ -15284,13 +15287,13 @@
         <v>35</v>
       </c>
       <c r="B763" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C763" t="s">
-        <v>666</v>
+        <v>62</v>
       </c>
       <c r="D763" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="764" spans="1:4">
@@ -15301,10 +15304,10 @@
         <v>68</v>
       </c>
       <c r="C764" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D764" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="765" spans="1:4">
@@ -15312,13 +15315,13 @@
         <v>35</v>
       </c>
       <c r="B765" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C765" t="s">
-        <v>38</v>
+        <v>667</v>
       </c>
       <c r="D765" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="766" spans="1:4">
@@ -15329,10 +15332,10 @@
         <v>38</v>
       </c>
       <c r="C766" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D766" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="767" spans="1:4">
@@ -15343,10 +15346,10 @@
         <v>38</v>
       </c>
       <c r="C767" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D767" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="768" spans="1:4">
@@ -15354,13 +15357,13 @@
         <v>35</v>
       </c>
       <c r="B768" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C768" t="s">
-        <v>669</v>
+        <v>19</v>
       </c>
       <c r="D768" t="s">
-        <v>1366</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="769" spans="1:4">
@@ -15368,13 +15371,13 @@
         <v>35</v>
       </c>
       <c r="B769" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="C769" t="s">
-        <v>19</v>
+        <v>517</v>
       </c>
       <c r="D769" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="770" spans="1:4">
@@ -15385,10 +15388,10 @@
         <v>19</v>
       </c>
       <c r="C770" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D770" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="771" spans="1:4">
@@ -15399,10 +15402,10 @@
         <v>19</v>
       </c>
       <c r="C771" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D771" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="772" spans="1:4">
@@ -15410,13 +15413,13 @@
         <v>35</v>
       </c>
       <c r="B772" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="C772" t="s">
-        <v>519</v>
+        <v>39</v>
       </c>
       <c r="D772" t="s">
-        <v>1216</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="773" spans="1:4">
@@ -15424,13 +15427,13 @@
         <v>35</v>
       </c>
       <c r="B773" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C773" t="s">
-        <v>39</v>
+        <v>670</v>
       </c>
       <c r="D773" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="774" spans="1:4">
@@ -15441,10 +15444,10 @@
         <v>39</v>
       </c>
       <c r="C774" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D774" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="775" spans="1:4">
@@ -15455,10 +15458,10 @@
         <v>39</v>
       </c>
       <c r="C775" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D775" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="776" spans="1:4">
@@ -15466,13 +15469,13 @@
         <v>35</v>
       </c>
       <c r="B776" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C776" t="s">
-        <v>672</v>
+        <v>9</v>
       </c>
       <c r="D776" t="s">
-        <v>1370</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="777" spans="1:4">
@@ -15480,13 +15483,13 @@
         <v>35</v>
       </c>
       <c r="B777" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C777" t="s">
-        <v>9</v>
+        <v>405</v>
       </c>
       <c r="D777" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="778" spans="1:4">
@@ -15497,10 +15500,10 @@
         <v>9</v>
       </c>
       <c r="C778" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D778" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="779" spans="1:4">
@@ -15511,24 +15514,24 @@
         <v>9</v>
       </c>
       <c r="C779" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D779" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="780" spans="1:4">
       <c r="A780" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B780" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C780" t="s">
-        <v>407</v>
+        <v>77</v>
       </c>
       <c r="D780" t="s">
-        <v>1131</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="781" spans="1:4">
@@ -15536,13 +15539,13 @@
         <v>36</v>
       </c>
       <c r="B781" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C781" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="D781" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="782" spans="1:4">
@@ -15553,10 +15556,10 @@
         <v>67</v>
       </c>
       <c r="C782" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D782" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="783" spans="1:4">
@@ -15567,10 +15570,10 @@
         <v>67</v>
       </c>
       <c r="C783" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D783" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="784" spans="1:4">
@@ -15581,10 +15584,10 @@
         <v>67</v>
       </c>
       <c r="C784" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D784" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="785" spans="1:4">
@@ -15595,24 +15598,24 @@
         <v>67</v>
       </c>
       <c r="C785" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D785" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="786" spans="1:4">
       <c r="A786" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B786" t="s">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="C786" t="s">
-        <v>7</v>
+        <v>404</v>
       </c>
       <c r="D786" t="s">
-        <v>1376</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="787" spans="1:4">
@@ -15620,13 +15623,10 @@
         <v>37</v>
       </c>
       <c r="B787" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C787" t="s">
-        <v>404</v>
-      </c>
-      <c r="D787" t="s">
-        <v>1358</v>
+        <v>663</v>
       </c>
     </row>
     <row r="788" spans="1:4">
@@ -15637,7 +15637,10 @@
         <v>68</v>
       </c>
       <c r="C788" t="s">
-        <v>663</v>
+        <v>664</v>
+      </c>
+      <c r="D788" t="s">
+        <v>1359</v>
       </c>
     </row>
     <row r="789" spans="1:4">
@@ -15648,10 +15651,10 @@
         <v>68</v>
       </c>
       <c r="C789" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D789" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="790" spans="1:4">
@@ -15662,24 +15665,24 @@
         <v>68</v>
       </c>
       <c r="C790" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D790" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="791" spans="1:4">
       <c r="A791" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B791" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C791" t="s">
-        <v>666</v>
+        <v>404</v>
       </c>
       <c r="D791" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="792" spans="1:4">
@@ -15687,13 +15690,13 @@
         <v>38</v>
       </c>
       <c r="B792" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C792" t="s">
-        <v>404</v>
+        <v>667</v>
       </c>
       <c r="D792" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="793" spans="1:4">
@@ -15704,10 +15707,10 @@
         <v>68</v>
       </c>
       <c r="C793" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D793" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="794" spans="1:4">
@@ -15718,24 +15721,24 @@
         <v>68</v>
       </c>
       <c r="C794" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D794" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="795" spans="1:4">
       <c r="A795" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B795" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C795" t="s">
-        <v>669</v>
+        <v>404</v>
       </c>
       <c r="D795" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="796" spans="1:4">
@@ -15743,13 +15746,13 @@
         <v>39</v>
       </c>
       <c r="B796" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C796" t="s">
-        <v>404</v>
+        <v>670</v>
       </c>
       <c r="D796" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="797" spans="1:4">
@@ -15760,10 +15763,10 @@
         <v>68</v>
       </c>
       <c r="C797" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D797" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="798" spans="1:4">
@@ -15774,24 +15777,24 @@
         <v>68</v>
       </c>
       <c r="C798" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D798" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="799" spans="1:4">
       <c r="A799" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B799" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C799" t="s">
-        <v>672</v>
+        <v>404</v>
       </c>
       <c r="D799" t="s">
-        <v>1370</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="800" spans="1:4">
@@ -15799,13 +15802,10 @@
         <v>40</v>
       </c>
       <c r="B800" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C800" t="s">
-        <v>404</v>
-      </c>
-      <c r="D800" t="s">
-        <v>1328</v>
+        <v>635</v>
       </c>
     </row>
     <row r="801" spans="1:4">
@@ -15816,7 +15816,10 @@
         <v>68</v>
       </c>
       <c r="C801" t="s">
-        <v>635</v>
+        <v>636</v>
+      </c>
+      <c r="D801" t="s">
+        <v>1329</v>
       </c>
     </row>
     <row r="802" spans="1:4">
@@ -15827,10 +15830,10 @@
         <v>68</v>
       </c>
       <c r="C802" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D802" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="803" spans="1:4">
@@ -15841,10 +15844,10 @@
         <v>68</v>
       </c>
       <c r="C803" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D803" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="804" spans="1:4">
@@ -15855,10 +15858,10 @@
         <v>68</v>
       </c>
       <c r="C804" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D804" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="805" spans="1:4">
@@ -15869,10 +15872,10 @@
         <v>68</v>
       </c>
       <c r="C805" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D805" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="806" spans="1:4">
@@ -15883,10 +15886,10 @@
         <v>68</v>
       </c>
       <c r="C806" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D806" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="807" spans="1:4">
@@ -15897,10 +15900,10 @@
         <v>68</v>
       </c>
       <c r="C807" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D807" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="808" spans="1:4">
@@ -15911,10 +15914,10 @@
         <v>68</v>
       </c>
       <c r="C808" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D808" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="809" spans="1:4">
@@ -15925,10 +15928,10 @@
         <v>68</v>
       </c>
       <c r="C809" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D809" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="810" spans="1:4">
@@ -15939,10 +15942,10 @@
         <v>68</v>
       </c>
       <c r="C810" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D810" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="811" spans="1:4">
@@ -15953,10 +15956,10 @@
         <v>68</v>
       </c>
       <c r="C811" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D811" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="812" spans="1:4">
@@ -15967,10 +15970,10 @@
         <v>68</v>
       </c>
       <c r="C812" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D812" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="813" spans="1:4">
@@ -15981,10 +15984,10 @@
         <v>68</v>
       </c>
       <c r="C813" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D813" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="814" spans="1:4">
@@ -15995,10 +15998,10 @@
         <v>68</v>
       </c>
       <c r="C814" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D814" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="815" spans="1:4">
@@ -16009,10 +16012,10 @@
         <v>68</v>
       </c>
       <c r="C815" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D815" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="816" spans="1:4">
@@ -16023,10 +16026,10 @@
         <v>68</v>
       </c>
       <c r="C816" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D816" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="817" spans="1:4">
@@ -16037,10 +16040,10 @@
         <v>68</v>
       </c>
       <c r="C817" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D817" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="818" spans="1:4">
@@ -16051,10 +16054,10 @@
         <v>68</v>
       </c>
       <c r="C818" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D818" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="819" spans="1:4">
@@ -16065,10 +16068,10 @@
         <v>68</v>
       </c>
       <c r="C819" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D819" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="820" spans="1:4">
@@ -16079,10 +16082,10 @@
         <v>68</v>
       </c>
       <c r="C820" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D820" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="821" spans="1:4">
@@ -16093,10 +16096,10 @@
         <v>68</v>
       </c>
       <c r="C821" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D821" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="822" spans="1:4">
@@ -16107,10 +16110,10 @@
         <v>68</v>
       </c>
       <c r="C822" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D822" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="823" spans="1:4">
@@ -16121,10 +16124,10 @@
         <v>68</v>
       </c>
       <c r="C823" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D823" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="824" spans="1:4">
@@ -16135,21 +16138,18 @@
         <v>68</v>
       </c>
       <c r="C824" t="s">
-        <v>658</v>
-      </c>
-      <c r="D824" t="s">
-        <v>1351</v>
+        <v>14</v>
       </c>
     </row>
     <row r="825" spans="1:4">
       <c r="A825" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B825" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C825" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="826" spans="1:4">
@@ -16160,7 +16160,10 @@
         <v>67</v>
       </c>
       <c r="C826" t="s">
-        <v>3</v>
+        <v>673</v>
+      </c>
+      <c r="D826" t="s">
+        <v>1377</v>
       </c>
     </row>
     <row r="827" spans="1:4">
@@ -16171,10 +16174,10 @@
         <v>67</v>
       </c>
       <c r="C827" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D827" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="828" spans="1:4">
@@ -16185,10 +16188,10 @@
         <v>67</v>
       </c>
       <c r="C828" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D828" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="829" spans="1:4">
@@ -16199,10 +16202,10 @@
         <v>67</v>
       </c>
       <c r="C829" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D829" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="830" spans="1:4">
@@ -16213,10 +16216,10 @@
         <v>67</v>
       </c>
       <c r="C830" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D830" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="831" spans="1:4">
@@ -16227,10 +16230,10 @@
         <v>67</v>
       </c>
       <c r="C831" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D831" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="832" spans="1:4">
@@ -16241,24 +16244,21 @@
         <v>67</v>
       </c>
       <c r="C832" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D832" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="833" spans="1:4">
       <c r="A833" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B833" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C833" t="s">
-        <v>679</v>
-      </c>
-      <c r="D833" t="s">
-        <v>1383</v>
+        <v>77</v>
       </c>
     </row>
     <row r="834" spans="1:4">
@@ -16266,10 +16266,13 @@
         <v>42</v>
       </c>
       <c r="B834" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C834" t="s">
-        <v>77</v>
+        <v>0</v>
+      </c>
+      <c r="D834" t="s">
+        <v>1384</v>
       </c>
     </row>
     <row r="835" spans="1:4">
@@ -16280,10 +16283,10 @@
         <v>67</v>
       </c>
       <c r="C835" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D835" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="836" spans="1:4">
@@ -16294,10 +16297,10 @@
         <v>67</v>
       </c>
       <c r="C836" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D836" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="837" spans="1:4">
@@ -16308,24 +16311,21 @@
         <v>67</v>
       </c>
       <c r="C837" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D837" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="838" spans="1:4">
       <c r="A838" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B838" t="s">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="C838" t="s">
-        <v>3</v>
-      </c>
-      <c r="D838" t="s">
-        <v>1387</v>
+        <v>404</v>
       </c>
     </row>
     <row r="839" spans="1:4">
@@ -16333,10 +16333,13 @@
         <v>43</v>
       </c>
       <c r="B839" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C839" t="s">
-        <v>404</v>
+        <v>440</v>
+      </c>
+      <c r="D839" t="s">
+        <v>1159</v>
       </c>
     </row>
     <row r="840" spans="1:4">
@@ -16347,10 +16350,10 @@
         <v>68</v>
       </c>
       <c r="C840" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D840" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="841" spans="1:4">
@@ -16361,10 +16364,10 @@
         <v>68</v>
       </c>
       <c r="C841" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D841" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="842" spans="1:4">
@@ -16375,10 +16378,10 @@
         <v>68</v>
       </c>
       <c r="C842" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D842" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="843" spans="1:4">
@@ -16389,10 +16392,10 @@
         <v>68</v>
       </c>
       <c r="C843" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D843" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="844" spans="1:4">
@@ -16403,24 +16406,24 @@
         <v>68</v>
       </c>
       <c r="C844" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D844" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="845" spans="1:4">
       <c r="A845" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B845" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C845" t="s">
-        <v>445</v>
+        <v>680</v>
       </c>
       <c r="D845" t="s">
-        <v>1164</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="846" spans="1:4">
@@ -16431,10 +16434,10 @@
         <v>65</v>
       </c>
       <c r="C846" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D846" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="847" spans="1:4">
@@ -16445,24 +16448,24 @@
         <v>65</v>
       </c>
       <c r="C847" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D847" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="848" spans="1:4">
       <c r="A848" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B848" t="s">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C848" t="s">
-        <v>682</v>
+        <v>404</v>
       </c>
       <c r="D848" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="849" spans="1:4">
@@ -16470,13 +16473,13 @@
         <v>45</v>
       </c>
       <c r="B849" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C849" t="s">
-        <v>404</v>
+        <v>683</v>
       </c>
       <c r="D849" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="850" spans="1:4">
@@ -16487,10 +16490,10 @@
         <v>68</v>
       </c>
       <c r="C850" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D850" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="851" spans="1:4">
@@ -16501,10 +16504,10 @@
         <v>68</v>
       </c>
       <c r="C851" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D851" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="852" spans="1:4">
@@ -16515,10 +16518,10 @@
         <v>68</v>
       </c>
       <c r="C852" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D852" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="853" spans="1:4">
@@ -16529,10 +16532,10 @@
         <v>68</v>
       </c>
       <c r="C853" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D853" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="854" spans="1:4">
@@ -16543,10 +16546,10 @@
         <v>68</v>
       </c>
       <c r="C854" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D854" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="855" spans="1:4">
@@ -16557,10 +16560,10 @@
         <v>68</v>
       </c>
       <c r="C855" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D855" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="856" spans="1:4">
@@ -16571,10 +16574,10 @@
         <v>68</v>
       </c>
       <c r="C856" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D856" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="857" spans="1:4">
@@ -16585,10 +16588,10 @@
         <v>68</v>
       </c>
       <c r="C857" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D857" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="858" spans="1:4">
@@ -16599,24 +16602,24 @@
         <v>68</v>
       </c>
       <c r="C858" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D858" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="859" spans="1:4">
       <c r="A859" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B859" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C859" t="s">
-        <v>692</v>
+        <v>404</v>
       </c>
       <c r="D859" t="s">
-        <v>1401</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="860" spans="1:4">
@@ -16624,13 +16627,13 @@
         <v>46</v>
       </c>
       <c r="B860" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C860" t="s">
-        <v>404</v>
+        <v>520</v>
       </c>
       <c r="D860" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="861" spans="1:4">
@@ -16641,10 +16644,10 @@
         <v>68</v>
       </c>
       <c r="C861" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D861" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="862" spans="1:4">
@@ -16655,10 +16658,7 @@
         <v>68</v>
       </c>
       <c r="C862" t="s">
-        <v>521</v>
-      </c>
-      <c r="D862" t="s">
-        <v>1219</v>
+        <v>522</v>
       </c>
     </row>
     <row r="863" spans="1:4">
@@ -16669,7 +16669,7 @@
         <v>68</v>
       </c>
       <c r="C863" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="864" spans="1:4">
@@ -16680,7 +16680,7 @@
         <v>68</v>
       </c>
       <c r="C864" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="865" spans="1:4">
@@ -16691,7 +16691,7 @@
         <v>68</v>
       </c>
       <c r="C865" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="866" spans="1:4">
@@ -16702,7 +16702,10 @@
         <v>68</v>
       </c>
       <c r="C866" t="s">
-        <v>525</v>
+        <v>25</v>
+      </c>
+      <c r="D866" t="s">
+        <v>1220</v>
       </c>
     </row>
     <row r="867" spans="1:4">
@@ -16710,13 +16713,13 @@
         <v>46</v>
       </c>
       <c r="B867" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C867" t="s">
-        <v>25</v>
+        <v>575</v>
       </c>
       <c r="D867" t="s">
-        <v>1220</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="868" spans="1:4">
@@ -16727,10 +16730,10 @@
         <v>25</v>
       </c>
       <c r="C868" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D868" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="869" spans="1:4">
@@ -16741,10 +16744,10 @@
         <v>25</v>
       </c>
       <c r="C869" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D869" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="870" spans="1:4">
@@ -16752,13 +16755,13 @@
         <v>46</v>
       </c>
       <c r="B870" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C870" t="s">
-        <v>577</v>
+        <v>526</v>
       </c>
       <c r="D870" t="s">
-        <v>1272</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="871" spans="1:4">
@@ -16769,10 +16772,10 @@
         <v>68</v>
       </c>
       <c r="C871" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D871" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="872" spans="1:4">
@@ -16783,24 +16786,21 @@
         <v>68</v>
       </c>
       <c r="C872" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D872" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="873" spans="1:4">
       <c r="A873" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B873" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C873" t="s">
-        <v>528</v>
-      </c>
-      <c r="D873" t="s">
-        <v>1223</v>
+        <v>404</v>
       </c>
     </row>
     <row r="874" spans="1:4">
@@ -16808,10 +16808,13 @@
         <v>47</v>
       </c>
       <c r="B874" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C874" t="s">
-        <v>404</v>
+        <v>693</v>
+      </c>
+      <c r="D874" t="s">
+        <v>1402</v>
       </c>
     </row>
     <row r="875" spans="1:4">
@@ -16822,10 +16825,10 @@
         <v>68</v>
       </c>
       <c r="C875" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D875" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="876" spans="1:4">
@@ -16836,10 +16839,10 @@
         <v>68</v>
       </c>
       <c r="C876" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D876" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="877" spans="1:4">
@@ -16850,10 +16853,10 @@
         <v>68</v>
       </c>
       <c r="C877" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D877" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="878" spans="1:4">
@@ -16864,10 +16867,10 @@
         <v>68</v>
       </c>
       <c r="C878" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D878" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="879" spans="1:4">
@@ -16878,10 +16881,10 @@
         <v>68</v>
       </c>
       <c r="C879" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D879" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="880" spans="1:4">
@@ -16892,10 +16895,10 @@
         <v>68</v>
       </c>
       <c r="C880" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D880" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="881" spans="1:4">
@@ -16906,10 +16909,10 @@
         <v>68</v>
       </c>
       <c r="C881" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D881" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="882" spans="1:4">
@@ -16920,24 +16923,21 @@
         <v>68</v>
       </c>
       <c r="C882" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D882" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="883" spans="1:4">
       <c r="A883" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B883" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C883" t="s">
-        <v>701</v>
-      </c>
-      <c r="D883" t="s">
-        <v>1410</v>
+        <v>3</v>
       </c>
     </row>
     <row r="884" spans="1:4">
@@ -16948,7 +16948,7 @@
         <v>67</v>
       </c>
       <c r="C884" t="s">
-        <v>3</v>
+        <v>702</v>
       </c>
     </row>
     <row r="885" spans="1:4">
@@ -16959,7 +16959,7 @@
         <v>67</v>
       </c>
       <c r="C885" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="886" spans="1:4">
@@ -16970,7 +16970,7 @@
         <v>67</v>
       </c>
       <c r="C886" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="887" spans="1:4">
@@ -16981,7 +16981,7 @@
         <v>67</v>
       </c>
       <c r="C887" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="888" spans="1:4">
@@ -16992,7 +16992,7 @@
         <v>67</v>
       </c>
       <c r="C888" t="s">
-        <v>705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="889" spans="1:4">
@@ -17003,7 +17003,7 @@
         <v>67</v>
       </c>
       <c r="C889" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="890" spans="1:4">
@@ -17014,7 +17014,7 @@
         <v>67</v>
       </c>
       <c r="C890" t="s">
-        <v>1</v>
+        <v>706</v>
       </c>
     </row>
     <row r="891" spans="1:4">
@@ -17025,7 +17025,7 @@
         <v>67</v>
       </c>
       <c r="C891" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="892" spans="1:4">
@@ -17036,18 +17036,18 @@
         <v>67</v>
       </c>
       <c r="C892" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="893" spans="1:4">
       <c r="A893" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B893" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C893" t="s">
-        <v>708</v>
+        <v>77</v>
       </c>
     </row>
     <row r="894" spans="1:4">
@@ -17055,10 +17055,13 @@
         <v>49</v>
       </c>
       <c r="B894" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C894" t="s">
-        <v>77</v>
+        <v>709</v>
+      </c>
+      <c r="D894" t="s">
+        <v>1411</v>
       </c>
     </row>
     <row r="895" spans="1:4">
@@ -17069,10 +17072,10 @@
         <v>67</v>
       </c>
       <c r="C895" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D895" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="896" spans="1:4">
@@ -17083,10 +17086,10 @@
         <v>67</v>
       </c>
       <c r="C896" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D896" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="897" spans="1:4">
@@ -17097,10 +17100,10 @@
         <v>67</v>
       </c>
       <c r="C897" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D897" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="898" spans="1:4">
@@ -17111,24 +17114,24 @@
         <v>67</v>
       </c>
       <c r="C898" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D898" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="899" spans="1:4">
       <c r="A899" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B899" t="s">
         <v>67</v>
       </c>
       <c r="C899" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D899" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="900" spans="1:4">
@@ -17139,10 +17142,10 @@
         <v>67</v>
       </c>
       <c r="C900" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D900" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="901" spans="1:4">
@@ -17153,10 +17156,10 @@
         <v>67</v>
       </c>
       <c r="C901" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D901" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="902" spans="1:4">
@@ -17167,21 +17170,21 @@
         <v>67</v>
       </c>
       <c r="C902" t="s">
-        <v>716</v>
-      </c>
-      <c r="D902" t="s">
-        <v>1418</v>
+        <v>31</v>
       </c>
     </row>
     <row r="903" spans="1:4">
       <c r="A903" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B903" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C903" t="s">
-        <v>31</v>
+        <v>77</v>
+      </c>
+      <c r="D903" t="s">
+        <v>1419</v>
       </c>
     </row>
     <row r="904" spans="1:4">
@@ -17189,13 +17192,13 @@
         <v>51</v>
       </c>
       <c r="B904" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C904" t="s">
-        <v>77</v>
+        <v>717</v>
       </c>
       <c r="D904" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="905" spans="1:4">
@@ -17206,10 +17209,10 @@
         <v>67</v>
       </c>
       <c r="C905" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D905" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="906" spans="1:4">
@@ -17220,10 +17223,10 @@
         <v>67</v>
       </c>
       <c r="C906" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D906" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="907" spans="1:4">
@@ -17234,10 +17237,10 @@
         <v>67</v>
       </c>
       <c r="C907" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D907" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="908" spans="1:4">
@@ -17248,10 +17251,10 @@
         <v>67</v>
       </c>
       <c r="C908" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D908" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="909" spans="1:4">
@@ -17262,10 +17265,10 @@
         <v>67</v>
       </c>
       <c r="C909" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D909" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="910" spans="1:4">
@@ -17276,10 +17279,10 @@
         <v>67</v>
       </c>
       <c r="C910" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D910" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="911" spans="1:4">
@@ -17290,10 +17293,10 @@
         <v>67</v>
       </c>
       <c r="C911" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D911" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="912" spans="1:4">
@@ -17304,10 +17307,10 @@
         <v>67</v>
       </c>
       <c r="C912" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D912" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="913" spans="1:4">
@@ -17318,10 +17321,10 @@
         <v>67</v>
       </c>
       <c r="C913" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D913" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="914" spans="1:4">
@@ -17332,10 +17335,10 @@
         <v>67</v>
       </c>
       <c r="C914" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D914" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="915" spans="1:4">
@@ -17346,10 +17349,10 @@
         <v>67</v>
       </c>
       <c r="C915" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D915" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="916" spans="1:4">
@@ -17360,10 +17363,10 @@
         <v>67</v>
       </c>
       <c r="C916" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D916" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="917" spans="1:4">
@@ -17374,10 +17377,10 @@
         <v>67</v>
       </c>
       <c r="C917" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D917" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="918" spans="1:4">
@@ -17388,10 +17391,10 @@
         <v>67</v>
       </c>
       <c r="C918" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D918" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="919" spans="1:4">
@@ -17402,24 +17405,24 @@
         <v>67</v>
       </c>
       <c r="C919" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D919" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="920" spans="1:4">
       <c r="A920" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B920" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C920" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D920" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="921" spans="1:4">
@@ -17430,10 +17433,10 @@
         <v>68</v>
       </c>
       <c r="C921" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D921" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="922" spans="1:4">
@@ -17444,10 +17447,10 @@
         <v>68</v>
       </c>
       <c r="C922" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D922" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="923" spans="1:4">
@@ -17458,10 +17461,10 @@
         <v>68</v>
       </c>
       <c r="C923" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D923" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="924" spans="1:4">
@@ -17472,10 +17475,10 @@
         <v>68</v>
       </c>
       <c r="C924" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D924" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="925" spans="1:4">
@@ -17486,10 +17489,10 @@
         <v>68</v>
       </c>
       <c r="C925" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D925" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="926" spans="1:4">
@@ -17500,10 +17503,10 @@
         <v>68</v>
       </c>
       <c r="C926" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D926" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="927" spans="1:4">
@@ -17514,10 +17517,10 @@
         <v>68</v>
       </c>
       <c r="C927" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D927" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="928" spans="1:4">
@@ -17528,10 +17531,10 @@
         <v>68</v>
       </c>
       <c r="C928" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D928" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="929" spans="1:4">
@@ -17542,10 +17545,10 @@
         <v>68</v>
       </c>
       <c r="C929" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D929" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="930" spans="1:4">
@@ -17556,10 +17559,10 @@
         <v>68</v>
       </c>
       <c r="C930" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D930" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="931" spans="1:4">
@@ -17570,24 +17573,24 @@
         <v>68</v>
       </c>
       <c r="C931" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D931" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="932" spans="1:4">
       <c r="A932" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B932" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C932" t="s">
-        <v>744</v>
+        <v>404</v>
       </c>
       <c r="D932" t="s">
-        <v>1447</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="933" spans="1:4">
@@ -17595,13 +17598,13 @@
         <v>53</v>
       </c>
       <c r="B933" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C933" t="s">
-        <v>404</v>
+        <v>551</v>
       </c>
       <c r="D933" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="934" spans="1:4">
@@ -17612,10 +17615,10 @@
         <v>68</v>
       </c>
       <c r="C934" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D934" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="935" spans="1:4">
@@ -17626,10 +17629,10 @@
         <v>68</v>
       </c>
       <c r="C935" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D935" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="936" spans="1:4">
@@ -17640,10 +17643,10 @@
         <v>68</v>
       </c>
       <c r="C936" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D936" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="937" spans="1:4">
@@ -17654,10 +17657,10 @@
         <v>68</v>
       </c>
       <c r="C937" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D937" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="938" spans="1:4">
@@ -17668,24 +17671,24 @@
         <v>68</v>
       </c>
       <c r="C938" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D938" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="939" spans="1:4">
       <c r="A939" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B939" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C939" t="s">
-        <v>556</v>
+        <v>404</v>
       </c>
       <c r="D939" t="s">
-        <v>1247</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="940" spans="1:4">
@@ -17693,13 +17696,10 @@
         <v>54</v>
       </c>
       <c r="B940" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C940" t="s">
-        <v>404</v>
-      </c>
-      <c r="D940" t="s">
-        <v>1448</v>
+        <v>745</v>
       </c>
     </row>
     <row r="941" spans="1:4">
@@ -17710,7 +17710,7 @@
         <v>68</v>
       </c>
       <c r="C941" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="942" spans="1:4">
@@ -17721,7 +17721,7 @@
         <v>68</v>
       </c>
       <c r="C942" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="943" spans="1:4">
@@ -17732,7 +17732,7 @@
         <v>68</v>
       </c>
       <c r="C943" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="944" spans="1:4">
@@ -17754,7 +17754,7 @@
         <v>68</v>
       </c>
       <c r="C945" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="946" spans="1:4">
@@ -17765,7 +17765,7 @@
         <v>68</v>
       </c>
       <c r="C946" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="947" spans="1:4">
@@ -17776,18 +17776,18 @@
         <v>68</v>
       </c>
       <c r="C947" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="948" spans="1:4">
       <c r="A948" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B948" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C948" t="s">
-        <v>751</v>
+        <v>404</v>
       </c>
     </row>
     <row r="949" spans="1:4">
@@ -17795,10 +17795,13 @@
         <v>55</v>
       </c>
       <c r="B949" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C949" t="s">
-        <v>404</v>
+        <v>752</v>
+      </c>
+      <c r="D949" t="s">
+        <v>1449</v>
       </c>
     </row>
     <row r="950" spans="1:4">
@@ -17809,10 +17812,10 @@
         <v>68</v>
       </c>
       <c r="C950" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D950" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="951" spans="1:4">
@@ -17823,10 +17826,10 @@
         <v>68</v>
       </c>
       <c r="C951" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D951" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="952" spans="1:4">
@@ -17837,10 +17840,10 @@
         <v>68</v>
       </c>
       <c r="C952" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D952" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="953" spans="1:4">
@@ -17851,10 +17854,10 @@
         <v>68</v>
       </c>
       <c r="C953" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D953" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="954" spans="1:4">
@@ -17865,10 +17868,10 @@
         <v>68</v>
       </c>
       <c r="C954" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D954" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="955" spans="1:4">
@@ -17879,10 +17882,10 @@
         <v>68</v>
       </c>
       <c r="C955" t="s">
-        <v>757</v>
+        <v>54</v>
       </c>
       <c r="D955" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="956" spans="1:4">
@@ -17890,13 +17893,10 @@
         <v>55</v>
       </c>
       <c r="B956" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C956" t="s">
-        <v>54</v>
-      </c>
-      <c r="D956" t="s">
-        <v>1448</v>
+        <v>745</v>
       </c>
     </row>
     <row r="957" spans="1:4">
@@ -17907,7 +17907,7 @@
         <v>54</v>
       </c>
       <c r="C957" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="958" spans="1:4">
@@ -17918,7 +17918,7 @@
         <v>54</v>
       </c>
       <c r="C958" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="959" spans="1:4">
@@ -17929,7 +17929,7 @@
         <v>54</v>
       </c>
       <c r="C959" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="960" spans="1:4">
@@ -17951,7 +17951,7 @@
         <v>54</v>
       </c>
       <c r="C961" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="962" spans="1:4">
@@ -17962,7 +17962,7 @@
         <v>54</v>
       </c>
       <c r="C962" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="963" spans="1:4">
@@ -17973,7 +17973,7 @@
         <v>54</v>
       </c>
       <c r="C963" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="964" spans="1:4">
@@ -17981,10 +17981,13 @@
         <v>55</v>
       </c>
       <c r="B964" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C964" t="s">
-        <v>751</v>
+        <v>758</v>
+      </c>
+      <c r="D964" t="s">
+        <v>1455</v>
       </c>
     </row>
     <row r="965" spans="1:4">
@@ -17995,10 +17998,10 @@
         <v>68</v>
       </c>
       <c r="C965" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D965" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="966" spans="1:4">
@@ -18009,10 +18012,10 @@
         <v>68</v>
       </c>
       <c r="C966" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D966" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="967" spans="1:4">
@@ -18020,13 +18023,13 @@
         <v>55</v>
       </c>
       <c r="B967" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C967" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D967" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="968" spans="1:4">
@@ -18037,10 +18040,10 @@
         <v>70</v>
       </c>
       <c r="C968" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D968" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="969" spans="1:4">
@@ -18051,10 +18054,10 @@
         <v>70</v>
       </c>
       <c r="C969" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D969" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="970" spans="1:4">
@@ -18065,10 +18068,10 @@
         <v>70</v>
       </c>
       <c r="C970" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D970" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="971" spans="1:4">
@@ -18079,10 +18082,10 @@
         <v>70</v>
       </c>
       <c r="C971" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D971" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="972" spans="1:4">
@@ -18093,10 +18096,10 @@
         <v>70</v>
       </c>
       <c r="C972" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D972" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="973" spans="1:4">
@@ -18107,10 +18110,10 @@
         <v>70</v>
       </c>
       <c r="C973" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D973" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="974" spans="1:4">
@@ -18121,10 +18124,10 @@
         <v>70</v>
       </c>
       <c r="C974" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D974" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="975" spans="1:4">
@@ -18135,10 +18138,10 @@
         <v>70</v>
       </c>
       <c r="C975" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D975" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="976" spans="1:4">
@@ -18149,10 +18152,10 @@
         <v>70</v>
       </c>
       <c r="C976" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D976" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="977" spans="1:4">
@@ -18163,10 +18166,10 @@
         <v>70</v>
       </c>
       <c r="C977" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D977" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="978" spans="1:4">
@@ -18177,10 +18180,10 @@
         <v>70</v>
       </c>
       <c r="C978" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D978" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="979" spans="1:4">
@@ -18191,10 +18194,10 @@
         <v>70</v>
       </c>
       <c r="C979" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D979" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="980" spans="1:4">
@@ -18205,10 +18208,10 @@
         <v>70</v>
       </c>
       <c r="C980" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D980" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="981" spans="1:4">
@@ -18219,10 +18222,10 @@
         <v>70</v>
       </c>
       <c r="C981" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D981" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="982" spans="1:4">
@@ -18233,10 +18236,10 @@
         <v>70</v>
       </c>
       <c r="C982" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D982" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="983" spans="1:4">
@@ -18247,10 +18250,10 @@
         <v>70</v>
       </c>
       <c r="C983" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D983" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="984" spans="1:4">
@@ -18261,10 +18264,10 @@
         <v>70</v>
       </c>
       <c r="C984" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D984" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="985" spans="1:4">
@@ -18275,10 +18278,10 @@
         <v>70</v>
       </c>
       <c r="C985" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D985" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="986" spans="1:4">
@@ -18289,10 +18292,10 @@
         <v>70</v>
       </c>
       <c r="C986" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D986" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="987" spans="1:4">
@@ -18303,24 +18306,21 @@
         <v>70</v>
       </c>
       <c r="C987" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D987" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="988" spans="1:4">
       <c r="A988" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B988" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C988" t="s">
-        <v>781</v>
-      </c>
-      <c r="D988" t="s">
-        <v>1478</v>
+        <v>71</v>
       </c>
     </row>
     <row r="989" spans="1:4">
@@ -18328,10 +18328,13 @@
         <v>56</v>
       </c>
       <c r="B989" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C989" t="s">
-        <v>71</v>
+        <v>782</v>
+      </c>
+      <c r="D989" t="s">
+        <v>1479</v>
       </c>
     </row>
     <row r="990" spans="1:4">
@@ -18345,7 +18348,7 @@
         <v>782</v>
       </c>
       <c r="D990" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="991" spans="1:4">
@@ -18359,7 +18362,7 @@
         <v>782</v>
       </c>
       <c r="D991" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="992" spans="1:4">
@@ -18373,7 +18376,7 @@
         <v>782</v>
       </c>
       <c r="D992" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="993" spans="1:4">
@@ -18387,21 +18390,21 @@
         <v>782</v>
       </c>
       <c r="D993" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="994" spans="1:4">
       <c r="A994" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B994" t="s">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C994" t="s">
-        <v>782</v>
+        <v>404</v>
       </c>
       <c r="D994" t="s">
-        <v>1483</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="995" spans="1:4">
@@ -18409,13 +18412,13 @@
         <v>57</v>
       </c>
       <c r="B995" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C995" t="s">
-        <v>404</v>
+        <v>659</v>
       </c>
       <c r="D995" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="996" spans="1:4">
@@ -18426,10 +18429,10 @@
         <v>68</v>
       </c>
       <c r="C996" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D996" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="997" spans="1:4">
@@ -18440,10 +18443,10 @@
         <v>68</v>
       </c>
       <c r="C997" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D997" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="998" spans="1:4">
@@ -18454,10 +18457,10 @@
         <v>68</v>
       </c>
       <c r="C998" t="s">
-        <v>661</v>
+        <v>5</v>
       </c>
       <c r="D998" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="999" spans="1:4">
@@ -18468,24 +18471,21 @@
         <v>68</v>
       </c>
       <c r="C999" t="s">
-        <v>5</v>
+        <v>662</v>
       </c>
       <c r="D999" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="1000" spans="1:4">
       <c r="A1000" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1000" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C1000" t="s">
-        <v>662</v>
-      </c>
-      <c r="D1000" t="s">
-        <v>1357</v>
+        <v>404</v>
       </c>
     </row>
     <row r="1001" spans="1:4">
@@ -18493,10 +18493,13 @@
         <v>58</v>
       </c>
       <c r="B1001" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C1001" t="s">
-        <v>404</v>
+        <v>783</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>1484</v>
       </c>
     </row>
     <row r="1002" spans="1:4">
@@ -18507,10 +18510,10 @@
         <v>68</v>
       </c>
       <c r="C1002" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D1002" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1003" spans="1:4">
@@ -18521,24 +18524,21 @@
         <v>68</v>
       </c>
       <c r="C1003" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D1003" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1004" spans="1:4">
       <c r="A1004" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1004" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C1004" t="s">
-        <v>785</v>
-      </c>
-      <c r="D1004" t="s">
-        <v>1486</v>
+        <v>404</v>
       </c>
     </row>
     <row r="1005" spans="1:4">
@@ -18546,10 +18546,13 @@
         <v>59</v>
       </c>
       <c r="B1005" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C1005" t="s">
-        <v>404</v>
+        <v>429</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>1149</v>
       </c>
     </row>
     <row r="1006" spans="1:4">
@@ -18560,10 +18563,10 @@
         <v>68</v>
       </c>
       <c r="C1006" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D1006" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1007" spans="1:4">
@@ -18574,10 +18577,10 @@
         <v>68</v>
       </c>
       <c r="C1007" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D1007" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1008" spans="1:4">
@@ -18585,27 +18588,24 @@
         <v>59</v>
       </c>
       <c r="B1008" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1008" t="s">
-        <v>431</v>
+        <v>786</v>
       </c>
       <c r="D1008" t="s">
-        <v>1151</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1009" spans="1:4">
       <c r="A1009" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1009" t="s">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C1009" t="s">
-        <v>786</v>
-      </c>
-      <c r="D1009" t="s">
-        <v>1487</v>
+        <v>404</v>
       </c>
     </row>
     <row r="1010" spans="1:4">
@@ -18613,10 +18613,13 @@
         <v>60</v>
       </c>
       <c r="B1010" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C1010" t="s">
-        <v>404</v>
+        <v>426</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>1146</v>
       </c>
     </row>
     <row r="1011" spans="1:4">
@@ -18627,10 +18630,10 @@
         <v>68</v>
       </c>
       <c r="C1011" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D1011" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1012" spans="1:4">
@@ -18641,10 +18644,10 @@
         <v>68</v>
       </c>
       <c r="C1012" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D1012" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1013" spans="1:4">
@@ -18652,13 +18655,13 @@
         <v>60</v>
       </c>
       <c r="B1013" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1013" t="s">
-        <v>428</v>
+        <v>787</v>
       </c>
       <c r="D1013" t="s">
-        <v>1148</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1014" spans="1:4">
@@ -18669,10 +18672,10 @@
         <v>70</v>
       </c>
       <c r="C1014" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D1014" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1015" spans="1:4">
@@ -18683,24 +18686,24 @@
         <v>70</v>
       </c>
       <c r="C1015" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D1015" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1016" spans="1:4">
       <c r="A1016" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1016" t="s">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C1016" t="s">
-        <v>789</v>
+        <v>404</v>
       </c>
       <c r="D1016" t="s">
-        <v>1490</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="1017" spans="1:4">
@@ -18708,13 +18711,13 @@
         <v>61</v>
       </c>
       <c r="B1017" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C1017" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="D1017" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1018" spans="1:4">
@@ -18725,10 +18728,10 @@
         <v>68</v>
       </c>
       <c r="C1018" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D1018" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1019" spans="1:4">
@@ -18739,10 +18742,10 @@
         <v>68</v>
       </c>
       <c r="C1019" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D1019" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="1020" spans="1:4">
@@ -18753,35 +18756,35 @@
         <v>68</v>
       </c>
       <c r="C1020" t="s">
-        <v>436</v>
-      </c>
-      <c r="D1020" t="s">
-        <v>1157</v>
+        <v>437</v>
       </c>
     </row>
     <row r="1021" spans="1:4">
       <c r="A1021" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1021" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C1021" t="s">
-        <v>437</v>
+        <v>404</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>1362</v>
       </c>
     </row>
     <row r="1022" spans="1:4">
       <c r="A1022" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1022" t="s">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="C1022" t="s">
-        <v>404</v>
+        <v>71</v>
       </c>
       <c r="D1022" t="s">
-        <v>1362</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1023" spans="1:4">
@@ -18789,13 +18792,13 @@
         <v>63</v>
       </c>
       <c r="B1023" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1023" t="s">
-        <v>71</v>
+        <v>790</v>
       </c>
       <c r="D1023" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1024" spans="1:4">
@@ -18806,10 +18809,10 @@
         <v>65</v>
       </c>
       <c r="C1024" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D1024" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1025" spans="1:4">
@@ -18820,10 +18823,10 @@
         <v>65</v>
       </c>
       <c r="C1025" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D1025" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1026" spans="1:4">
@@ -18834,10 +18837,10 @@
         <v>65</v>
       </c>
       <c r="C1026" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D1026" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1027" spans="1:4">
@@ -18848,10 +18851,10 @@
         <v>65</v>
       </c>
       <c r="C1027" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D1027" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1028" spans="1:4">
@@ -18862,10 +18865,10 @@
         <v>65</v>
       </c>
       <c r="C1028" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D1028" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1029" spans="1:4">
@@ -18876,10 +18879,10 @@
         <v>65</v>
       </c>
       <c r="C1029" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D1029" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="1030" spans="1:4">
@@ -18890,10 +18893,10 @@
         <v>65</v>
       </c>
       <c r="C1030" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D1030" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1031" spans="1:4">
@@ -18904,10 +18907,10 @@
         <v>65</v>
       </c>
       <c r="C1031" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D1031" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1032" spans="1:4">
@@ -18918,23 +18921,9 @@
         <v>65</v>
       </c>
       <c r="C1032" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D1032" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="1033" spans="1:4">
-      <c r="A1033" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1033" t="s">
-        <v>799</v>
-      </c>
-      <c r="D1033" t="s">
         <v>1501</v>
       </c>
     </row>

--- a/Streamlit/Data/knowledge_base.xlsx
+++ b/Streamlit/Data/knowledge_base.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="1502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3964" uniqueCount="1504">
   <si>
     <t>Process</t>
   </si>
@@ -2414,6 +2414,9 @@
   </si>
   <si>
     <t>Stakeholders Have Conflicting Values</t>
+  </si>
+  <si>
+    <t>Chaos Theory</t>
   </si>
   <si>
     <t>Agents make plans and take actions to achieve goals, combining a Language Model's (LM) ability to reason with the practical ability to act, allowing it to handle complex, multi-step tasks that a model alone cannot.  Agents VASTLY range in capabilities, from Classifying agents from simple, connected problem-solvers
@@ -4643,6 +4646,9 @@
   </si>
   <si>
     <t>What’s “better” for one group may be “worse” for another.</t>
+  </si>
+  <si>
+    <t>Branch of mathematics, formally established in the 1960s, that studies complex dynamical systems highly sensitive to initial conditions. Its core principle—famously illustrated by the butterfly effect—demonstrates that minuscule shifts in a starting state can trigger vastly diverging outcomes over time. This framework is vital because it proves that fully deterministic systems can still generate fundamental unpredictability, shattering the traditional view of absolute clockwork order in nature. Today, its applications range from improving weather forecasting and analyzing economic market volatility to modeling complex biological rhythms.</t>
   </si>
 </sst>
 </file>
@@ -4974,7 +4980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1032"/>
+  <dimension ref="A1:D1033"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5002,7 +5008,7 @@
         <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5016,7 +5022,7 @@
         <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5030,7 +5036,7 @@
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5044,7 +5050,7 @@
         <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5058,7 +5064,7 @@
         <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5072,7 +5078,7 @@
         <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5119,7 +5125,7 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5166,7 +5172,7 @@
         <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -5180,7 +5186,7 @@
         <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5194,7 +5200,7 @@
         <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -5208,7 +5214,7 @@
         <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -5222,7 +5228,7 @@
         <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -5236,7 +5242,7 @@
         <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5250,7 +5256,7 @@
         <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -5264,7 +5270,7 @@
         <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5278,7 +5284,7 @@
         <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5292,7 +5298,7 @@
         <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -5306,7 +5312,7 @@
         <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5320,7 +5326,7 @@
         <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5334,7 +5340,7 @@
         <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -5348,7 +5354,7 @@
         <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5362,7 +5368,7 @@
         <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -5376,7 +5382,7 @@
         <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -5390,7 +5396,7 @@
         <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5404,7 +5410,7 @@
         <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5418,7 +5424,7 @@
         <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5432,7 +5438,7 @@
         <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5446,7 +5452,7 @@
         <v>103</v>
       </c>
       <c r="D35" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5460,7 +5466,7 @@
         <v>104</v>
       </c>
       <c r="D36" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5474,7 +5480,7 @@
         <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -5488,7 +5494,7 @@
         <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -5502,7 +5508,7 @@
         <v>107</v>
       </c>
       <c r="D39" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -5516,7 +5522,7 @@
         <v>108</v>
       </c>
       <c r="D40" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -5530,7 +5536,7 @@
         <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5544,7 +5550,7 @@
         <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -5558,7 +5564,7 @@
         <v>111</v>
       </c>
       <c r="D43" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -5572,7 +5578,7 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -5586,7 +5592,7 @@
         <v>113</v>
       </c>
       <c r="D45" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -5600,7 +5606,7 @@
         <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5614,7 +5620,7 @@
         <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -5628,7 +5634,7 @@
         <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -5642,7 +5648,7 @@
         <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -5656,7 +5662,7 @@
         <v>118</v>
       </c>
       <c r="D50" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -5670,7 +5676,7 @@
         <v>119</v>
       </c>
       <c r="D51" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -5684,7 +5690,7 @@
         <v>120</v>
       </c>
       <c r="D52" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -5698,7 +5704,7 @@
         <v>121</v>
       </c>
       <c r="D53" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -5712,7 +5718,7 @@
         <v>122</v>
       </c>
       <c r="D54" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -5726,7 +5732,7 @@
         <v>123</v>
       </c>
       <c r="D55" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -5740,7 +5746,7 @@
         <v>124</v>
       </c>
       <c r="D56" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -5754,7 +5760,7 @@
         <v>125</v>
       </c>
       <c r="D57" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -5768,7 +5774,7 @@
         <v>126</v>
       </c>
       <c r="D58" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -5782,7 +5788,7 @@
         <v>127</v>
       </c>
       <c r="D59" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -5796,7 +5802,7 @@
         <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -5810,7 +5816,7 @@
         <v>129</v>
       </c>
       <c r="D61" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -5824,7 +5830,7 @@
         <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -5838,7 +5844,7 @@
         <v>131</v>
       </c>
       <c r="D63" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -5852,7 +5858,7 @@
         <v>132</v>
       </c>
       <c r="D64" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -5866,7 +5872,7 @@
         <v>133</v>
       </c>
       <c r="D65" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -5880,7 +5886,7 @@
         <v>134</v>
       </c>
       <c r="D66" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -5894,7 +5900,7 @@
         <v>135</v>
       </c>
       <c r="D67" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -5908,7 +5914,7 @@
         <v>136</v>
       </c>
       <c r="D68" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -5922,7 +5928,7 @@
         <v>137</v>
       </c>
       <c r="D69" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -5936,7 +5942,7 @@
         <v>138</v>
       </c>
       <c r="D70" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -5950,7 +5956,7 @@
         <v>139</v>
       </c>
       <c r="D71" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -5964,7 +5970,7 @@
         <v>140</v>
       </c>
       <c r="D72" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -5978,7 +5984,7 @@
         <v>141</v>
       </c>
       <c r="D73" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -5992,7 +5998,7 @@
         <v>142</v>
       </c>
       <c r="D74" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -6006,7 +6012,7 @@
         <v>143</v>
       </c>
       <c r="D75" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -6020,7 +6026,7 @@
         <v>144</v>
       </c>
       <c r="D76" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -6034,7 +6040,7 @@
         <v>145</v>
       </c>
       <c r="D77" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -6048,7 +6054,7 @@
         <v>146</v>
       </c>
       <c r="D78" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -6062,7 +6068,7 @@
         <v>147</v>
       </c>
       <c r="D79" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -6076,7 +6082,7 @@
         <v>148</v>
       </c>
       <c r="D80" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -6090,7 +6096,7 @@
         <v>149</v>
       </c>
       <c r="D81" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -6104,7 +6110,7 @@
         <v>150</v>
       </c>
       <c r="D82" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -6118,7 +6124,7 @@
         <v>151</v>
       </c>
       <c r="D83" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -6132,7 +6138,7 @@
         <v>152</v>
       </c>
       <c r="D84" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -6146,7 +6152,7 @@
         <v>153</v>
       </c>
       <c r="D85" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -6160,7 +6166,7 @@
         <v>154</v>
       </c>
       <c r="D86" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -6174,7 +6180,7 @@
         <v>155</v>
       </c>
       <c r="D87" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -6188,7 +6194,7 @@
         <v>156</v>
       </c>
       <c r="D88" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -6202,7 +6208,7 @@
         <v>157</v>
       </c>
       <c r="D89" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -6216,7 +6222,7 @@
         <v>158</v>
       </c>
       <c r="D90" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -6230,7 +6236,7 @@
         <v>159</v>
       </c>
       <c r="D91" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -6244,7 +6250,7 @@
         <v>160</v>
       </c>
       <c r="D92" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -6258,7 +6264,7 @@
         <v>161</v>
       </c>
       <c r="D93" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -6272,7 +6278,7 @@
         <v>162</v>
       </c>
       <c r="D94" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -6286,7 +6292,7 @@
         <v>163</v>
       </c>
       <c r="D95" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6300,7 +6306,7 @@
         <v>164</v>
       </c>
       <c r="D96" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -6314,7 +6320,7 @@
         <v>165</v>
       </c>
       <c r="D97" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -6328,7 +6334,7 @@
         <v>166</v>
       </c>
       <c r="D98" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -6342,7 +6348,7 @@
         <v>167</v>
       </c>
       <c r="D99" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -6356,7 +6362,7 @@
         <v>168</v>
       </c>
       <c r="D100" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -6370,7 +6376,7 @@
         <v>169</v>
       </c>
       <c r="D101" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -6384,7 +6390,7 @@
         <v>170</v>
       </c>
       <c r="D102" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -6398,7 +6404,7 @@
         <v>171</v>
       </c>
       <c r="D103" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -6412,7 +6418,7 @@
         <v>172</v>
       </c>
       <c r="D104" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -6426,7 +6432,7 @@
         <v>173</v>
       </c>
       <c r="D105" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -6440,7 +6446,7 @@
         <v>174</v>
       </c>
       <c r="D106" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -6454,7 +6460,7 @@
         <v>175</v>
       </c>
       <c r="D107" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -6468,7 +6474,7 @@
         <v>176</v>
       </c>
       <c r="D108" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -6482,7 +6488,7 @@
         <v>177</v>
       </c>
       <c r="D109" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -6496,7 +6502,7 @@
         <v>178</v>
       </c>
       <c r="D110" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -6510,7 +6516,7 @@
         <v>179</v>
       </c>
       <c r="D111" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -6524,7 +6530,7 @@
         <v>180</v>
       </c>
       <c r="D112" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -6538,7 +6544,7 @@
         <v>181</v>
       </c>
       <c r="D113" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -6552,7 +6558,7 @@
         <v>182</v>
       </c>
       <c r="D114" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -6566,7 +6572,7 @@
         <v>183</v>
       </c>
       <c r="D115" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -6580,7 +6586,7 @@
         <v>184</v>
       </c>
       <c r="D116" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -6594,7 +6600,7 @@
         <v>185</v>
       </c>
       <c r="D117" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -6608,7 +6614,7 @@
         <v>186</v>
       </c>
       <c r="D118" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -6622,7 +6628,7 @@
         <v>187</v>
       </c>
       <c r="D119" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6636,7 +6642,7 @@
         <v>188</v>
       </c>
       <c r="D120" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -6650,7 +6656,7 @@
         <v>189</v>
       </c>
       <c r="D121" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -6664,7 +6670,7 @@
         <v>190</v>
       </c>
       <c r="D122" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -6678,7 +6684,7 @@
         <v>191</v>
       </c>
       <c r="D123" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -6692,7 +6698,7 @@
         <v>192</v>
       </c>
       <c r="D124" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -6706,7 +6712,7 @@
         <v>193</v>
       </c>
       <c r="D125" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -6720,7 +6726,7 @@
         <v>194</v>
       </c>
       <c r="D126" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -6734,7 +6740,7 @@
         <v>195</v>
       </c>
       <c r="D127" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -6748,7 +6754,7 @@
         <v>196</v>
       </c>
       <c r="D128" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -6762,7 +6768,7 @@
         <v>197</v>
       </c>
       <c r="D129" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -6776,7 +6782,7 @@
         <v>198</v>
       </c>
       <c r="D130" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -6790,7 +6796,7 @@
         <v>199</v>
       </c>
       <c r="D131" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -6804,7 +6810,7 @@
         <v>200</v>
       </c>
       <c r="D132" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -6818,7 +6824,7 @@
         <v>201</v>
       </c>
       <c r="D133" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -6832,7 +6838,7 @@
         <v>202</v>
       </c>
       <c r="D134" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -6846,7 +6852,7 @@
         <v>203</v>
       </c>
       <c r="D135" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -6860,7 +6866,7 @@
         <v>204</v>
       </c>
       <c r="D136" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -6874,7 +6880,7 @@
         <v>205</v>
       </c>
       <c r="D137" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -6888,7 +6894,7 @@
         <v>206</v>
       </c>
       <c r="D138" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -6902,7 +6908,7 @@
         <v>207</v>
       </c>
       <c r="D139" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -6916,7 +6922,7 @@
         <v>208</v>
       </c>
       <c r="D140" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -6930,7 +6936,7 @@
         <v>209</v>
       </c>
       <c r="D141" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -6944,7 +6950,7 @@
         <v>210</v>
       </c>
       <c r="D142" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -6958,7 +6964,7 @@
         <v>211</v>
       </c>
       <c r="D143" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -6972,7 +6978,7 @@
         <v>212</v>
       </c>
       <c r="D144" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -6986,7 +6992,7 @@
         <v>213</v>
       </c>
       <c r="D145" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -7000,7 +7006,7 @@
         <v>214</v>
       </c>
       <c r="D146" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -7014,7 +7020,7 @@
         <v>215</v>
       </c>
       <c r="D147" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -7028,7 +7034,7 @@
         <v>216</v>
       </c>
       <c r="D148" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -7042,7 +7048,7 @@
         <v>217</v>
       </c>
       <c r="D149" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -7056,7 +7062,7 @@
         <v>218</v>
       </c>
       <c r="D150" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -7070,7 +7076,7 @@
         <v>219</v>
       </c>
       <c r="D151" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -7084,7 +7090,7 @@
         <v>220</v>
       </c>
       <c r="D152" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -7098,7 +7104,7 @@
         <v>221</v>
       </c>
       <c r="D153" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -7112,7 +7118,7 @@
         <v>222</v>
       </c>
       <c r="D154" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -7126,7 +7132,7 @@
         <v>223</v>
       </c>
       <c r="D155" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -7140,7 +7146,7 @@
         <v>224</v>
       </c>
       <c r="D156" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -7154,7 +7160,7 @@
         <v>225</v>
       </c>
       <c r="D157" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -7168,7 +7174,7 @@
         <v>226</v>
       </c>
       <c r="D158" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -7182,7 +7188,7 @@
         <v>227</v>
       </c>
       <c r="D159" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -7196,7 +7202,7 @@
         <v>228</v>
       </c>
       <c r="D160" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -7210,7 +7216,7 @@
         <v>229</v>
       </c>
       <c r="D161" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -7224,7 +7230,7 @@
         <v>230</v>
       </c>
       <c r="D162" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -7238,7 +7244,7 @@
         <v>231</v>
       </c>
       <c r="D163" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -7252,7 +7258,7 @@
         <v>232</v>
       </c>
       <c r="D164" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -7266,7 +7272,7 @@
         <v>233</v>
       </c>
       <c r="D165" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -7280,7 +7286,7 @@
         <v>234</v>
       </c>
       <c r="D166" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -7294,7 +7300,7 @@
         <v>235</v>
       </c>
       <c r="D167" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -7308,7 +7314,7 @@
         <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -7322,7 +7328,7 @@
         <v>237</v>
       </c>
       <c r="D169" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -7336,7 +7342,7 @@
         <v>238</v>
       </c>
       <c r="D170" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -7350,7 +7356,7 @@
         <v>239</v>
       </c>
       <c r="D171" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -7364,7 +7370,7 @@
         <v>240</v>
       </c>
       <c r="D172" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -7378,7 +7384,7 @@
         <v>241</v>
       </c>
       <c r="D173" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -7392,7 +7398,7 @@
         <v>242</v>
       </c>
       <c r="D174" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -7406,7 +7412,7 @@
         <v>243</v>
       </c>
       <c r="D175" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -7420,7 +7426,7 @@
         <v>244</v>
       </c>
       <c r="D176" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -7434,7 +7440,7 @@
         <v>245</v>
       </c>
       <c r="D177" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -7448,7 +7454,7 @@
         <v>246</v>
       </c>
       <c r="D178" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -7462,7 +7468,7 @@
         <v>247</v>
       </c>
       <c r="D179" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -7476,7 +7482,7 @@
         <v>248</v>
       </c>
       <c r="D180" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -7490,7 +7496,7 @@
         <v>249</v>
       </c>
       <c r="D181" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -7504,7 +7510,7 @@
         <v>250</v>
       </c>
       <c r="D182" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -7518,7 +7524,7 @@
         <v>251</v>
       </c>
       <c r="D183" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -7532,7 +7538,7 @@
         <v>252</v>
       </c>
       <c r="D184" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -7546,7 +7552,7 @@
         <v>253</v>
       </c>
       <c r="D185" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -7560,7 +7566,7 @@
         <v>254</v>
       </c>
       <c r="D186" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -7574,7 +7580,7 @@
         <v>255</v>
       </c>
       <c r="D187" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -7588,7 +7594,7 @@
         <v>256</v>
       </c>
       <c r="D188" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -7602,7 +7608,7 @@
         <v>257</v>
       </c>
       <c r="D189" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -7616,7 +7622,7 @@
         <v>258</v>
       </c>
       <c r="D190" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -7630,7 +7636,7 @@
         <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -7644,7 +7650,7 @@
         <v>260</v>
       </c>
       <c r="D192" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -7658,7 +7664,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -7672,7 +7678,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -7686,7 +7692,7 @@
         <v>263</v>
       </c>
       <c r="D195" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -7700,7 +7706,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -7714,7 +7720,7 @@
         <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -7728,7 +7734,7 @@
         <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -7742,7 +7748,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -7756,7 +7762,7 @@
         <v>268</v>
       </c>
       <c r="D200" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -7770,7 +7776,7 @@
         <v>269</v>
       </c>
       <c r="D201" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -7784,7 +7790,7 @@
         <v>270</v>
       </c>
       <c r="D202" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -7798,7 +7804,7 @@
         <v>271</v>
       </c>
       <c r="D203" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -7812,7 +7818,7 @@
         <v>272</v>
       </c>
       <c r="D204" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -7826,7 +7832,7 @@
         <v>273</v>
       </c>
       <c r="D205" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -7840,7 +7846,7 @@
         <v>274</v>
       </c>
       <c r="D206" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -7854,7 +7860,7 @@
         <v>275</v>
       </c>
       <c r="D207" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -7868,7 +7874,7 @@
         <v>276</v>
       </c>
       <c r="D208" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -7882,7 +7888,7 @@
         <v>277</v>
       </c>
       <c r="D209" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -7896,7 +7902,7 @@
         <v>278</v>
       </c>
       <c r="D210" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -7910,7 +7916,7 @@
         <v>279</v>
       </c>
       <c r="D211" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -7924,7 +7930,7 @@
         <v>280</v>
       </c>
       <c r="D212" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -7938,7 +7944,7 @@
         <v>281</v>
       </c>
       <c r="D213" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -7952,7 +7958,7 @@
         <v>282</v>
       </c>
       <c r="D214" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -7966,7 +7972,7 @@
         <v>283</v>
       </c>
       <c r="D215" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -7980,7 +7986,7 @@
         <v>284</v>
       </c>
       <c r="D216" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -7994,7 +8000,7 @@
         <v>285</v>
       </c>
       <c r="D217" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -8008,7 +8014,7 @@
         <v>286</v>
       </c>
       <c r="D218" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -8022,7 +8028,7 @@
         <v>287</v>
       </c>
       <c r="D219" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -8036,7 +8042,7 @@
         <v>288</v>
       </c>
       <c r="D220" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -8050,7 +8056,7 @@
         <v>289</v>
       </c>
       <c r="D221" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -8064,7 +8070,7 @@
         <v>290</v>
       </c>
       <c r="D222" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -8078,7 +8084,7 @@
         <v>291</v>
       </c>
       <c r="D223" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -8092,7 +8098,7 @@
         <v>292</v>
       </c>
       <c r="D224" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -8106,7 +8112,7 @@
         <v>293</v>
       </c>
       <c r="D225" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -8120,7 +8126,7 @@
         <v>294</v>
       </c>
       <c r="D226" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -8134,7 +8140,7 @@
         <v>295</v>
       </c>
       <c r="D227" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -8148,7 +8154,7 @@
         <v>296</v>
       </c>
       <c r="D228" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -8162,7 +8168,7 @@
         <v>297</v>
       </c>
       <c r="D229" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -8176,7 +8182,7 @@
         <v>298</v>
       </c>
       <c r="D230" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -8190,7 +8196,7 @@
         <v>299</v>
       </c>
       <c r="D231" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -8204,7 +8210,7 @@
         <v>300</v>
       </c>
       <c r="D232" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -8218,7 +8224,7 @@
         <v>301</v>
       </c>
       <c r="D233" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -8232,7 +8238,7 @@
         <v>302</v>
       </c>
       <c r="D234" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -8246,7 +8252,7 @@
         <v>303</v>
       </c>
       <c r="D235" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -8260,7 +8266,7 @@
         <v>304</v>
       </c>
       <c r="D236" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -8274,7 +8280,7 @@
         <v>305</v>
       </c>
       <c r="D237" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -8288,7 +8294,7 @@
         <v>306</v>
       </c>
       <c r="D238" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -8302,7 +8308,7 @@
         <v>307</v>
       </c>
       <c r="D239" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -8316,7 +8322,7 @@
         <v>308</v>
       </c>
       <c r="D240" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -8330,7 +8336,7 @@
         <v>309</v>
       </c>
       <c r="D241" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -8344,7 +8350,7 @@
         <v>310</v>
       </c>
       <c r="D242" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -8358,7 +8364,7 @@
         <v>311</v>
       </c>
       <c r="D243" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -8372,7 +8378,7 @@
         <v>312</v>
       </c>
       <c r="D244" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -8386,7 +8392,7 @@
         <v>313</v>
       </c>
       <c r="D245" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -8400,7 +8406,7 @@
         <v>314</v>
       </c>
       <c r="D246" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -8414,7 +8420,7 @@
         <v>315</v>
       </c>
       <c r="D247" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -8428,7 +8434,7 @@
         <v>316</v>
       </c>
       <c r="D248" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -8442,7 +8448,7 @@
         <v>317</v>
       </c>
       <c r="D249" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -8456,7 +8462,7 @@
         <v>318</v>
       </c>
       <c r="D250" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -8470,7 +8476,7 @@
         <v>319</v>
       </c>
       <c r="D251" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -8484,7 +8490,7 @@
         <v>320</v>
       </c>
       <c r="D252" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -8498,7 +8504,7 @@
         <v>321</v>
       </c>
       <c r="D253" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -8512,7 +8518,7 @@
         <v>322</v>
       </c>
       <c r="D254" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -8526,7 +8532,7 @@
         <v>323</v>
       </c>
       <c r="D255" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -8540,7 +8546,7 @@
         <v>324</v>
       </c>
       <c r="D256" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -8554,7 +8560,7 @@
         <v>325</v>
       </c>
       <c r="D257" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -8568,7 +8574,7 @@
         <v>326</v>
       </c>
       <c r="D258" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -8582,7 +8588,7 @@
         <v>327</v>
       </c>
       <c r="D259" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -8596,7 +8602,7 @@
         <v>328</v>
       </c>
       <c r="D260" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -8610,7 +8616,7 @@
         <v>329</v>
       </c>
       <c r="D261" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -8624,7 +8630,7 @@
         <v>330</v>
       </c>
       <c r="D262" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -8638,7 +8644,7 @@
         <v>331</v>
       </c>
       <c r="D263" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -8652,7 +8658,7 @@
         <v>332</v>
       </c>
       <c r="D264" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -8666,7 +8672,7 @@
         <v>333</v>
       </c>
       <c r="D265" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -8680,7 +8686,7 @@
         <v>334</v>
       </c>
       <c r="D266" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -8705,7 +8711,7 @@
         <v>336</v>
       </c>
       <c r="D268" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -8719,7 +8725,7 @@
         <v>337</v>
       </c>
       <c r="D269" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -8733,7 +8739,7 @@
         <v>338</v>
       </c>
       <c r="D270" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -8747,7 +8753,7 @@
         <v>339</v>
       </c>
       <c r="D271" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -8761,7 +8767,7 @@
         <v>340</v>
       </c>
       <c r="D272" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -8775,7 +8781,7 @@
         <v>341</v>
       </c>
       <c r="D273" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -8789,7 +8795,7 @@
         <v>342</v>
       </c>
       <c r="D274" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -8803,7 +8809,7 @@
         <v>343</v>
       </c>
       <c r="D275" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -8817,7 +8823,7 @@
         <v>344</v>
       </c>
       <c r="D276" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -8831,7 +8837,7 @@
         <v>345</v>
       </c>
       <c r="D277" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -8845,7 +8851,7 @@
         <v>346</v>
       </c>
       <c r="D278" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -8859,7 +8865,7 @@
         <v>347</v>
       </c>
       <c r="D279" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -8873,7 +8879,7 @@
         <v>348</v>
       </c>
       <c r="D280" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -8887,7 +8893,7 @@
         <v>349</v>
       </c>
       <c r="D281" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -8901,7 +8907,7 @@
         <v>350</v>
       </c>
       <c r="D282" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -8915,7 +8921,7 @@
         <v>351</v>
       </c>
       <c r="D283" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -8929,7 +8935,7 @@
         <v>352</v>
       </c>
       <c r="D284" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -8943,7 +8949,7 @@
         <v>353</v>
       </c>
       <c r="D285" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -8957,7 +8963,7 @@
         <v>354</v>
       </c>
       <c r="D286" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -8971,7 +8977,7 @@
         <v>355</v>
       </c>
       <c r="D287" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -8985,7 +8991,7 @@
         <v>356</v>
       </c>
       <c r="D288" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -8999,7 +9005,7 @@
         <v>357</v>
       </c>
       <c r="D289" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -9013,7 +9019,7 @@
         <v>358</v>
       </c>
       <c r="D290" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -9027,7 +9033,7 @@
         <v>359</v>
       </c>
       <c r="D291" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -9041,7 +9047,7 @@
         <v>360</v>
       </c>
       <c r="D292" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -9055,7 +9061,7 @@
         <v>361</v>
       </c>
       <c r="D293" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -9069,7 +9075,7 @@
         <v>362</v>
       </c>
       <c r="D294" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -9083,7 +9089,7 @@
         <v>363</v>
       </c>
       <c r="D295" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -9097,7 +9103,7 @@
         <v>364</v>
       </c>
       <c r="D296" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -9111,7 +9117,7 @@
         <v>365</v>
       </c>
       <c r="D297" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -9125,7 +9131,7 @@
         <v>366</v>
       </c>
       <c r="D298" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -9139,7 +9145,7 @@
         <v>367</v>
       </c>
       <c r="D299" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -9153,7 +9159,7 @@
         <v>368</v>
       </c>
       <c r="D300" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -9167,7 +9173,7 @@
         <v>369</v>
       </c>
       <c r="D301" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -9181,7 +9187,7 @@
         <v>370</v>
       </c>
       <c r="D302" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -9195,7 +9201,7 @@
         <v>371</v>
       </c>
       <c r="D303" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -9209,7 +9215,7 @@
         <v>372</v>
       </c>
       <c r="D304" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -9223,7 +9229,7 @@
         <v>373</v>
       </c>
       <c r="D305" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -9237,7 +9243,7 @@
         <v>374</v>
       </c>
       <c r="D306" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -9251,7 +9257,7 @@
         <v>375</v>
       </c>
       <c r="D307" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -9265,7 +9271,7 @@
         <v>376</v>
       </c>
       <c r="D308" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -9279,7 +9285,7 @@
         <v>377</v>
       </c>
       <c r="D309" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -9304,7 +9310,7 @@
         <v>26</v>
       </c>
       <c r="D311" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -9318,7 +9324,7 @@
         <v>378</v>
       </c>
       <c r="D312" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -9332,7 +9338,7 @@
         <v>379</v>
       </c>
       <c r="D313" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -9346,7 +9352,7 @@
         <v>380</v>
       </c>
       <c r="D314" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -9360,7 +9366,7 @@
         <v>381</v>
       </c>
       <c r="D315" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -9374,7 +9380,7 @@
         <v>382</v>
       </c>
       <c r="D316" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -9388,7 +9394,7 @@
         <v>383</v>
       </c>
       <c r="D317" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -9402,7 +9408,7 @@
         <v>384</v>
       </c>
       <c r="D318" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -9416,7 +9422,7 @@
         <v>385</v>
       </c>
       <c r="D319" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -9430,7 +9436,7 @@
         <v>386</v>
       </c>
       <c r="D320" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -9444,7 +9450,7 @@
         <v>387</v>
       </c>
       <c r="D321" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -9458,7 +9464,7 @@
         <v>388</v>
       </c>
       <c r="D322" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -9472,7 +9478,7 @@
         <v>389</v>
       </c>
       <c r="D323" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -9486,7 +9492,7 @@
         <v>390</v>
       </c>
       <c r="D324" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -9500,7 +9506,7 @@
         <v>391</v>
       </c>
       <c r="D325" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -9514,7 +9520,7 @@
         <v>392</v>
       </c>
       <c r="D326" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -9528,7 +9534,7 @@
         <v>393</v>
       </c>
       <c r="D327" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -9542,7 +9548,7 @@
         <v>394</v>
       </c>
       <c r="D328" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -9556,7 +9562,7 @@
         <v>395</v>
       </c>
       <c r="D329" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -9570,7 +9576,7 @@
         <v>396</v>
       </c>
       <c r="D330" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -9584,7 +9590,7 @@
         <v>397</v>
       </c>
       <c r="D331" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -9609,7 +9615,7 @@
         <v>398</v>
       </c>
       <c r="D333" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -9623,7 +9629,7 @@
         <v>399</v>
       </c>
       <c r="D334" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -9637,7 +9643,7 @@
         <v>400</v>
       </c>
       <c r="D335" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -9651,7 +9657,7 @@
         <v>401</v>
       </c>
       <c r="D336" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -9665,7 +9671,7 @@
         <v>402</v>
       </c>
       <c r="D337" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -9679,7 +9685,7 @@
         <v>403</v>
       </c>
       <c r="D338" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -9693,7 +9699,7 @@
         <v>404</v>
       </c>
       <c r="D339" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -9707,7 +9713,7 @@
         <v>405</v>
       </c>
       <c r="D340" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -9721,7 +9727,7 @@
         <v>406</v>
       </c>
       <c r="D341" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -9735,7 +9741,7 @@
         <v>407</v>
       </c>
       <c r="D342" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -9760,7 +9766,7 @@
         <v>408</v>
       </c>
       <c r="D344" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -9774,7 +9780,7 @@
         <v>409</v>
       </c>
       <c r="D345" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -9788,7 +9794,7 @@
         <v>410</v>
       </c>
       <c r="D346" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -9802,7 +9808,7 @@
         <v>411</v>
       </c>
       <c r="D347" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -9849,7 +9855,7 @@
         <v>415</v>
       </c>
       <c r="D351" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -9885,7 +9891,7 @@
         <v>417</v>
       </c>
       <c r="D354" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -9899,7 +9905,7 @@
         <v>418</v>
       </c>
       <c r="D355" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -9913,7 +9919,7 @@
         <v>419</v>
       </c>
       <c r="D356" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -9927,7 +9933,7 @@
         <v>420</v>
       </c>
       <c r="D357" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -9941,7 +9947,7 @@
         <v>421</v>
       </c>
       <c r="D358" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -9955,7 +9961,7 @@
         <v>422</v>
       </c>
       <c r="D359" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -9969,7 +9975,7 @@
         <v>423</v>
       </c>
       <c r="D360" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -9983,7 +9989,7 @@
         <v>424</v>
       </c>
       <c r="D361" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -9997,7 +10003,7 @@
         <v>425</v>
       </c>
       <c r="D362" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -10033,7 +10039,7 @@
         <v>426</v>
       </c>
       <c r="D365" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -10047,7 +10053,7 @@
         <v>427</v>
       </c>
       <c r="D366" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -10061,7 +10067,7 @@
         <v>428</v>
       </c>
       <c r="D367" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -10086,7 +10092,7 @@
         <v>429</v>
       </c>
       <c r="D369" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -10100,7 +10106,7 @@
         <v>430</v>
       </c>
       <c r="D370" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -10114,7 +10120,7 @@
         <v>431</v>
       </c>
       <c r="D371" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -10128,7 +10134,7 @@
         <v>432</v>
       </c>
       <c r="D372" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -10142,7 +10148,7 @@
         <v>433</v>
       </c>
       <c r="D373" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -10156,7 +10162,7 @@
         <v>61</v>
       </c>
       <c r="D374" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -10170,7 +10176,7 @@
         <v>434</v>
       </c>
       <c r="D375" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -10184,7 +10190,7 @@
         <v>435</v>
       </c>
       <c r="D376" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -10198,7 +10204,7 @@
         <v>436</v>
       </c>
       <c r="D377" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -10223,7 +10229,7 @@
         <v>438</v>
       </c>
       <c r="D379" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -10259,7 +10265,7 @@
         <v>408</v>
       </c>
       <c r="D382" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -10273,7 +10279,7 @@
         <v>409</v>
       </c>
       <c r="D383" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -10287,7 +10293,7 @@
         <v>410</v>
       </c>
       <c r="D384" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -10301,7 +10307,7 @@
         <v>411</v>
       </c>
       <c r="D385" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -10348,7 +10354,7 @@
         <v>415</v>
       </c>
       <c r="D389" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -10384,7 +10390,7 @@
         <v>440</v>
       </c>
       <c r="D392" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -10398,7 +10404,7 @@
         <v>441</v>
       </c>
       <c r="D393" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -10412,7 +10418,7 @@
         <v>442</v>
       </c>
       <c r="D394" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -10426,7 +10432,7 @@
         <v>443</v>
       </c>
       <c r="D395" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -10440,7 +10446,7 @@
         <v>444</v>
       </c>
       <c r="D396" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -10454,7 +10460,7 @@
         <v>445</v>
       </c>
       <c r="D397" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -10479,7 +10485,7 @@
         <v>447</v>
       </c>
       <c r="D399" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -10504,7 +10510,7 @@
         <v>448</v>
       </c>
       <c r="D401" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -10518,7 +10524,7 @@
         <v>449</v>
       </c>
       <c r="D402" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -10532,7 +10538,7 @@
         <v>450</v>
       </c>
       <c r="D403" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -10546,7 +10552,7 @@
         <v>451</v>
       </c>
       <c r="D404" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -10560,7 +10566,7 @@
         <v>452</v>
       </c>
       <c r="D405" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -10574,7 +10580,7 @@
         <v>453</v>
       </c>
       <c r="D406" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -10588,7 +10594,7 @@
         <v>454</v>
       </c>
       <c r="D407" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -10602,7 +10608,7 @@
         <v>455</v>
       </c>
       <c r="D408" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -10616,7 +10622,7 @@
         <v>456</v>
       </c>
       <c r="D409" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -10630,7 +10636,7 @@
         <v>457</v>
       </c>
       <c r="D410" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -10787,7 +10793,7 @@
         <v>471</v>
       </c>
       <c r="D424" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -10801,7 +10807,7 @@
         <v>472</v>
       </c>
       <c r="D425" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -10958,7 +10964,7 @@
         <v>451</v>
       </c>
       <c r="D439" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -11016,7 +11022,7 @@
         <v>478</v>
       </c>
       <c r="D444" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -11030,7 +11036,7 @@
         <v>479</v>
       </c>
       <c r="D445" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -11055,7 +11061,7 @@
         <v>449</v>
       </c>
       <c r="D447" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -11091,7 +11097,7 @@
         <v>457</v>
       </c>
       <c r="D450" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -11116,7 +11122,7 @@
         <v>480</v>
       </c>
       <c r="D452" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -11130,7 +11136,7 @@
         <v>448</v>
       </c>
       <c r="D453" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -11166,7 +11172,7 @@
         <v>481</v>
       </c>
       <c r="D456" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -11180,7 +11186,7 @@
         <v>482</v>
       </c>
       <c r="D457" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -11227,7 +11233,7 @@
         <v>450</v>
       </c>
       <c r="D461" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -11241,7 +11247,7 @@
         <v>71</v>
       </c>
       <c r="D462" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -11255,7 +11261,7 @@
         <v>483</v>
       </c>
       <c r="D463" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -11269,7 +11275,7 @@
         <v>484</v>
       </c>
       <c r="D464" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -11327,7 +11333,7 @@
         <v>489</v>
       </c>
       <c r="D469" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -11341,7 +11347,7 @@
         <v>490</v>
       </c>
       <c r="D470" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -11355,7 +11361,7 @@
         <v>491</v>
       </c>
       <c r="D471" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -11369,7 +11375,7 @@
         <v>492</v>
       </c>
       <c r="D472" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -11383,7 +11389,7 @@
         <v>493</v>
       </c>
       <c r="D473" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -11397,7 +11403,7 @@
         <v>494</v>
       </c>
       <c r="D474" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -11411,7 +11417,7 @@
         <v>404</v>
       </c>
       <c r="D475" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -11425,7 +11431,7 @@
         <v>495</v>
       </c>
       <c r="D476" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -11439,7 +11445,7 @@
         <v>496</v>
       </c>
       <c r="D477" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -11453,7 +11459,7 @@
         <v>497</v>
       </c>
       <c r="D478" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -11467,7 +11473,7 @@
         <v>498</v>
       </c>
       <c r="D479" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -11481,7 +11487,7 @@
         <v>499</v>
       </c>
       <c r="D480" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -11495,7 +11501,7 @@
         <v>500</v>
       </c>
       <c r="D481" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -11509,7 +11515,7 @@
         <v>501</v>
       </c>
       <c r="D482" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -11534,7 +11540,7 @@
         <v>502</v>
       </c>
       <c r="D484" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -11548,7 +11554,7 @@
         <v>503</v>
       </c>
       <c r="D485" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -11562,7 +11568,7 @@
         <v>504</v>
       </c>
       <c r="D486" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -11576,7 +11582,7 @@
         <v>505</v>
       </c>
       <c r="D487" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -11590,7 +11596,7 @@
         <v>404</v>
       </c>
       <c r="D488" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -11604,7 +11610,7 @@
         <v>506</v>
       </c>
       <c r="D489" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -11618,7 +11624,7 @@
         <v>507</v>
       </c>
       <c r="D490" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -11632,7 +11638,7 @@
         <v>404</v>
       </c>
       <c r="D491" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -11646,7 +11652,7 @@
         <v>508</v>
       </c>
       <c r="D492" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -11671,7 +11677,7 @@
         <v>510</v>
       </c>
       <c r="D494" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -11685,7 +11691,7 @@
         <v>511</v>
       </c>
       <c r="D495" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -11699,7 +11705,7 @@
         <v>512</v>
       </c>
       <c r="D496" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -11713,7 +11719,7 @@
         <v>513</v>
       </c>
       <c r="D497" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -11727,7 +11733,7 @@
         <v>514</v>
       </c>
       <c r="D498" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -11741,7 +11747,7 @@
         <v>515</v>
       </c>
       <c r="D499" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -11755,7 +11761,7 @@
         <v>516</v>
       </c>
       <c r="D500" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -11769,7 +11775,7 @@
         <v>404</v>
       </c>
       <c r="D501" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -11783,7 +11789,7 @@
         <v>517</v>
       </c>
       <c r="D502" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -11797,7 +11803,7 @@
         <v>518</v>
       </c>
       <c r="D503" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -11811,7 +11817,7 @@
         <v>519</v>
       </c>
       <c r="D504" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -11836,7 +11842,7 @@
         <v>46</v>
       </c>
       <c r="D506" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -11850,7 +11856,7 @@
         <v>520</v>
       </c>
       <c r="D507" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -11864,7 +11870,7 @@
         <v>521</v>
       </c>
       <c r="D508" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -11922,7 +11928,7 @@
         <v>25</v>
       </c>
       <c r="D513" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -11936,7 +11942,7 @@
         <v>526</v>
       </c>
       <c r="D514" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -11950,7 +11956,7 @@
         <v>527</v>
       </c>
       <c r="D515" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -11964,7 +11970,7 @@
         <v>528</v>
       </c>
       <c r="D516" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -11978,7 +11984,7 @@
         <v>29</v>
       </c>
       <c r="D517" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -12069,7 +12075,7 @@
         <v>535</v>
       </c>
       <c r="D525" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -12083,7 +12089,7 @@
         <v>536</v>
       </c>
       <c r="D526" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -12097,7 +12103,7 @@
         <v>537</v>
       </c>
       <c r="D527" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -12111,7 +12117,7 @@
         <v>538</v>
       </c>
       <c r="D528" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -12136,7 +12142,7 @@
         <v>540</v>
       </c>
       <c r="D530" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -12150,7 +12156,7 @@
         <v>541</v>
       </c>
       <c r="D531" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -12164,7 +12170,7 @@
         <v>542</v>
       </c>
       <c r="D532" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -12178,7 +12184,7 @@
         <v>543</v>
       </c>
       <c r="D533" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -12192,7 +12198,7 @@
         <v>544</v>
       </c>
       <c r="D534" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -12206,7 +12212,7 @@
         <v>545</v>
       </c>
       <c r="D535" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -12220,7 +12226,7 @@
         <v>546</v>
       </c>
       <c r="D536" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -12234,7 +12240,7 @@
         <v>547</v>
       </c>
       <c r="D537" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -12248,7 +12254,7 @@
         <v>404</v>
       </c>
       <c r="D538" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -12262,7 +12268,7 @@
         <v>548</v>
       </c>
       <c r="D539" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -12276,7 +12282,7 @@
         <v>549</v>
       </c>
       <c r="D540" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -12290,7 +12296,7 @@
         <v>550</v>
       </c>
       <c r="D541" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -12304,7 +12310,7 @@
         <v>53</v>
       </c>
       <c r="D542" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -12318,7 +12324,7 @@
         <v>551</v>
       </c>
       <c r="D543" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -12332,7 +12338,7 @@
         <v>552</v>
       </c>
       <c r="D544" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -12346,7 +12352,7 @@
         <v>553</v>
       </c>
       <c r="D545" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -12360,7 +12366,7 @@
         <v>554</v>
       </c>
       <c r="D546" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -12374,7 +12380,7 @@
         <v>555</v>
       </c>
       <c r="D547" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -12388,7 +12394,7 @@
         <v>556</v>
       </c>
       <c r="D548" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -12402,7 +12408,7 @@
         <v>404</v>
       </c>
       <c r="D549" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -12416,7 +12422,7 @@
         <v>547</v>
       </c>
       <c r="D550" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -12430,7 +12436,7 @@
         <v>557</v>
       </c>
       <c r="D551" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -12444,7 +12450,7 @@
         <v>23</v>
       </c>
       <c r="D552" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -12458,7 +12464,7 @@
         <v>558</v>
       </c>
       <c r="D553" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -12472,7 +12478,7 @@
         <v>559</v>
       </c>
       <c r="D554" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -12486,7 +12492,7 @@
         <v>560</v>
       </c>
       <c r="D555" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -12500,7 +12506,7 @@
         <v>561</v>
       </c>
       <c r="D556" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -12514,7 +12520,7 @@
         <v>562</v>
       </c>
       <c r="D557" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -12528,7 +12534,7 @@
         <v>404</v>
       </c>
       <c r="D558" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -12542,7 +12548,7 @@
         <v>558</v>
       </c>
       <c r="D559" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -12556,7 +12562,7 @@
         <v>559</v>
       </c>
       <c r="D560" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -12570,7 +12576,7 @@
         <v>560</v>
       </c>
       <c r="D561" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -12584,7 +12590,7 @@
         <v>561</v>
       </c>
       <c r="D562" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -12598,7 +12604,7 @@
         <v>562</v>
       </c>
       <c r="D563" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -12612,7 +12618,7 @@
         <v>404</v>
       </c>
       <c r="D564" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -12626,7 +12632,7 @@
         <v>563</v>
       </c>
       <c r="D565" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -12640,7 +12646,7 @@
         <v>564</v>
       </c>
       <c r="D566" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -12654,7 +12660,7 @@
         <v>565</v>
       </c>
       <c r="D567" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -12668,7 +12674,7 @@
         <v>566</v>
       </c>
       <c r="D568" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -12682,7 +12688,7 @@
         <v>567</v>
       </c>
       <c r="D569" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -12696,7 +12702,7 @@
         <v>568</v>
       </c>
       <c r="D570" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -12710,7 +12716,7 @@
         <v>569</v>
       </c>
       <c r="D571" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -12724,7 +12730,7 @@
         <v>570</v>
       </c>
       <c r="D572" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -12738,7 +12744,7 @@
         <v>571</v>
       </c>
       <c r="D573" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -12752,7 +12758,7 @@
         <v>572</v>
       </c>
       <c r="D574" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -12766,7 +12772,7 @@
         <v>573</v>
       </c>
       <c r="D575" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -12780,7 +12786,7 @@
         <v>574</v>
       </c>
       <c r="D576" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -12794,7 +12800,7 @@
         <v>404</v>
       </c>
       <c r="D577" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -12808,7 +12814,7 @@
         <v>575</v>
       </c>
       <c r="D578" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -12822,7 +12828,7 @@
         <v>576</v>
       </c>
       <c r="D579" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -12836,7 +12842,7 @@
         <v>577</v>
       </c>
       <c r="D580" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -12894,7 +12900,7 @@
         <v>5</v>
       </c>
       <c r="D585" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -12919,7 +12925,7 @@
         <v>34</v>
       </c>
       <c r="D587" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -12944,7 +12950,7 @@
         <v>583</v>
       </c>
       <c r="D589" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -12969,7 +12975,7 @@
         <v>3</v>
       </c>
       <c r="D591" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -12983,7 +12989,7 @@
         <v>584</v>
       </c>
       <c r="D592" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -12997,7 +13003,7 @@
         <v>585</v>
       </c>
       <c r="D593" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -13011,7 +13017,7 @@
         <v>586</v>
       </c>
       <c r="D594" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -13025,7 +13031,7 @@
         <v>587</v>
       </c>
       <c r="D595" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -13050,7 +13056,7 @@
         <v>588</v>
       </c>
       <c r="D597" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -13064,7 +13070,7 @@
         <v>589</v>
       </c>
       <c r="D598" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -13078,7 +13084,7 @@
         <v>590</v>
       </c>
       <c r="D599" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -13092,7 +13098,7 @@
         <v>591</v>
       </c>
       <c r="D600" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -13106,7 +13112,7 @@
         <v>592</v>
       </c>
       <c r="D601" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -13120,7 +13126,7 @@
         <v>404</v>
       </c>
       <c r="D602" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -13167,7 +13173,7 @@
         <v>588</v>
       </c>
       <c r="D606" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -13181,7 +13187,7 @@
         <v>589</v>
       </c>
       <c r="D607" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -13195,7 +13201,7 @@
         <v>590</v>
       </c>
       <c r="D608" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -13209,7 +13215,7 @@
         <v>591</v>
       </c>
       <c r="D609" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -13223,7 +13229,7 @@
         <v>592</v>
       </c>
       <c r="D610" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -13281,7 +13287,7 @@
         <v>404</v>
       </c>
       <c r="D615" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -13295,7 +13301,7 @@
         <v>593</v>
       </c>
       <c r="D616" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -13309,7 +13315,7 @@
         <v>594</v>
       </c>
       <c r="D617" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -13323,7 +13329,7 @@
         <v>595</v>
       </c>
       <c r="D618" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -13337,7 +13343,7 @@
         <v>596</v>
       </c>
       <c r="D619" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -13362,7 +13368,7 @@
         <v>597</v>
       </c>
       <c r="D621" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -13376,7 +13382,7 @@
         <v>598</v>
       </c>
       <c r="D622" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -13390,7 +13396,7 @@
         <v>599</v>
       </c>
       <c r="D623" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -13404,7 +13410,7 @@
         <v>600</v>
       </c>
       <c r="D624" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -13418,7 +13424,7 @@
         <v>601</v>
       </c>
       <c r="D625" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -13432,7 +13438,7 @@
         <v>602</v>
       </c>
       <c r="D626" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -13446,7 +13452,7 @@
         <v>603</v>
       </c>
       <c r="D627" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -13460,7 +13466,7 @@
         <v>604</v>
       </c>
       <c r="D628" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -13474,7 +13480,7 @@
         <v>605</v>
       </c>
       <c r="D629" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -13488,7 +13494,7 @@
         <v>606</v>
       </c>
       <c r="D630" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -13502,7 +13508,7 @@
         <v>607</v>
       </c>
       <c r="D631" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -13516,7 +13522,7 @@
         <v>608</v>
       </c>
       <c r="D632" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -13530,7 +13536,7 @@
         <v>609</v>
       </c>
       <c r="D633" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -13544,7 +13550,7 @@
         <v>610</v>
       </c>
       <c r="D634" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -13558,7 +13564,7 @@
         <v>611</v>
       </c>
       <c r="D635" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -13583,7 +13589,7 @@
         <v>612</v>
       </c>
       <c r="D637" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -13597,7 +13603,7 @@
         <v>613</v>
       </c>
       <c r="D638" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -13611,7 +13617,7 @@
         <v>11</v>
       </c>
       <c r="D639" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -13625,7 +13631,7 @@
         <v>614</v>
       </c>
       <c r="D640" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -13639,7 +13645,7 @@
         <v>615</v>
       </c>
       <c r="D641" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -13653,7 +13659,7 @@
         <v>616</v>
       </c>
       <c r="D642" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -13667,7 +13673,7 @@
         <v>617</v>
       </c>
       <c r="D643" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -13681,7 +13687,7 @@
         <v>618</v>
       </c>
       <c r="D644" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -13717,7 +13723,7 @@
         <v>621</v>
       </c>
       <c r="D647" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -13731,7 +13737,7 @@
         <v>622</v>
       </c>
       <c r="D648" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -13745,7 +13751,7 @@
         <v>623</v>
       </c>
       <c r="D649" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="650" spans="1:4">
@@ -13770,7 +13776,7 @@
         <v>624</v>
       </c>
       <c r="D651" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -13784,7 +13790,7 @@
         <v>625</v>
       </c>
       <c r="D652" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -13798,7 +13804,7 @@
         <v>626</v>
       </c>
       <c r="D653" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -13812,7 +13818,7 @@
         <v>627</v>
       </c>
       <c r="D654" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -13826,7 +13832,7 @@
         <v>628</v>
       </c>
       <c r="D655" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -13840,7 +13846,7 @@
         <v>629</v>
       </c>
       <c r="D656" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="657" spans="1:4">
@@ -13854,7 +13860,7 @@
         <v>630</v>
       </c>
       <c r="D657" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -13868,7 +13874,7 @@
         <v>631</v>
       </c>
       <c r="D658" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="659" spans="1:4">
@@ -13882,7 +13888,7 @@
         <v>632</v>
       </c>
       <c r="D659" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="660" spans="1:4">
@@ -13896,7 +13902,7 @@
         <v>633</v>
       </c>
       <c r="D660" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="661" spans="1:4">
@@ -13910,7 +13916,7 @@
         <v>634</v>
       </c>
       <c r="D661" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="662" spans="1:4">
@@ -13924,7 +13930,7 @@
         <v>404</v>
       </c>
       <c r="D662" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="663" spans="1:4">
@@ -13938,7 +13944,7 @@
         <v>29</v>
       </c>
       <c r="D663" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="664" spans="1:4">
@@ -14029,7 +14035,7 @@
         <v>46</v>
       </c>
       <c r="D671" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="672" spans="1:4">
@@ -14043,7 +14049,7 @@
         <v>520</v>
       </c>
       <c r="D672" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="673" spans="1:4">
@@ -14057,7 +14063,7 @@
         <v>521</v>
       </c>
       <c r="D673" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="674" spans="1:4">
@@ -14115,7 +14121,7 @@
         <v>25</v>
       </c>
       <c r="D678" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -14129,7 +14135,7 @@
         <v>526</v>
       </c>
       <c r="D679" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -14143,7 +14149,7 @@
         <v>527</v>
       </c>
       <c r="D680" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -14157,7 +14163,7 @@
         <v>528</v>
       </c>
       <c r="D681" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -14171,7 +14177,7 @@
         <v>15</v>
       </c>
       <c r="D682" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -14185,7 +14191,7 @@
         <v>495</v>
       </c>
       <c r="D683" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="684" spans="1:4">
@@ -14199,7 +14205,7 @@
         <v>496</v>
       </c>
       <c r="D684" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="685" spans="1:4">
@@ -14213,7 +14219,7 @@
         <v>497</v>
       </c>
       <c r="D685" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -14227,7 +14233,7 @@
         <v>498</v>
       </c>
       <c r="D686" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -14241,7 +14247,7 @@
         <v>499</v>
       </c>
       <c r="D687" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="688" spans="1:4">
@@ -14255,7 +14261,7 @@
         <v>500</v>
       </c>
       <c r="D688" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -14269,7 +14275,7 @@
         <v>501</v>
       </c>
       <c r="D689" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="690" spans="1:4">
@@ -14283,7 +14289,7 @@
         <v>17</v>
       </c>
       <c r="D690" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="691" spans="1:4">
@@ -14297,7 +14303,7 @@
         <v>506</v>
       </c>
       <c r="D691" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="692" spans="1:4">
@@ -14311,7 +14317,7 @@
         <v>507</v>
       </c>
       <c r="D692" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -14336,7 +14342,7 @@
         <v>502</v>
       </c>
       <c r="D694" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="695" spans="1:4">
@@ -14350,7 +14356,7 @@
         <v>503</v>
       </c>
       <c r="D695" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -14364,7 +14370,7 @@
         <v>504</v>
       </c>
       <c r="D696" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="697" spans="1:4">
@@ -14378,7 +14384,7 @@
         <v>505</v>
       </c>
       <c r="D697" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="698" spans="1:4">
@@ -14392,7 +14398,7 @@
         <v>21</v>
       </c>
       <c r="D698" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="699" spans="1:4">
@@ -14406,7 +14412,7 @@
         <v>547</v>
       </c>
       <c r="D699" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -14420,7 +14426,7 @@
         <v>548</v>
       </c>
       <c r="D700" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -14434,7 +14440,7 @@
         <v>549</v>
       </c>
       <c r="D701" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="702" spans="1:4">
@@ -14448,7 +14454,7 @@
         <v>550</v>
       </c>
       <c r="D702" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -14462,7 +14468,7 @@
         <v>53</v>
       </c>
       <c r="D703" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="704" spans="1:4">
@@ -14476,7 +14482,7 @@
         <v>22</v>
       </c>
       <c r="D704" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -14490,7 +14496,7 @@
         <v>547</v>
       </c>
       <c r="D705" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -14504,7 +14510,7 @@
         <v>557</v>
       </c>
       <c r="D706" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -14518,7 +14524,7 @@
         <v>23</v>
       </c>
       <c r="D707" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -14532,7 +14538,7 @@
         <v>24</v>
       </c>
       <c r="D708" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -14546,7 +14552,7 @@
         <v>563</v>
       </c>
       <c r="D709" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -14560,7 +14566,7 @@
         <v>564</v>
       </c>
       <c r="D710" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -14574,7 +14580,7 @@
         <v>565</v>
       </c>
       <c r="D711" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -14588,7 +14594,7 @@
         <v>566</v>
       </c>
       <c r="D712" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -14602,7 +14608,7 @@
         <v>567</v>
       </c>
       <c r="D713" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -14616,7 +14622,7 @@
         <v>568</v>
       </c>
       <c r="D714" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -14630,7 +14636,7 @@
         <v>569</v>
       </c>
       <c r="D715" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -14644,7 +14650,7 @@
         <v>570</v>
       </c>
       <c r="D716" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -14658,7 +14664,7 @@
         <v>571</v>
       </c>
       <c r="D717" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -14672,7 +14678,7 @@
         <v>572</v>
       </c>
       <c r="D718" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -14686,7 +14692,7 @@
         <v>573</v>
       </c>
       <c r="D719" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -14700,7 +14706,7 @@
         <v>574</v>
       </c>
       <c r="D720" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="721" spans="1:4">
@@ -14714,7 +14720,7 @@
         <v>40</v>
       </c>
       <c r="D721" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="722" spans="1:4">
@@ -14739,7 +14745,7 @@
         <v>636</v>
       </c>
       <c r="D723" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="724" spans="1:4">
@@ -14753,7 +14759,7 @@
         <v>637</v>
       </c>
       <c r="D724" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="725" spans="1:4">
@@ -14767,7 +14773,7 @@
         <v>638</v>
       </c>
       <c r="D725" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="726" spans="1:4">
@@ -14781,7 +14787,7 @@
         <v>639</v>
       </c>
       <c r="D726" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="727" spans="1:4">
@@ -14795,7 +14801,7 @@
         <v>640</v>
       </c>
       <c r="D727" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="728" spans="1:4">
@@ -14809,7 +14815,7 @@
         <v>641</v>
       </c>
       <c r="D728" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="729" spans="1:4">
@@ -14823,7 +14829,7 @@
         <v>642</v>
       </c>
       <c r="D729" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="730" spans="1:4">
@@ -14837,7 +14843,7 @@
         <v>643</v>
       </c>
       <c r="D730" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="731" spans="1:4">
@@ -14851,7 +14857,7 @@
         <v>644</v>
       </c>
       <c r="D731" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="732" spans="1:4">
@@ -14865,7 +14871,7 @@
         <v>645</v>
       </c>
       <c r="D732" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="733" spans="1:4">
@@ -14879,7 +14885,7 @@
         <v>646</v>
       </c>
       <c r="D733" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -14893,7 +14899,7 @@
         <v>647</v>
       </c>
       <c r="D734" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="735" spans="1:4">
@@ -14907,7 +14913,7 @@
         <v>648</v>
       </c>
       <c r="D735" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="736" spans="1:4">
@@ -14921,7 +14927,7 @@
         <v>649</v>
       </c>
       <c r="D736" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="737" spans="1:4">
@@ -14935,7 +14941,7 @@
         <v>650</v>
       </c>
       <c r="D737" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="738" spans="1:4">
@@ -14949,7 +14955,7 @@
         <v>651</v>
       </c>
       <c r="D738" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="739" spans="1:4">
@@ -14963,7 +14969,7 @@
         <v>652</v>
       </c>
       <c r="D739" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="740" spans="1:4">
@@ -14977,7 +14983,7 @@
         <v>653</v>
       </c>
       <c r="D740" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="741" spans="1:4">
@@ -14991,7 +14997,7 @@
         <v>654</v>
       </c>
       <c r="D741" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="742" spans="1:4">
@@ -15005,7 +15011,7 @@
         <v>655</v>
       </c>
       <c r="D742" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="743" spans="1:4">
@@ -15019,7 +15025,7 @@
         <v>656</v>
       </c>
       <c r="D743" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="744" spans="1:4">
@@ -15033,7 +15039,7 @@
         <v>657</v>
       </c>
       <c r="D744" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="745" spans="1:4">
@@ -15047,7 +15053,7 @@
         <v>658</v>
       </c>
       <c r="D745" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="746" spans="1:4">
@@ -15072,7 +15078,7 @@
         <v>57</v>
       </c>
       <c r="D747" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="748" spans="1:4">
@@ -15086,7 +15092,7 @@
         <v>659</v>
       </c>
       <c r="D748" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="749" spans="1:4">
@@ -15100,7 +15106,7 @@
         <v>660</v>
       </c>
       <c r="D749" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="750" spans="1:4">
@@ -15114,7 +15120,7 @@
         <v>661</v>
       </c>
       <c r="D750" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="751" spans="1:4">
@@ -15128,7 +15134,7 @@
         <v>5</v>
       </c>
       <c r="D751" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="752" spans="1:4">
@@ -15142,7 +15148,7 @@
         <v>662</v>
       </c>
       <c r="D752" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="753" spans="1:4">
@@ -15156,7 +15162,7 @@
         <v>30</v>
       </c>
       <c r="D753" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="754" spans="1:4">
@@ -15170,7 +15176,7 @@
         <v>593</v>
       </c>
       <c r="D754" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="755" spans="1:4">
@@ -15184,7 +15190,7 @@
         <v>594</v>
       </c>
       <c r="D755" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="756" spans="1:4">
@@ -15198,7 +15204,7 @@
         <v>595</v>
       </c>
       <c r="D756" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="757" spans="1:4">
@@ -15212,7 +15218,7 @@
         <v>596</v>
       </c>
       <c r="D757" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="758" spans="1:4">
@@ -15226,7 +15232,7 @@
         <v>37</v>
       </c>
       <c r="D758" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="759" spans="1:4">
@@ -15251,7 +15257,7 @@
         <v>664</v>
       </c>
       <c r="D760" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="761" spans="1:4">
@@ -15265,7 +15271,7 @@
         <v>665</v>
       </c>
       <c r="D761" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="762" spans="1:4">
@@ -15279,7 +15285,7 @@
         <v>666</v>
       </c>
       <c r="D762" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="763" spans="1:4">
@@ -15293,7 +15299,7 @@
         <v>62</v>
       </c>
       <c r="D763" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="764" spans="1:4">
@@ -15307,7 +15313,7 @@
         <v>38</v>
       </c>
       <c r="D764" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="765" spans="1:4">
@@ -15321,7 +15327,7 @@
         <v>667</v>
       </c>
       <c r="D765" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="766" spans="1:4">
@@ -15335,7 +15341,7 @@
         <v>668</v>
       </c>
       <c r="D766" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="767" spans="1:4">
@@ -15349,7 +15355,7 @@
         <v>669</v>
       </c>
       <c r="D767" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="768" spans="1:4">
@@ -15363,7 +15369,7 @@
         <v>19</v>
       </c>
       <c r="D768" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="769" spans="1:4">
@@ -15377,7 +15383,7 @@
         <v>517</v>
       </c>
       <c r="D769" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="770" spans="1:4">
@@ -15391,7 +15397,7 @@
         <v>518</v>
       </c>
       <c r="D770" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="771" spans="1:4">
@@ -15405,7 +15411,7 @@
         <v>519</v>
       </c>
       <c r="D771" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="772" spans="1:4">
@@ -15419,7 +15425,7 @@
         <v>39</v>
       </c>
       <c r="D772" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="773" spans="1:4">
@@ -15433,7 +15439,7 @@
         <v>670</v>
       </c>
       <c r="D773" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="774" spans="1:4">
@@ -15447,7 +15453,7 @@
         <v>671</v>
       </c>
       <c r="D774" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="775" spans="1:4">
@@ -15461,7 +15467,7 @@
         <v>672</v>
       </c>
       <c r="D775" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="776" spans="1:4">
@@ -15475,7 +15481,7 @@
         <v>9</v>
       </c>
       <c r="D776" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="777" spans="1:4">
@@ -15489,7 +15495,7 @@
         <v>405</v>
       </c>
       <c r="D777" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="778" spans="1:4">
@@ -15503,7 +15509,7 @@
         <v>406</v>
       </c>
       <c r="D778" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="779" spans="1:4">
@@ -15517,7 +15523,7 @@
         <v>407</v>
       </c>
       <c r="D779" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="780" spans="1:4">
@@ -15531,7 +15537,7 @@
         <v>77</v>
       </c>
       <c r="D780" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="781" spans="1:4">
@@ -15545,7 +15551,7 @@
         <v>33</v>
       </c>
       <c r="D781" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="782" spans="1:4">
@@ -15559,7 +15565,7 @@
         <v>32</v>
       </c>
       <c r="D782" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="783" spans="1:4">
@@ -15573,7 +15579,7 @@
         <v>13</v>
       </c>
       <c r="D783" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="784" spans="1:4">
@@ -15587,7 +15593,7 @@
         <v>6</v>
       </c>
       <c r="D784" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="785" spans="1:4">
@@ -15601,7 +15607,7 @@
         <v>7</v>
       </c>
       <c r="D785" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="786" spans="1:4">
@@ -15615,7 +15621,7 @@
         <v>404</v>
       </c>
       <c r="D786" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="787" spans="1:4">
@@ -15640,7 +15646,7 @@
         <v>664</v>
       </c>
       <c r="D788" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="789" spans="1:4">
@@ -15654,7 +15660,7 @@
         <v>665</v>
       </c>
       <c r="D789" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="790" spans="1:4">
@@ -15668,7 +15674,7 @@
         <v>666</v>
       </c>
       <c r="D790" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="791" spans="1:4">
@@ -15682,7 +15688,7 @@
         <v>404</v>
       </c>
       <c r="D791" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="792" spans="1:4">
@@ -15696,7 +15702,7 @@
         <v>667</v>
       </c>
       <c r="D792" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="793" spans="1:4">
@@ -15710,7 +15716,7 @@
         <v>668</v>
       </c>
       <c r="D793" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="794" spans="1:4">
@@ -15724,7 +15730,7 @@
         <v>669</v>
       </c>
       <c r="D794" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="795" spans="1:4">
@@ -15738,7 +15744,7 @@
         <v>404</v>
       </c>
       <c r="D795" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="796" spans="1:4">
@@ -15752,7 +15758,7 @@
         <v>670</v>
       </c>
       <c r="D796" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="797" spans="1:4">
@@ -15766,7 +15772,7 @@
         <v>671</v>
       </c>
       <c r="D797" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="798" spans="1:4">
@@ -15780,7 +15786,7 @@
         <v>672</v>
       </c>
       <c r="D798" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="799" spans="1:4">
@@ -15794,7 +15800,7 @@
         <v>404</v>
       </c>
       <c r="D799" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="800" spans="1:4">
@@ -15819,7 +15825,7 @@
         <v>636</v>
       </c>
       <c r="D801" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="802" spans="1:4">
@@ -15833,7 +15839,7 @@
         <v>637</v>
       </c>
       <c r="D802" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="803" spans="1:4">
@@ -15847,7 +15853,7 @@
         <v>638</v>
       </c>
       <c r="D803" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="804" spans="1:4">
@@ -15861,7 +15867,7 @@
         <v>639</v>
       </c>
       <c r="D804" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="805" spans="1:4">
@@ -15875,7 +15881,7 @@
         <v>640</v>
       </c>
       <c r="D805" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="806" spans="1:4">
@@ -15889,7 +15895,7 @@
         <v>641</v>
       </c>
       <c r="D806" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="807" spans="1:4">
@@ -15903,7 +15909,7 @@
         <v>642</v>
       </c>
       <c r="D807" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="808" spans="1:4">
@@ -15917,7 +15923,7 @@
         <v>643</v>
       </c>
       <c r="D808" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="809" spans="1:4">
@@ -15931,7 +15937,7 @@
         <v>644</v>
       </c>
       <c r="D809" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="810" spans="1:4">
@@ -15945,7 +15951,7 @@
         <v>645</v>
       </c>
       <c r="D810" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="811" spans="1:4">
@@ -15959,7 +15965,7 @@
         <v>646</v>
       </c>
       <c r="D811" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="812" spans="1:4">
@@ -15973,7 +15979,7 @@
         <v>647</v>
       </c>
       <c r="D812" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="813" spans="1:4">
@@ -15987,7 +15993,7 @@
         <v>648</v>
       </c>
       <c r="D813" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="814" spans="1:4">
@@ -16001,7 +16007,7 @@
         <v>649</v>
       </c>
       <c r="D814" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="815" spans="1:4">
@@ -16015,7 +16021,7 @@
         <v>650</v>
       </c>
       <c r="D815" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="816" spans="1:4">
@@ -16029,7 +16035,7 @@
         <v>651</v>
       </c>
       <c r="D816" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="817" spans="1:4">
@@ -16043,7 +16049,7 @@
         <v>652</v>
       </c>
       <c r="D817" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="818" spans="1:4">
@@ -16057,7 +16063,7 @@
         <v>653</v>
       </c>
       <c r="D818" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="819" spans="1:4">
@@ -16071,7 +16077,7 @@
         <v>654</v>
       </c>
       <c r="D819" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="820" spans="1:4">
@@ -16085,7 +16091,7 @@
         <v>655</v>
       </c>
       <c r="D820" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="821" spans="1:4">
@@ -16099,7 +16105,7 @@
         <v>656</v>
       </c>
       <c r="D821" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="822" spans="1:4">
@@ -16113,7 +16119,7 @@
         <v>657</v>
       </c>
       <c r="D822" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="823" spans="1:4">
@@ -16127,7 +16133,7 @@
         <v>658</v>
       </c>
       <c r="D823" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="824" spans="1:4">
@@ -16163,7 +16169,7 @@
         <v>673</v>
       </c>
       <c r="D826" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="827" spans="1:4">
@@ -16177,7 +16183,7 @@
         <v>674</v>
       </c>
       <c r="D827" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="828" spans="1:4">
@@ -16191,7 +16197,7 @@
         <v>675</v>
       </c>
       <c r="D828" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="829" spans="1:4">
@@ -16205,7 +16211,7 @@
         <v>676</v>
       </c>
       <c r="D829" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="830" spans="1:4">
@@ -16219,7 +16225,7 @@
         <v>677</v>
       </c>
       <c r="D830" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="831" spans="1:4">
@@ -16233,7 +16239,7 @@
         <v>678</v>
       </c>
       <c r="D831" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="832" spans="1:4">
@@ -16247,7 +16253,7 @@
         <v>679</v>
       </c>
       <c r="D832" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="833" spans="1:4">
@@ -16272,7 +16278,7 @@
         <v>0</v>
       </c>
       <c r="D834" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="835" spans="1:4">
@@ -16286,7 +16292,7 @@
         <v>1</v>
       </c>
       <c r="D835" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="836" spans="1:4">
@@ -16300,7 +16306,7 @@
         <v>2</v>
       </c>
       <c r="D836" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="837" spans="1:4">
@@ -16314,7 +16320,7 @@
         <v>3</v>
       </c>
       <c r="D837" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="838" spans="1:4">
@@ -16339,7 +16345,7 @@
         <v>440</v>
       </c>
       <c r="D839" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="840" spans="1:4">
@@ -16353,7 +16359,7 @@
         <v>441</v>
       </c>
       <c r="D840" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="841" spans="1:4">
@@ -16367,7 +16373,7 @@
         <v>442</v>
       </c>
       <c r="D841" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="842" spans="1:4">
@@ -16381,7 +16387,7 @@
         <v>443</v>
       </c>
       <c r="D842" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="843" spans="1:4">
@@ -16395,7 +16401,7 @@
         <v>444</v>
       </c>
       <c r="D843" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="844" spans="1:4">
@@ -16409,7 +16415,7 @@
         <v>445</v>
       </c>
       <c r="D844" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="845" spans="1:4">
@@ -16423,7 +16429,7 @@
         <v>680</v>
       </c>
       <c r="D845" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="846" spans="1:4">
@@ -16437,7 +16443,7 @@
         <v>681</v>
       </c>
       <c r="D846" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="847" spans="1:4">
@@ -16451,7 +16457,7 @@
         <v>682</v>
       </c>
       <c r="D847" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="848" spans="1:4">
@@ -16465,7 +16471,7 @@
         <v>404</v>
       </c>
       <c r="D848" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="849" spans="1:4">
@@ -16479,7 +16485,7 @@
         <v>683</v>
       </c>
       <c r="D849" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="850" spans="1:4">
@@ -16493,7 +16499,7 @@
         <v>684</v>
       </c>
       <c r="D850" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="851" spans="1:4">
@@ -16507,7 +16513,7 @@
         <v>685</v>
       </c>
       <c r="D851" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="852" spans="1:4">
@@ -16521,7 +16527,7 @@
         <v>686</v>
       </c>
       <c r="D852" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="853" spans="1:4">
@@ -16535,7 +16541,7 @@
         <v>687</v>
       </c>
       <c r="D853" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="854" spans="1:4">
@@ -16549,7 +16555,7 @@
         <v>688</v>
       </c>
       <c r="D854" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="855" spans="1:4">
@@ -16563,7 +16569,7 @@
         <v>689</v>
       </c>
       <c r="D855" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="856" spans="1:4">
@@ -16577,7 +16583,7 @@
         <v>690</v>
       </c>
       <c r="D856" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="857" spans="1:4">
@@ -16591,7 +16597,7 @@
         <v>691</v>
       </c>
       <c r="D857" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="858" spans="1:4">
@@ -16605,7 +16611,7 @@
         <v>692</v>
       </c>
       <c r="D858" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="859" spans="1:4">
@@ -16619,7 +16625,7 @@
         <v>404</v>
       </c>
       <c r="D859" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="860" spans="1:4">
@@ -16633,7 +16639,7 @@
         <v>520</v>
       </c>
       <c r="D860" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="861" spans="1:4">
@@ -16647,7 +16653,7 @@
         <v>521</v>
       </c>
       <c r="D861" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="862" spans="1:4">
@@ -16705,7 +16711,7 @@
         <v>25</v>
       </c>
       <c r="D866" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="867" spans="1:4">
@@ -16719,7 +16725,7 @@
         <v>575</v>
       </c>
       <c r="D867" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="868" spans="1:4">
@@ -16733,7 +16739,7 @@
         <v>576</v>
       </c>
       <c r="D868" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="869" spans="1:4">
@@ -16747,7 +16753,7 @@
         <v>577</v>
       </c>
       <c r="D869" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="870" spans="1:4">
@@ -16761,7 +16767,7 @@
         <v>526</v>
       </c>
       <c r="D870" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="871" spans="1:4">
@@ -16775,7 +16781,7 @@
         <v>527</v>
       </c>
       <c r="D871" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="872" spans="1:4">
@@ -16789,7 +16795,7 @@
         <v>528</v>
       </c>
       <c r="D872" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="873" spans="1:4">
@@ -16814,7 +16820,7 @@
         <v>693</v>
       </c>
       <c r="D874" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="875" spans="1:4">
@@ -16828,7 +16834,7 @@
         <v>694</v>
       </c>
       <c r="D875" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="876" spans="1:4">
@@ -16842,7 +16848,7 @@
         <v>695</v>
       </c>
       <c r="D876" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="877" spans="1:4">
@@ -16856,7 +16862,7 @@
         <v>696</v>
       </c>
       <c r="D877" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="878" spans="1:4">
@@ -16870,7 +16876,7 @@
         <v>697</v>
       </c>
       <c r="D878" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="879" spans="1:4">
@@ -16884,7 +16890,7 @@
         <v>698</v>
       </c>
       <c r="D879" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="880" spans="1:4">
@@ -16898,7 +16904,7 @@
         <v>699</v>
       </c>
       <c r="D880" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="881" spans="1:4">
@@ -16912,7 +16918,7 @@
         <v>700</v>
       </c>
       <c r="D881" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="882" spans="1:4">
@@ -16926,7 +16932,7 @@
         <v>701</v>
       </c>
       <c r="D882" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="883" spans="1:4">
@@ -17061,7 +17067,7 @@
         <v>709</v>
       </c>
       <c r="D894" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="895" spans="1:4">
@@ -17075,7 +17081,7 @@
         <v>710</v>
       </c>
       <c r="D895" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="896" spans="1:4">
@@ -17089,7 +17095,7 @@
         <v>711</v>
       </c>
       <c r="D896" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="897" spans="1:4">
@@ -17103,7 +17109,7 @@
         <v>712</v>
       </c>
       <c r="D897" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="898" spans="1:4">
@@ -17117,7 +17123,7 @@
         <v>713</v>
       </c>
       <c r="D898" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="899" spans="1:4">
@@ -17131,7 +17137,7 @@
         <v>714</v>
       </c>
       <c r="D899" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="900" spans="1:4">
@@ -17145,7 +17151,7 @@
         <v>715</v>
       </c>
       <c r="D900" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="901" spans="1:4">
@@ -17159,7 +17165,7 @@
         <v>716</v>
       </c>
       <c r="D901" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="902" spans="1:4">
@@ -17184,7 +17190,7 @@
         <v>77</v>
       </c>
       <c r="D903" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="904" spans="1:4">
@@ -17198,7 +17204,7 @@
         <v>717</v>
       </c>
       <c r="D904" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="905" spans="1:4">
@@ -17212,7 +17218,7 @@
         <v>718</v>
       </c>
       <c r="D905" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="906" spans="1:4">
@@ -17226,7 +17232,7 @@
         <v>719</v>
       </c>
       <c r="D906" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="907" spans="1:4">
@@ -17240,7 +17246,7 @@
         <v>720</v>
       </c>
       <c r="D907" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="908" spans="1:4">
@@ -17254,7 +17260,7 @@
         <v>721</v>
       </c>
       <c r="D908" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="909" spans="1:4">
@@ -17268,7 +17274,7 @@
         <v>722</v>
       </c>
       <c r="D909" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="910" spans="1:4">
@@ -17282,7 +17288,7 @@
         <v>723</v>
       </c>
       <c r="D910" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="911" spans="1:4">
@@ -17296,7 +17302,7 @@
         <v>724</v>
       </c>
       <c r="D911" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="912" spans="1:4">
@@ -17310,7 +17316,7 @@
         <v>725</v>
       </c>
       <c r="D912" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="913" spans="1:4">
@@ -17324,7 +17330,7 @@
         <v>726</v>
       </c>
       <c r="D913" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="914" spans="1:4">
@@ -17338,7 +17344,7 @@
         <v>727</v>
       </c>
       <c r="D914" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="915" spans="1:4">
@@ -17352,7 +17358,7 @@
         <v>728</v>
       </c>
       <c r="D915" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="916" spans="1:4">
@@ -17366,7 +17372,7 @@
         <v>729</v>
       </c>
       <c r="D916" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="917" spans="1:4">
@@ -17380,7 +17386,7 @@
         <v>730</v>
       </c>
       <c r="D917" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="918" spans="1:4">
@@ -17394,7 +17400,7 @@
         <v>731</v>
       </c>
       <c r="D918" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="919" spans="1:4">
@@ -17408,7 +17414,7 @@
         <v>732</v>
       </c>
       <c r="D919" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="920" spans="1:4">
@@ -17422,7 +17428,7 @@
         <v>733</v>
       </c>
       <c r="D920" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="921" spans="1:4">
@@ -17436,7 +17442,7 @@
         <v>734</v>
       </c>
       <c r="D921" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="922" spans="1:4">
@@ -17450,7 +17456,7 @@
         <v>735</v>
       </c>
       <c r="D922" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="923" spans="1:4">
@@ -17464,7 +17470,7 @@
         <v>736</v>
       </c>
       <c r="D923" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="924" spans="1:4">
@@ -17478,7 +17484,7 @@
         <v>737</v>
       </c>
       <c r="D924" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="925" spans="1:4">
@@ -17492,7 +17498,7 @@
         <v>738</v>
       </c>
       <c r="D925" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="926" spans="1:4">
@@ -17506,7 +17512,7 @@
         <v>739</v>
       </c>
       <c r="D926" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="927" spans="1:4">
@@ -17520,7 +17526,7 @@
         <v>740</v>
       </c>
       <c r="D927" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="928" spans="1:4">
@@ -17534,7 +17540,7 @@
         <v>741</v>
       </c>
       <c r="D928" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="929" spans="1:4">
@@ -17548,7 +17554,7 @@
         <v>742</v>
       </c>
       <c r="D929" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="930" spans="1:4">
@@ -17562,7 +17568,7 @@
         <v>743</v>
       </c>
       <c r="D930" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="931" spans="1:4">
@@ -17576,7 +17582,7 @@
         <v>744</v>
       </c>
       <c r="D931" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="932" spans="1:4">
@@ -17590,7 +17596,7 @@
         <v>404</v>
       </c>
       <c r="D932" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="933" spans="1:4">
@@ -17604,7 +17610,7 @@
         <v>551</v>
       </c>
       <c r="D933" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="934" spans="1:4">
@@ -17618,7 +17624,7 @@
         <v>552</v>
       </c>
       <c r="D934" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="935" spans="1:4">
@@ -17632,7 +17638,7 @@
         <v>553</v>
       </c>
       <c r="D935" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="936" spans="1:4">
@@ -17646,7 +17652,7 @@
         <v>554</v>
       </c>
       <c r="D936" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="937" spans="1:4">
@@ -17660,7 +17666,7 @@
         <v>555</v>
       </c>
       <c r="D937" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="938" spans="1:4">
@@ -17674,7 +17680,7 @@
         <v>556</v>
       </c>
       <c r="D938" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="939" spans="1:4">
@@ -17688,7 +17694,7 @@
         <v>404</v>
       </c>
       <c r="D939" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="940" spans="1:4">
@@ -17801,7 +17807,7 @@
         <v>752</v>
       </c>
       <c r="D949" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="950" spans="1:4">
@@ -17815,7 +17821,7 @@
         <v>753</v>
       </c>
       <c r="D950" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="951" spans="1:4">
@@ -17829,7 +17835,7 @@
         <v>754</v>
       </c>
       <c r="D951" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="952" spans="1:4">
@@ -17843,7 +17849,7 @@
         <v>755</v>
       </c>
       <c r="D952" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="953" spans="1:4">
@@ -17857,7 +17863,7 @@
         <v>756</v>
       </c>
       <c r="D953" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="954" spans="1:4">
@@ -17871,7 +17877,7 @@
         <v>757</v>
       </c>
       <c r="D954" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="955" spans="1:4">
@@ -17885,7 +17891,7 @@
         <v>54</v>
       </c>
       <c r="D955" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="956" spans="1:4">
@@ -17987,7 +17993,7 @@
         <v>758</v>
       </c>
       <c r="D964" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="965" spans="1:4">
@@ -18001,7 +18007,7 @@
         <v>759</v>
       </c>
       <c r="D965" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="966" spans="1:4">
@@ -18015,7 +18021,7 @@
         <v>760</v>
       </c>
       <c r="D966" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="967" spans="1:4">
@@ -18029,7 +18035,7 @@
         <v>761</v>
       </c>
       <c r="D967" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="968" spans="1:4">
@@ -18043,7 +18049,7 @@
         <v>762</v>
       </c>
       <c r="D968" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="969" spans="1:4">
@@ -18057,7 +18063,7 @@
         <v>763</v>
       </c>
       <c r="D969" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="970" spans="1:4">
@@ -18071,7 +18077,7 @@
         <v>764</v>
       </c>
       <c r="D970" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="971" spans="1:4">
@@ -18085,7 +18091,7 @@
         <v>765</v>
       </c>
       <c r="D971" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="972" spans="1:4">
@@ -18099,7 +18105,7 @@
         <v>766</v>
       </c>
       <c r="D972" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="973" spans="1:4">
@@ -18113,7 +18119,7 @@
         <v>767</v>
       </c>
       <c r="D973" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="974" spans="1:4">
@@ -18127,7 +18133,7 @@
         <v>768</v>
       </c>
       <c r="D974" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="975" spans="1:4">
@@ -18141,7 +18147,7 @@
         <v>769</v>
       </c>
       <c r="D975" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="976" spans="1:4">
@@ -18155,7 +18161,7 @@
         <v>770</v>
       </c>
       <c r="D976" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="977" spans="1:4">
@@ -18169,7 +18175,7 @@
         <v>771</v>
       </c>
       <c r="D977" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="978" spans="1:4">
@@ -18183,7 +18189,7 @@
         <v>772</v>
       </c>
       <c r="D978" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="979" spans="1:4">
@@ -18197,7 +18203,7 @@
         <v>773</v>
       </c>
       <c r="D979" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="980" spans="1:4">
@@ -18211,7 +18217,7 @@
         <v>774</v>
       </c>
       <c r="D980" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="981" spans="1:4">
@@ -18225,7 +18231,7 @@
         <v>775</v>
       </c>
       <c r="D981" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="982" spans="1:4">
@@ -18239,7 +18245,7 @@
         <v>776</v>
       </c>
       <c r="D982" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="983" spans="1:4">
@@ -18253,7 +18259,7 @@
         <v>777</v>
       </c>
       <c r="D983" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="984" spans="1:4">
@@ -18267,7 +18273,7 @@
         <v>778</v>
       </c>
       <c r="D984" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="985" spans="1:4">
@@ -18281,7 +18287,7 @@
         <v>779</v>
       </c>
       <c r="D985" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="986" spans="1:4">
@@ -18295,7 +18301,7 @@
         <v>780</v>
       </c>
       <c r="D986" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="987" spans="1:4">
@@ -18309,7 +18315,7 @@
         <v>781</v>
       </c>
       <c r="D987" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="988" spans="1:4">
@@ -18334,7 +18340,7 @@
         <v>782</v>
       </c>
       <c r="D989" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="990" spans="1:4">
@@ -18348,7 +18354,7 @@
         <v>782</v>
       </c>
       <c r="D990" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="991" spans="1:4">
@@ -18362,7 +18368,7 @@
         <v>782</v>
       </c>
       <c r="D991" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="992" spans="1:4">
@@ -18376,7 +18382,7 @@
         <v>782</v>
       </c>
       <c r="D992" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="993" spans="1:4">
@@ -18390,7 +18396,7 @@
         <v>782</v>
       </c>
       <c r="D993" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="994" spans="1:4">
@@ -18404,7 +18410,7 @@
         <v>404</v>
       </c>
       <c r="D994" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="995" spans="1:4">
@@ -18418,7 +18424,7 @@
         <v>659</v>
       </c>
       <c r="D995" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="996" spans="1:4">
@@ -18432,7 +18438,7 @@
         <v>660</v>
       </c>
       <c r="D996" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="997" spans="1:4">
@@ -18446,7 +18452,7 @@
         <v>661</v>
       </c>
       <c r="D997" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="998" spans="1:4">
@@ -18460,7 +18466,7 @@
         <v>5</v>
       </c>
       <c r="D998" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="999" spans="1:4">
@@ -18474,7 +18480,7 @@
         <v>662</v>
       </c>
       <c r="D999" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="1000" spans="1:4">
@@ -18499,7 +18505,7 @@
         <v>783</v>
       </c>
       <c r="D1001" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1002" spans="1:4">
@@ -18513,7 +18519,7 @@
         <v>784</v>
       </c>
       <c r="D1002" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1003" spans="1:4">
@@ -18527,7 +18533,7 @@
         <v>785</v>
       </c>
       <c r="D1003" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1004" spans="1:4">
@@ -18552,7 +18558,7 @@
         <v>429</v>
       </c>
       <c r="D1005" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1006" spans="1:4">
@@ -18566,7 +18572,7 @@
         <v>430</v>
       </c>
       <c r="D1006" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1007" spans="1:4">
@@ -18580,7 +18586,7 @@
         <v>431</v>
       </c>
       <c r="D1007" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="1008" spans="1:4">
@@ -18594,7 +18600,7 @@
         <v>786</v>
       </c>
       <c r="D1008" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1009" spans="1:4">
@@ -18619,7 +18625,7 @@
         <v>426</v>
       </c>
       <c r="D1010" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1011" spans="1:4">
@@ -18633,7 +18639,7 @@
         <v>427</v>
       </c>
       <c r="D1011" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1012" spans="1:4">
@@ -18647,7 +18653,7 @@
         <v>428</v>
       </c>
       <c r="D1012" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="1013" spans="1:4">
@@ -18661,7 +18667,7 @@
         <v>787</v>
       </c>
       <c r="D1013" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1014" spans="1:4">
@@ -18675,7 +18681,7 @@
         <v>788</v>
       </c>
       <c r="D1014" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1015" spans="1:4">
@@ -18689,7 +18695,7 @@
         <v>789</v>
       </c>
       <c r="D1015" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1016" spans="1:4">
@@ -18703,7 +18709,7 @@
         <v>404</v>
       </c>
       <c r="D1016" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1017" spans="1:4">
@@ -18717,7 +18723,7 @@
         <v>434</v>
       </c>
       <c r="D1017" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1018" spans="1:4">
@@ -18731,7 +18737,7 @@
         <v>435</v>
       </c>
       <c r="D1018" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="1019" spans="1:4">
@@ -18745,7 +18751,7 @@
         <v>436</v>
       </c>
       <c r="D1019" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="1020" spans="1:4">
@@ -18770,7 +18776,7 @@
         <v>404</v>
       </c>
       <c r="D1021" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="1022" spans="1:4">
@@ -18784,7 +18790,7 @@
         <v>71</v>
       </c>
       <c r="D1022" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1023" spans="1:4">
@@ -18798,7 +18804,7 @@
         <v>790</v>
       </c>
       <c r="D1023" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1024" spans="1:4">
@@ -18812,7 +18818,7 @@
         <v>791</v>
       </c>
       <c r="D1024" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1025" spans="1:4">
@@ -18826,7 +18832,7 @@
         <v>792</v>
       </c>
       <c r="D1025" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1026" spans="1:4">
@@ -18840,7 +18846,7 @@
         <v>793</v>
       </c>
       <c r="D1026" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1027" spans="1:4">
@@ -18854,7 +18860,7 @@
         <v>794</v>
       </c>
       <c r="D1027" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1028" spans="1:4">
@@ -18868,7 +18874,7 @@
         <v>795</v>
       </c>
       <c r="D1028" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="1029" spans="1:4">
@@ -18882,7 +18888,7 @@
         <v>796</v>
       </c>
       <c r="D1029" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1030" spans="1:4">
@@ -18896,7 +18902,7 @@
         <v>797</v>
       </c>
       <c r="D1030" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1031" spans="1:4">
@@ -18910,7 +18916,7 @@
         <v>798</v>
       </c>
       <c r="D1031" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="1032" spans="1:4">
@@ -18924,7 +18930,15 @@
         <v>799</v>
       </c>
       <c r="D1032" t="s">
-        <v>1501</v>
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:4">
+      <c r="C1033" t="s">
+        <v>800</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>1503</v>
       </c>
     </row>
   </sheetData>
